--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.346</v>
+        <v>6.7479</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1019</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.401890440004495</v>
+        <v>2.3046</v>
       </c>
       <c r="E2" t="n">
-        <v>91.2705</v>
+        <v>6.7479</v>
       </c>
       <c r="F2" t="n">
-        <v>37.99768429849987</v>
+        <v>2.7093</v>
       </c>
       <c r="G2" t="n">
-        <v>53.27278880657579</v>
+        <v>4.0386</v>
       </c>
       <c r="H2" t="n">
-        <v>40.2083970922117</v>
+        <v>2.7093</v>
       </c>
       <c r="I2" t="n">
-        <v>20.7527210798512</v>
+        <v>2.196</v>
       </c>
       <c r="J2" t="n">
-        <v>53.27278880657579</v>
+        <v>4.0386</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -541,7 +529,7 @@
         <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>74.02549999999999</v>
+        <v>6.2346</v>
       </c>
       <c r="N2" t="n">
         <v>120</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.283</v>
+        <v>5.0135</v>
       </c>
       <c r="C3" t="n">
-        <v>0.94245</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.849550338226265</v>
+        <v>1.604</v>
       </c>
       <c r="E3" t="n">
-        <v>67.2372</v>
+        <v>5.0135</v>
       </c>
       <c r="F3" t="n">
-        <v>29.90578902382029</v>
+        <v>1.8087</v>
       </c>
       <c r="G3" t="n">
-        <v>37.33137504435166</v>
+        <v>3.2047</v>
       </c>
       <c r="H3" t="n">
-        <v>29.90578902382029</v>
+        <v>1.8087</v>
       </c>
       <c r="I3" t="n">
-        <v>15.43524594777821</v>
+        <v>1.466</v>
       </c>
       <c r="J3" t="n">
-        <v>37.33137504435166</v>
+        <v>3.2047</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -587,7 +575,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>52.7666</v>
+        <v>4.6707</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -596,369 +584,369 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7052</v>
+        <v>3.8752</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5557799999999999</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8543419526103661</v>
+        <v>1.1441</v>
       </c>
       <c r="E4" t="n">
-        <v>23.9339</v>
+        <v>3.8752</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.000089728621345</v>
+        <v>3.4935</v>
       </c>
       <c r="G4" t="n">
-        <v>28.93395097553932</v>
+        <v>0.3817</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.000089728621345</v>
+        <v>3.4935</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.580691472836823</v>
+        <v>2.8316</v>
       </c>
       <c r="J4" t="n">
-        <v>28.93395097553932</v>
+        <v>0.3817</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>26.3533</v>
+        <v>3.2133</v>
       </c>
       <c r="N4" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6032</v>
+        <v>3.4065</v>
       </c>
       <c r="C5" t="n">
-        <v>0.54048</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8231025083372021</v>
+        <v>0.9548</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5746</v>
+        <v>3.4065</v>
       </c>
       <c r="F5" t="n">
-        <v>19.90213772494819</v>
+        <v>3.921</v>
       </c>
       <c r="G5" t="n">
-        <v>2.672439240526245</v>
+        <v>-0.5145</v>
       </c>
       <c r="H5" t="n">
-        <v>19.90213772494819</v>
+        <v>3.921</v>
       </c>
       <c r="I5" t="n">
-        <v>11.04247641513254</v>
+        <v>3.1781</v>
       </c>
       <c r="J5" t="n">
-        <v>2.672439240526245</v>
+        <v>-0.5145</v>
       </c>
       <c r="K5" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M5" t="n">
-        <v>13.7149</v>
+        <v>2.6636</v>
       </c>
       <c r="N5" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3294</v>
+        <v>3.2312</v>
       </c>
       <c r="C6" t="n">
-        <v>0.49941</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7417792095013083</v>
+        <v>0.884</v>
       </c>
       <c r="E6" t="n">
-        <v>19.0361</v>
+        <v>3.2312</v>
       </c>
       <c r="F6" t="n">
-        <v>16.38479800683401</v>
+        <v>3.7219</v>
       </c>
       <c r="G6" t="n">
-        <v>2.651256286592529</v>
+        <v>-0.4907</v>
       </c>
       <c r="H6" t="n">
-        <v>16.38479800683401</v>
+        <v>3.7219</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4566699390111</v>
+        <v>3.0167</v>
       </c>
       <c r="J6" t="n">
-        <v>2.651256286592529</v>
+        <v>-0.4907</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M6" t="n">
-        <v>11.1079</v>
+        <v>2.526</v>
       </c>
       <c r="N6" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1388</v>
+        <v>2.9554</v>
       </c>
       <c r="C7" t="n">
-        <v>0.47082</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.687292259266604</v>
+        <v>0.7726</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6652</v>
+        <v>2.9554</v>
       </c>
       <c r="F7" t="n">
-        <v>8.379675465140174</v>
+        <v>1.3045</v>
       </c>
       <c r="G7" t="n">
-        <v>8.285553843366436</v>
+        <v>1.6509</v>
       </c>
       <c r="H7" t="n">
-        <v>8.379675465140174</v>
+        <v>1.3045</v>
       </c>
       <c r="I7" t="n">
-        <v>4.324993788459444</v>
+        <v>1.0574</v>
       </c>
       <c r="J7" t="n">
-        <v>8.285553843366436</v>
+        <v>1.6509</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M7" t="n">
-        <v>12.6105</v>
+        <v>2.7083</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9659</v>
+        <v>2.6465</v>
       </c>
       <c r="C8" t="n">
-        <v>0.444885</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6393760852877537</v>
+        <v>0.6478</v>
       </c>
       <c r="E8" t="n">
-        <v>14.5803</v>
+        <v>2.6465</v>
       </c>
       <c r="F8" t="n">
-        <v>14.31058930442442</v>
+        <v>2.6465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2697212857195588</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>14.31058930442442</v>
+        <v>2.6465</v>
       </c>
       <c r="I8" t="n">
-        <v>14.03361015659685</v>
+        <v>2.6465</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2697212857195588</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="L8" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>14.3033</v>
+        <v>2.6465</v>
       </c>
       <c r="N8" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4077</v>
+        <v>2.5899</v>
       </c>
       <c r="C9" t="n">
-        <v>0.361155</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4937279925717942</v>
+        <v>0.6249</v>
       </c>
       <c r="E9" t="n">
-        <v>8.242900000000001</v>
+        <v>2.5899</v>
       </c>
       <c r="F9" t="n">
-        <v>29.01533564460183</v>
+        <v>1.875</v>
       </c>
       <c r="G9" t="n">
-        <v>-20.77243494305527</v>
+        <v>0.7149</v>
       </c>
       <c r="H9" t="n">
-        <v>29.01533564460183</v>
+        <v>1.875</v>
       </c>
       <c r="I9" t="n">
-        <v>32.19766277981622</v>
+        <v>1.5197</v>
       </c>
       <c r="J9" t="n">
-        <v>-20.77243494305527</v>
+        <v>0.7149</v>
       </c>
       <c r="K9" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>11.4252</v>
+        <v>2.2346</v>
       </c>
       <c r="N9" t="n">
-        <v>131</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2809</v>
+        <v>1.9611</v>
       </c>
       <c r="C10" t="n">
-        <v>0.342135</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4625119117315893</v>
+        <v>0.3709</v>
       </c>
       <c r="E10" t="n">
-        <v>6.8846</v>
+        <v>1.9611</v>
       </c>
       <c r="F10" t="n">
-        <v>6.884633004998184</v>
+        <v>-0.5547</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.5158</v>
       </c>
       <c r="H10" t="n">
-        <v>6.884633004998184</v>
+        <v>-0.5547</v>
       </c>
       <c r="I10" t="n">
-        <v>7.017883966385245</v>
+        <v>-0.4496</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2.5158</v>
       </c>
       <c r="K10" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
-        <v>7.0179</v>
+        <v>2.0662</v>
       </c>
       <c r="N10" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0153</v>
+        <v>1.8629</v>
       </c>
       <c r="C11" t="n">
-        <v>0.302295</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3991795180118373</v>
+        <v>0.3312</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1289</v>
+        <v>1.8629</v>
       </c>
       <c r="F11" t="n">
-        <v>26.13828874086632</v>
+        <v>2.1528</v>
       </c>
       <c r="G11" t="n">
-        <v>-22.00936184051884</v>
+        <v>-0.2899</v>
       </c>
       <c r="H11" t="n">
-        <v>26.13828874086632</v>
+        <v>2.1528</v>
       </c>
       <c r="I11" t="n">
-        <v>29.00506879631617</v>
+        <v>1.7449</v>
       </c>
       <c r="J11" t="n">
-        <v>-22.00936184051884</v>
+        <v>-0.2899</v>
       </c>
       <c r="K11" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="L11" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>6.9957</v>
+        <v>1.455</v>
       </c>
       <c r="N11" t="n">
-        <v>131</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -968,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0069</v>
+        <v>1.7453</v>
       </c>
       <c r="C12" t="n">
-        <v>0.301035</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3972163377618113</v>
+        <v>0.2837</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0435</v>
+        <v>1.7453</v>
       </c>
       <c r="F12" t="n">
-        <v>4.043505404620257</v>
+        <v>1.7453</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.043505404620257</v>
+        <v>1.7453</v>
       </c>
       <c r="I12" t="n">
-        <v>6.365260120821566</v>
+        <v>1.7453</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1001,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>6.3653</v>
+        <v>1.7453</v>
       </c>
       <c r="N12" t="n">
         <v>122</v>
@@ -1010,633 +998,633 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5992</v>
+        <v>1.7079</v>
       </c>
       <c r="C13" t="n">
-        <v>0.23988</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3054341126618985</v>
+        <v>0.2686</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0499</v>
+        <v>1.7079</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0498960816337388</v>
+        <v>0.2974</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.4105</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0498960816337388</v>
+        <v>0.2974</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04442360816423196</v>
+        <v>0.241</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.4105</v>
       </c>
       <c r="K13" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0444</v>
+        <v>1.6515</v>
       </c>
       <c r="N13" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>deco</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5776</v>
+        <v>1.3998</v>
       </c>
       <c r="C14" t="n">
-        <v>0.23664</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3007353830606738</v>
+        <v>0.1441</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1546</v>
+        <v>1.3998</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1545540754769301</v>
+        <v>1.592</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.1922</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1545540754769301</v>
+        <v>1.592</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2093958441945505</v>
+        <v>1.2904</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.1922</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2094</v>
+        <v>1.0982</v>
       </c>
       <c r="N14" t="n">
-        <v>105</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.509</v>
+        <v>1.3866</v>
       </c>
       <c r="C15" t="n">
-        <v>0.22635</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2859435016261264</v>
+        <v>0.1388</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7982</v>
+        <v>1.3866</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.395416354765721</v>
+        <v>1.6358</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5972409731239683</v>
+        <v>-0.2492</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.395416354765721</v>
+        <v>1.6358</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.368408296286385</v>
+        <v>1.3259</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5972409731239683</v>
+        <v>-0.2492</v>
       </c>
       <c r="K15" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L15" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7712</v>
+        <v>1.0767</v>
       </c>
       <c r="N15" t="n">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.149</v>
+        <v>1.1865</v>
       </c>
       <c r="C16" t="n">
-        <v>0.17235</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2110685777072514</v>
+        <v>0.058</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.0561</v>
+        <v>1.1865</v>
       </c>
       <c r="F16" t="n">
-        <v>3.223602482978119</v>
+        <v>0.4297</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.279720172019978</v>
+        <v>0.7568</v>
       </c>
       <c r="H16" t="n">
-        <v>3.223602482978119</v>
+        <v>0.4297</v>
       </c>
       <c r="I16" t="n">
-        <v>3.57715888433701</v>
+        <v>0.3483</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.279720172019978</v>
+        <v>0.7568</v>
       </c>
       <c r="K16" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7026</v>
+        <v>1.1051</v>
       </c>
       <c r="N16" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>deco</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1443</v>
+        <v>1.184</v>
       </c>
       <c r="C17" t="n">
-        <v>0.171645</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2101123156878591</v>
+        <v>0.0569</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.0977</v>
+        <v>1.184</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.09772636557706</v>
+        <v>1.184</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.09772636557706</v>
+        <v>1.184</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.450614407747114</v>
+        <v>1.184</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.4506</v>
+        <v>1.184</v>
       </c>
       <c r="N17" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7729</v>
+        <v>1.1796</v>
       </c>
       <c r="C18" t="n">
-        <v>0.115935</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1374848353297962</v>
+        <v>0.0552</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.2579</v>
+        <v>1.1796</v>
       </c>
       <c r="F18" t="n">
-        <v>3.370227705377406</v>
+        <v>1.3006</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.62810607584693</v>
+        <v>-0.121</v>
       </c>
       <c r="H18" t="n">
-        <v>3.370227705377406</v>
+        <v>1.3006</v>
       </c>
       <c r="I18" t="n">
-        <v>1.86993279137069</v>
+        <v>1.0542</v>
       </c>
       <c r="J18" t="n">
-        <v>-10.62810607584693</v>
+        <v>-0.121</v>
       </c>
       <c r="K18" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L18" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M18" t="n">
-        <v>-8.7582</v>
+        <v>0.9332</v>
       </c>
       <c r="N18" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5059</v>
+        <v>1.026</v>
       </c>
       <c r="C19" t="n">
-        <v>0.07588499999999999</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08797309851763895</v>
+        <v>-0.0069</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.4122</v>
+        <v>1.026</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.412222891045696</v>
+        <v>0.999</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.412222891045696</v>
+        <v>0.999</v>
       </c>
       <c r="I19" t="n">
-        <v>-14.81666055106548</v>
+        <v>0.8097</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="K19" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>-14.8167</v>
+        <v>0.8367</v>
       </c>
       <c r="N19" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aNdu</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4992</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07487999999999999</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0867567338845865</v>
+        <v>-0.0225</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.4651</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.465149099071501</v>
+        <v>0.9094</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="H20" t="n">
-        <v>-9.465149099071501</v>
+        <v>0.9094</v>
       </c>
       <c r="I20" t="n">
-        <v>-9.648345533247078</v>
+        <v>0.7371</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="K20" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M20" t="n">
-        <v>-9.648300000000001</v>
+        <v>0.8150999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.114</v>
+        <v>0.899</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01917945141176629</v>
+        <v>-0.0582</v>
       </c>
       <c r="E21" t="n">
-        <v>-12.4056</v>
+        <v>0.899</v>
       </c>
       <c r="F21" t="n">
-        <v>5.318021166663746</v>
+        <v>0.899</v>
       </c>
       <c r="G21" t="n">
-        <v>-17.72357909774781</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.318021166663746</v>
+        <v>0.899</v>
       </c>
       <c r="I21" t="n">
-        <v>5.901288004297834</v>
+        <v>0.899</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.72357909774781</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-11.8223</v>
+        <v>0.899</v>
       </c>
       <c r="N21" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1457</v>
+        <v>0.8818</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.021855</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.02457761181354758</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.3095</v>
+        <v>0.8818</v>
       </c>
       <c r="F22" t="n">
-        <v>5.054137649641934</v>
+        <v>0.8818</v>
       </c>
       <c r="G22" t="n">
-        <v>-19.36364392642033</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.054137649641934</v>
+        <v>0.8818</v>
       </c>
       <c r="I22" t="n">
-        <v>4.956315630616606</v>
+        <v>0.8818</v>
       </c>
       <c r="J22" t="n">
-        <v>-19.36364392642033</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-14.4073</v>
+        <v>0.8818</v>
       </c>
       <c r="N22" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NikoM</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.2685</v>
+        <v>0.7978</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.040275</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.04576513281426508</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.2314</v>
+        <v>0.7978</v>
       </c>
       <c r="F23" t="n">
-        <v>-15.23141333783873</v>
+        <v>0.7978</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-15.23141333783873</v>
+        <v>0.7978</v>
       </c>
       <c r="I23" t="n">
-        <v>-20.63610839320086</v>
+        <v>0.7978</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-20.6361</v>
+        <v>0.7978</v>
       </c>
       <c r="N23" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>reversive</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.4852</v>
+        <v>0.4715</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07278</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08422835654237096</v>
+        <v>-0.2309</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.905</v>
+        <v>0.4715</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.90501722688659</v>
+        <v>0.4715</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-16.90501722688659</v>
+        <v>0.4715</v>
       </c>
       <c r="I24" t="n">
-        <v>-22.90357172674957</v>
+        <v>0.4715</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-22.9036</v>
+        <v>0.4715</v>
       </c>
       <c r="N24" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6667999999999999</v>
+        <v>0.3185</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.10002</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1175417121746952</v>
+        <v>-0.2927</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.3545</v>
+        <v>0.3185</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.35454111332963</v>
+        <v>2.3185</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H25" t="n">
-        <v>-18.35454111332963</v>
+        <v>2.3185</v>
       </c>
       <c r="I25" t="n">
-        <v>-16.34146241057735</v>
+        <v>1.8792</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K25" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>-16.3415</v>
+        <v>-0.1208</v>
       </c>
       <c r="N25" t="n">
-        <v>69</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7746</v>
+        <v>0.2419</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.11619</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1377945870519437</v>
+        <v>-0.3236</v>
       </c>
       <c r="E26" t="n">
-        <v>-19.2358</v>
+        <v>0.2419</v>
       </c>
       <c r="F26" t="n">
-        <v>14.53496973003343</v>
+        <v>0.2289</v>
       </c>
       <c r="G26" t="n">
-        <v>-33.77074977431088</v>
+        <v>0.013</v>
       </c>
       <c r="H26" t="n">
-        <v>14.53496973003343</v>
+        <v>0.2289</v>
       </c>
       <c r="I26" t="n">
-        <v>8.064563850212096</v>
+        <v>0.1856</v>
       </c>
       <c r="J26" t="n">
-        <v>-33.77074977431088</v>
+        <v>0.013</v>
       </c>
       <c r="K26" t="n">
         <v>43</v>
@@ -1645,7 +1633,7 @@
         <v>117</v>
       </c>
       <c r="M26" t="n">
-        <v>-25.7062</v>
+        <v>0.1986</v>
       </c>
       <c r="N26" t="n">
         <v>160</v>
@@ -1654,262 +1642,262 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Noktse</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8457</v>
+        <v>0.1508</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.126855</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1513633782406939</v>
+        <v>-0.3604</v>
       </c>
       <c r="E27" t="n">
-        <v>-19.8262</v>
+        <v>0.1508</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.82618249893642</v>
+        <v>0.1658</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="H27" t="n">
-        <v>-19.82618249893642</v>
+        <v>0.1658</v>
       </c>
       <c r="I27" t="n">
-        <v>-26.86127951468804</v>
+        <v>0.1344</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M27" t="n">
-        <v>-26.8613</v>
+        <v>0.1194</v>
       </c>
       <c r="N27" t="n">
-        <v>105</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8963</v>
+        <v>-0.1378</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.134445</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1611211068309885</v>
+        <v>-0.477</v>
       </c>
       <c r="E28" t="n">
-        <v>-20.2508</v>
+        <v>-0.1378</v>
       </c>
       <c r="F28" t="n">
-        <v>-20.25075878074863</v>
+        <v>-0.1378</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-20.25075878074863</v>
+        <v>-0.1378</v>
       </c>
       <c r="I28" t="n">
-        <v>-27.43651189649814</v>
+        <v>-0.1378</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-27.4365</v>
+        <v>-0.1378</v>
       </c>
       <c r="N28" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.3339</v>
+        <v>-0.1744</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.200085</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2489577713939515</v>
+        <v>-0.4918</v>
       </c>
       <c r="E29" t="n">
-        <v>-24.0727</v>
+        <v>-0.1744</v>
       </c>
       <c r="F29" t="n">
-        <v>-24.07268968421964</v>
+        <v>-0.1744</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-24.07268968421964</v>
+        <v>-0.1744</v>
       </c>
       <c r="I29" t="n">
-        <v>-21.43245920272458</v>
+        <v>-0.1744</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-21.4325</v>
+        <v>-0.1744</v>
       </c>
       <c r="N29" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.3658</v>
+        <v>-0.3852</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.20487</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2556224069303296</v>
+        <v>-0.577</v>
       </c>
       <c r="E30" t="n">
-        <v>-24.3627</v>
+        <v>-0.3852</v>
       </c>
       <c r="F30" t="n">
-        <v>-24.36267993650882</v>
+        <v>-0.3852</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-24.36267993650882</v>
+        <v>-0.3852</v>
       </c>
       <c r="I30" t="n">
-        <v>-38.35157357747195</v>
+        <v>-0.3852</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-38.3516</v>
+        <v>-0.3852</v>
       </c>
       <c r="N30" t="n">
-        <v>122</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>Noktse</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.3673</v>
+        <v>-0.3901</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.205095</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2559283699893166</v>
+        <v>-0.579</v>
       </c>
       <c r="E31" t="n">
-        <v>-24.376</v>
+        <v>-0.3901</v>
       </c>
       <c r="F31" t="n">
-        <v>-24.37599293827501</v>
+        <v>-0.3901</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-24.37599293827501</v>
+        <v>-0.3901</v>
       </c>
       <c r="I31" t="n">
-        <v>-21.70249693859324</v>
+        <v>-0.3901</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-21.7025</v>
+        <v>-0.3901</v>
       </c>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>aNdu</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.3918</v>
+        <v>-0.3945</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.20877</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2610731531932977</v>
+        <v>-0.5807</v>
       </c>
       <c r="E32" t="n">
-        <v>-24.5999</v>
+        <v>-0.3945</v>
       </c>
       <c r="F32" t="n">
-        <v>-24.59985168811244</v>
+        <v>-0.3945</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-24.59985168811244</v>
+        <v>-0.3945</v>
       </c>
       <c r="I32" t="n">
-        <v>-25.07597784981784</v>
+        <v>-0.3945</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1921,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-25.076</v>
+        <v>-0.3945</v>
       </c>
       <c r="N32" t="n">
         <v>79</v>
@@ -1930,231 +1918,231 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.7745</v>
+        <v>-0.4475</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.266175</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3441343994129286</v>
+        <v>-0.6021</v>
       </c>
       <c r="E33" t="n">
-        <v>-28.214</v>
+        <v>-0.4475</v>
       </c>
       <c r="F33" t="n">
-        <v>5.859299647408325</v>
+        <v>-0.4475</v>
       </c>
       <c r="G33" t="n">
-        <v>-34.07329521708931</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>5.859299647408325</v>
+        <v>-0.4475</v>
       </c>
       <c r="I33" t="n">
-        <v>5.745893847781067</v>
+        <v>-0.4475</v>
       </c>
       <c r="J33" t="n">
-        <v>-34.07329521708931</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L33" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-28.3274</v>
+        <v>-0.4475</v>
       </c>
       <c r="N33" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>NikoM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.8016</v>
+        <v>-0.599</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.27024</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3502139960057467</v>
+        <v>-0.6633</v>
       </c>
       <c r="E34" t="n">
-        <v>-28.4785</v>
+        <v>-0.599</v>
       </c>
       <c r="F34" t="n">
-        <v>-28.47852972764725</v>
+        <v>-0.599</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-28.47852972764725</v>
+        <v>-0.599</v>
       </c>
       <c r="I34" t="n">
-        <v>-29.02972707721461</v>
+        <v>-0.599</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-29.0297</v>
+        <v>-0.599</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>reversive</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.8577</v>
+        <v>-0.764</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.278655</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3628999394852997</v>
+        <v>-0.73</v>
       </c>
       <c r="E35" t="n">
-        <v>-29.0305</v>
+        <v>-0.764</v>
       </c>
       <c r="F35" t="n">
-        <v>-29.03051789415413</v>
+        <v>-0.764</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-29.03051789415413</v>
+        <v>-0.764</v>
       </c>
       <c r="I35" t="n">
-        <v>-45.6996539753136</v>
+        <v>-0.764</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-45.6997</v>
+        <v>-0.764</v>
       </c>
       <c r="N35" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.9526</v>
+        <v>-1.0796</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.29289</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3846281811341827</v>
+        <v>-0.8575</v>
       </c>
       <c r="E36" t="n">
-        <v>-29.976</v>
+        <v>-1.0796</v>
       </c>
       <c r="F36" t="n">
-        <v>-9.196503706709253</v>
+        <v>-1.0796</v>
       </c>
       <c r="G36" t="n">
-        <v>-20.77944897426359</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-9.196503706709253</v>
+        <v>-1.0796</v>
       </c>
       <c r="I36" t="n">
-        <v>-9.018506860772945</v>
+        <v>-1.0796</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.77944897426359</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="L36" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-29.798</v>
+        <v>-1.0796</v>
       </c>
       <c r="N36" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.2744</v>
+        <v>-1.1661</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.34116</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4609234079327973</v>
+        <v>-0.8924</v>
       </c>
       <c r="E37" t="n">
-        <v>-33.2957</v>
+        <v>-1.1661</v>
       </c>
       <c r="F37" t="n">
-        <v>-15.10919611440798</v>
+        <v>-1.1661</v>
       </c>
       <c r="G37" t="n">
-        <v>-18.18649880108395</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-15.10919611440798</v>
+        <v>-1.1661</v>
       </c>
       <c r="I37" t="n">
-        <v>-16.76633375276241</v>
+        <v>-1.1661</v>
       </c>
       <c r="J37" t="n">
-        <v>-18.18649880108395</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L37" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-34.9528</v>
+        <v>-1.1661</v>
       </c>
       <c r="N37" t="n">
-        <v>131</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -2164,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.4354</v>
+        <v>-1.2739</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.36531</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.5006454144897095</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-35.0241</v>
+        <v>-1.2739</v>
       </c>
       <c r="F38" t="n">
-        <v>-35.02407070438493</v>
+        <v>-1.2739</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-35.02407070438493</v>
+        <v>-1.2739</v>
       </c>
       <c r="I38" t="n">
-        <v>-35.70195594382464</v>
+        <v>-1.2739</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2197,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-35.702</v>
+        <v>-1.2739</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2206,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.6506</v>
+        <v>-1.6124</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3975899999999999</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5554408710840794</v>
+        <v>-1.0727</v>
       </c>
       <c r="E39" t="n">
-        <v>-37.4083</v>
+        <v>-1.6124</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.139519917605641</v>
+        <v>-1.6124</v>
       </c>
       <c r="G39" t="n">
-        <v>-35.26879943704204</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.139519917605641</v>
+        <v>-1.6124</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.187088470413452</v>
+        <v>-1.6124</v>
       </c>
       <c r="J39" t="n">
-        <v>-35.26879943704204</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L39" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-36.4559</v>
+        <v>-1.6124</v>
       </c>
       <c r="N39" t="n">
-        <v>160</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -2256,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.7126</v>
+        <v>-1.6313</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.55689</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.8566408320824844</v>
+        <v>-1.0804</v>
       </c>
       <c r="E40" t="n">
-        <v>-50.5141</v>
+        <v>-1.6313</v>
       </c>
       <c r="F40" t="n">
-        <v>-50.51407017967917</v>
+        <v>-1.6313</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-50.51407017967917</v>
+        <v>-1.6313</v>
       </c>
       <c r="I40" t="n">
-        <v>-44.97381732126274</v>
+        <v>-1.6313</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2289,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-44.9738</v>
+        <v>-1.6313</v>
       </c>
       <c r="N40" t="n">
         <v>69</v>
@@ -2298,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.9471</v>
+        <v>-1.9126</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.742065</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.28079183670851</v>
+        <v>-1.194</v>
       </c>
       <c r="E41" t="n">
-        <v>-68.9696</v>
+        <v>-1.9126</v>
       </c>
       <c r="F41" t="n">
-        <v>29.24957182783059</v>
+        <v>-1.5079</v>
       </c>
       <c r="G41" t="n">
-        <v>-98.21921338404425</v>
+        <v>-0.4047</v>
       </c>
       <c r="H41" t="n">
-        <v>29.24957182783059</v>
+        <v>-1.5079</v>
       </c>
       <c r="I41" t="n">
-        <v>16.22879469157052</v>
+        <v>-1.2222</v>
       </c>
       <c r="J41" t="n">
-        <v>-98.21921338404425</v>
+        <v>-0.4047</v>
       </c>
       <c r="K41" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L41" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-81.99039999999999</v>
+        <v>-1.6269</v>
       </c>
       <c r="N41" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1.081192189227114</v>
+        <v>1.3022</v>
       </c>
       <c r="J2" t="n">
-        <v>19.46145940608806</v>
+        <v>23.4396</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9062558367199309</v>
+        <v>1.0384</v>
       </c>
       <c r="J3" t="n">
-        <v>16.31260506095876</v>
+        <v>18.6912</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.519011733822025</v>
+        <v>0.5942</v>
       </c>
       <c r="J4" t="n">
-        <v>9.342211208796451</v>
+        <v>10.6956</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3615207682303527</v>
+        <v>0.3891</v>
       </c>
       <c r="J5" t="n">
-        <v>6.507373828146349</v>
+        <v>7.0038</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06095006304971157</v>
+        <v>-0.2079</v>
       </c>
       <c r="J6" t="n">
-        <v>1.097101134894808</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2460181406862954</v>
+        <v>0.5678</v>
       </c>
       <c r="J7" t="n">
-        <v>4.428326532353318</v>
+        <v>10.2204</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9198118266220169</v>
+        <v>-0.215</v>
       </c>
       <c r="J8" t="n">
-        <v>-16.5566128791963</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.062928161593649</v>
+        <v>-0.2773</v>
       </c>
       <c r="J9" t="n">
-        <v>-19.13270690868568</v>
+        <v>-4.9914</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.271333115861389</v>
+        <v>-0.3903</v>
       </c>
       <c r="J10" t="n">
-        <v>-22.883996085505</v>
+        <v>-7.0254</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.720976183792801</v>
+        <v>-0.6734</v>
       </c>
       <c r="J11" t="n">
-        <v>-30.97757130827042</v>
+        <v>-12.1212</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.235480706837448</v>
+        <v>1.5465</v>
       </c>
       <c r="J12" t="n">
-        <v>21.00317201623661</v>
+        <v>26.2905</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.72</v>
       </c>
       <c r="I13" t="n">
-        <v>1.224138772146402</v>
+        <v>1.5282</v>
       </c>
       <c r="J13" t="n">
-        <v>20.81035912648884</v>
+        <v>25.9794</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.087422119972976</v>
+        <v>1.3212</v>
       </c>
       <c r="J14" t="n">
-        <v>18.4861760395406</v>
+        <v>22.4604</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>1.19</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3538621137985177</v>
+        <v>0.3767</v>
       </c>
       <c r="J15" t="n">
-        <v>6.0156559345748</v>
+        <v>6.4039</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1144969533645434</v>
+        <v>-0.1929</v>
       </c>
       <c r="J16" t="n">
-        <v>1.946448207197238</v>
+        <v>-3.2793</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4507415124718369</v>
+        <v>0.8804</v>
       </c>
       <c r="J17" t="n">
-        <v>7.662605712021228</v>
+        <v>14.9668</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.053145376856096</v>
+        <v>-0.355</v>
       </c>
       <c r="J18" t="n">
-        <v>-17.90347140655363</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.627184835785189</v>
+        <v>-0.6514</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.66214220834822</v>
+        <v>-11.0738</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.45</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.80998014250803</v>
+        <v>-0.7701</v>
       </c>
       <c r="J20" t="n">
-        <v>-30.76966242263651</v>
+        <v>-13.0917</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.225655797551458</v>
+        <v>-1.0795</v>
       </c>
       <c r="J21" t="n">
-        <v>-37.83614855837479</v>
+        <v>-18.3515</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.56</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8946552093835616</v>
+        <v>1.3891</v>
       </c>
       <c r="J22" t="n">
-        <v>31.31293232842465</v>
+        <v>48.6185</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3303219473939553</v>
+        <v>0.4399</v>
       </c>
       <c r="J23" t="n">
-        <v>11.56126815878843</v>
+        <v>15.3965</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.07325101060573215</v>
+        <v>-0.1844</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.563785371200625</v>
+        <v>-6.454</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1407300897982096</v>
+        <v>-0.2584</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.925553142937336</v>
+        <v>-9.044</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3114732271484732</v>
+        <v>-0.4994</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.90156295019656</v>
+        <v>-17.479</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3560320809536916</v>
+        <v>0.5174</v>
       </c>
       <c r="J27" t="n">
-        <v>12.46112283337921</v>
+        <v>18.109</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0696305636229322</v>
+        <v>0.1279</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.437069726802627</v>
+        <v>4.4765</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.429619382657861</v>
+        <v>-0.1623</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.03667839302514</v>
+        <v>-5.6805</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4558586970441303</v>
+        <v>-0.1814</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.95505439654456</v>
+        <v>-6.349</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9241147420803909</v>
+        <v>-0.5536</v>
       </c>
       <c r="J31" t="n">
-        <v>-32.34401597281368</v>
+        <v>-19.376</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2689561528711077</v>
+        <v>0.309</v>
       </c>
       <c r="J32" t="n">
-        <v>6.454947668906586</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1551752371511879</v>
+        <v>0.2105</v>
       </c>
       <c r="J33" t="n">
-        <v>3.72420569162851</v>
+        <v>5.052</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2290119138617311</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.496285932681547</v>
+        <v>-2.2152</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3275800750396881</v>
+        <v>-0.1743</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.861921800952514</v>
+        <v>-4.1832</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4677399667642064</v>
+        <v>-0.2934</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.22575920234095</v>
+        <v>-7.0416</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3901087668350723</v>
+        <v>0.3718</v>
       </c>
       <c r="J37" t="n">
-        <v>9.362610404041735</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1863015279299962</v>
+        <v>0.1593</v>
       </c>
       <c r="J38" t="n">
-        <v>4.471236670319907</v>
+        <v>3.8232</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1654405205474337</v>
+        <v>0.1395</v>
       </c>
       <c r="J39" t="n">
-        <v>3.97057249313841</v>
+        <v>3.348</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02368155063445299</v>
+        <v>0.0139</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5683572152268717</v>
+        <v>0.3336</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4517722691477481</v>
+        <v>-0.3476</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.84253445954595</v>
+        <v>-8.3424</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.67</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9498717250373581</v>
+        <v>1.6015</v>
       </c>
       <c r="J42" t="n">
-        <v>21.84704967585924</v>
+        <v>36.8345</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5977367100366056</v>
+        <v>0.9624</v>
       </c>
       <c r="J43" t="n">
-        <v>13.74794433084193</v>
+        <v>22.1352</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1719805899596694</v>
+        <v>-0.0177</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.955553569072397</v>
+        <v>-0.4071</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1719805899596694</v>
+        <v>-0.0177</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.955553569072397</v>
+        <v>-0.4071</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.44</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9280618353702986</v>
+        <v>-1.4616</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.34542221351687</v>
+        <v>-33.6168</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4853340302534433</v>
+        <v>0.7179</v>
       </c>
       <c r="J47" t="n">
-        <v>11.1626826958292</v>
+        <v>16.5117</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3962284876204488</v>
+        <v>0.6113</v>
       </c>
       <c r="J48" t="n">
-        <v>9.113255215270323</v>
+        <v>14.0599</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5547721201255008</v>
+        <v>-0.1496</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.75975876288652</v>
+        <v>-3.4408</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6168263035548159</v>
+        <v>-0.2054</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.18700498176077</v>
+        <v>-4.7242</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9085715953372224</v>
+        <v>-0.4596</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.89714669275612</v>
+        <v>-10.5708</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6829958738446421</v>
+        <v>1.8066</v>
       </c>
       <c r="J52" t="n">
-        <v>16.39190097227141</v>
+        <v>43.3584</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4251168271587681</v>
+        <v>1.0606</v>
       </c>
       <c r="J53" t="n">
-        <v>10.20280385181043</v>
+        <v>25.4544</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2924649125461076</v>
+        <v>-0.2791</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.019157901106581</v>
+        <v>-6.6984</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5737758391923863</v>
+        <v>-0.5164</v>
       </c>
       <c r="J55" t="n">
-        <v>-13.77062014061727</v>
+        <v>-12.3936</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.022264603277712</v>
+        <v>-0.989</v>
       </c>
       <c r="J56" t="n">
-        <v>-24.53435047866508</v>
+        <v>-23.736</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4515821226654744</v>
+        <v>0.5867</v>
       </c>
       <c r="J57" t="n">
-        <v>10.83797094397138</v>
+        <v>14.0808</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1517442854930206</v>
+        <v>0.0281</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.641862851832494</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2662218720410645</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.389324928985548</v>
+        <v>-2.0184</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7320284727535881</v>
+        <v>-0.4578</v>
       </c>
       <c r="J60" t="n">
-        <v>-17.56868334608611</v>
+        <v>-10.9872</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7320284727535881</v>
+        <v>-0.4578</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.56868334608611</v>
+        <v>-10.9872</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3726835454449796</v>
+        <v>0.6892</v>
       </c>
       <c r="J62" t="n">
-        <v>7.826354454344572</v>
+        <v>14.4732</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3155649926479554</v>
+        <v>0.5589</v>
       </c>
       <c r="J63" t="n">
-        <v>6.626864845607064</v>
+        <v>11.7369</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.265790806129</v>
+        <v>0.4656</v>
       </c>
       <c r="J64" t="n">
-        <v>5.581606928709</v>
+        <v>9.7776</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.265790806129</v>
+        <v>0.4656</v>
       </c>
       <c r="J65" t="n">
-        <v>5.581606928709</v>
+        <v>9.7776</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1240644539257471</v>
+        <v>0.1293</v>
       </c>
       <c r="J66" t="n">
-        <v>2.605353532440688</v>
+        <v>2.7153</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.007375988174366335</v>
+        <v>0.2086</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.154895751661693</v>
+        <v>4.3806</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2114608806872725</v>
+        <v>-0.0567</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.440678494432722</v>
+        <v>-1.1907</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5617701843856382</v>
+        <v>-0.3206</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.7971738720984</v>
+        <v>-6.7326</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8157415281534653</v>
+        <v>-0.5188</v>
       </c>
       <c r="J70" t="n">
-        <v>-17.13057209122277</v>
+        <v>-10.8948</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8627471959995887</v>
+        <v>-0.5597</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.11769111599136</v>
+        <v>-11.7537</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3386482453198451</v>
+        <v>1.2091</v>
       </c>
       <c r="J72" t="n">
-        <v>6.772964906396902</v>
+        <v>24.182</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3169370423304896</v>
+        <v>1.1069</v>
       </c>
       <c r="J73" t="n">
-        <v>6.338740846609793</v>
+        <v>22.138</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1505601299469737</v>
+        <v>0.4763</v>
       </c>
       <c r="J74" t="n">
-        <v>3.011202598939474</v>
+        <v>9.526</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.99</v>
       </c>
       <c r="I75" t="n">
-        <v>0.014896175189175</v>
+        <v>-0.1766</v>
       </c>
       <c r="J75" t="n">
-        <v>0.2979235037835</v>
+        <v>-3.532</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2956273219648866</v>
+        <v>-0.6539</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.912546439297732</v>
+        <v>-13.078</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3737657701884468</v>
+        <v>0.7866</v>
       </c>
       <c r="J77" t="n">
-        <v>7.475315403768937</v>
+        <v>15.732</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1348579210372366</v>
+        <v>0.0512</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.697158420744732</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.7</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4937367414867227</v>
+        <v>-0.5002</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.874734829734454</v>
+        <v>-10.004</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4937367414867227</v>
+        <v>-0.5002</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.874734829734454</v>
+        <v>-10.004</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.63</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5479408292154196</v>
+        <v>-0.5923</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.95881658430839</v>
+        <v>-11.846</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>2.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5854926077530564</v>
+        <v>2.0593</v>
       </c>
       <c r="J82" t="n">
-        <v>9.367881724048903</v>
+        <v>32.9488</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>0.256241697382051</v>
+        <v>0.9746</v>
       </c>
       <c r="J83" t="n">
-        <v>4.099867158112816</v>
+        <v>15.5936</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1660912224367993</v>
+        <v>0.6081</v>
       </c>
       <c r="J84" t="n">
-        <v>2.657459558988789</v>
+        <v>9.7296</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1525422803307159</v>
+        <v>0.5421</v>
       </c>
       <c r="J85" t="n">
-        <v>2.440676485291454</v>
+        <v>8.6736</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1437129873357927</v>
+        <v>0.4974</v>
       </c>
       <c r="J86" t="n">
-        <v>2.299407797372683</v>
+        <v>7.9584</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2505785891696326</v>
+        <v>-0.0371</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.009257426714122</v>
+        <v>-0.5936</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.84</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.304461005829086</v>
+        <v>-0.1546</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.871376093265376</v>
+        <v>-2.4736</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4921295692647625</v>
+        <v>-0.4532</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.874073108236201</v>
+        <v>-7.2512</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6897069296454725</v>
+        <v>-0.7531</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.03531087432756</v>
+        <v>-12.0496</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.43</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7108340310100454</v>
+        <v>-0.7917</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.37334449616073</v>
+        <v>-12.6672</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>2.28</v>
       </c>
       <c r="I92" t="n">
-        <v>1.108615702954577</v>
+        <v>2.0593</v>
       </c>
       <c r="J92" t="n">
-        <v>17.73785124727324</v>
+        <v>32.9488</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>2.03</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9786590668076034</v>
+        <v>1.9822</v>
       </c>
       <c r="J93" t="n">
-        <v>15.65854506892165</v>
+        <v>31.7152</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4098099357243156</v>
+        <v>0.8756</v>
       </c>
       <c r="J94" t="n">
-        <v>6.55695897158905</v>
+        <v>14.0096</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.09709475123350636</v>
+        <v>0.0176</v>
       </c>
       <c r="J95" t="n">
-        <v>1.553516019736102</v>
+        <v>0.2816</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.02574121475608981</v>
+        <v>-0.5491</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.411859436097437</v>
+        <v>-8.785600000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0302275891570515</v>
+        <v>0.7315</v>
       </c>
       <c r="J97" t="n">
-        <v>0.4836414265128239</v>
+        <v>11.704</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.803170224960294</v>
+        <v>-0.4541</v>
       </c>
       <c r="J98" t="n">
-        <v>-12.8507235993647</v>
+        <v>-7.2656</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9158589609760356</v>
+        <v>-0.5626</v>
       </c>
       <c r="J99" t="n">
-        <v>-14.65374337561657</v>
+        <v>-9.0016</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.43</v>
       </c>
       <c r="I100" t="n">
-        <v>-1.123646223948906</v>
+        <v>-0.8012</v>
       </c>
       <c r="J100" t="n">
-        <v>-17.97833958318249</v>
+        <v>-12.8192</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.42</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.133477986861979</v>
+        <v>-0.8136</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.13564778979167</v>
+        <v>-13.0176</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5926450952791199</v>
+        <v>1.2375</v>
       </c>
       <c r="J102" t="n">
-        <v>12.44554700086152</v>
+        <v>25.9875</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.45</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5194604587097024</v>
+        <v>1.0745</v>
       </c>
       <c r="J103" t="n">
-        <v>10.90866963290375</v>
+        <v>22.5645</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1970407743626067</v>
+        <v>0.5104</v>
       </c>
       <c r="J104" t="n">
-        <v>4.137856261614741</v>
+        <v>10.7184</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1125332261912524</v>
+        <v>0.332</v>
       </c>
       <c r="J105" t="n">
-        <v>2.363197750016302</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.06703926531301721</v>
+        <v>0.2252</v>
       </c>
       <c r="J106" t="n">
-        <v>1.407824571573361</v>
+        <v>4.7292</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.55</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2466846157194853</v>
+        <v>0.8468</v>
       </c>
       <c r="J107" t="n">
-        <v>5.18037693010919</v>
+        <v>17.7828</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.02791100221100425</v>
+        <v>0.4241</v>
       </c>
       <c r="J108" t="n">
-        <v>0.5861310464310892</v>
+        <v>8.9061</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.6537441644337</v>
+        <v>-0.3641</v>
       </c>
       <c r="J109" t="n">
-        <v>-13.7286274531077</v>
+        <v>-7.6461</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.8270936454595597</v>
+        <v>-0.5581</v>
       </c>
       <c r="J110" t="n">
-        <v>-17.36896655465075</v>
+        <v>-11.7201</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.41</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.06520041393376</v>
+        <v>-0.8579</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.36920869260896</v>
+        <v>-18.0159</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3881087288959204</v>
+        <v>1.5382</v>
       </c>
       <c r="J112" t="n">
-        <v>9.314609493502088</v>
+        <v>36.9168</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>0.293760561653327</v>
+        <v>1.1067</v>
       </c>
       <c r="J113" t="n">
-        <v>7.050253479679848</v>
+        <v>26.5608</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.08138174091945598</v>
+        <v>-0.1016</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.953161782066943</v>
+        <v>-2.4384</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.08138174091945598</v>
+        <v>-0.1016</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.953161782066943</v>
+        <v>-2.4384</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6295553142528303</v>
+        <v>-1.0511</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.10932754206793</v>
+        <v>-25.2264</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1056619876839789</v>
+        <v>0.3832</v>
       </c>
       <c r="J117" t="n">
-        <v>2.535887704415493</v>
+        <v>9.1968</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.008683535536094578</v>
+        <v>0.1718</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.2084048528662699</v>
+        <v>4.1232</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2170104827622167</v>
+        <v>-0.062</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.2082515862932</v>
+        <v>-1.488</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.91</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3891323522742287</v>
+        <v>-0.1957</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.339176454581489</v>
+        <v>-4.6968</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7650939952901111</v>
+        <v>-0.5518</v>
       </c>
       <c r="J121" t="n">
-        <v>-18.36225588696267</v>
+        <v>-13.2432</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2196466825905055</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>5.271520382172131</v>
+        <v>19.8504</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1115995167970512</v>
+        <v>0.4459</v>
       </c>
       <c r="J123" t="n">
-        <v>2.678388403129229</v>
+        <v>10.7016</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1023690813923375</v>
+        <v>0.4169</v>
       </c>
       <c r="J124" t="n">
-        <v>2.4568579534161</v>
+        <v>10.0056</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2907888456115338</v>
+        <v>-0.395</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.978932294676812</v>
+        <v>-9.48</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3966839495811872</v>
+        <v>-0.5876</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.520414789948493</v>
+        <v>-14.1024</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.85</v>
       </c>
       <c r="I127" t="n">
-        <v>0.371675916983976</v>
+        <v>1.1149</v>
       </c>
       <c r="J127" t="n">
-        <v>8.920222007615422</v>
+        <v>26.7576</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3409321261751692</v>
+        <v>-0.1177</v>
       </c>
       <c r="J128" t="n">
-        <v>-8.182371028204061</v>
+        <v>-2.8248</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.5412188275551911</v>
+        <v>-0.3102</v>
       </c>
       <c r="J129" t="n">
-        <v>-12.98925186132459</v>
+        <v>-7.4448</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5726053690645703</v>
+        <v>-0.3403</v>
       </c>
       <c r="J130" t="n">
-        <v>-13.74252885754969</v>
+        <v>-8.167199999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6028600536513038</v>
+        <v>-0.3695</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.46864128763129</v>
+        <v>-8.868</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2280462809346954</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.648740494955126</v>
+        <v>1.0048</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2960573299865164</v>
+        <v>-0.1037</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.736917279784262</v>
+        <v>-1.6592</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5261791225955381</v>
+        <v>-0.4632</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.41886596152861</v>
+        <v>-7.4112</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.696530847658612</v>
+        <v>-0.7352</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.14449356253779</v>
+        <v>-11.7632</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7173353641159261</v>
+        <v>-0.7735</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.47736582585482</v>
+        <v>-12.376</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>2.67</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9324432520571372</v>
+        <v>2.0593</v>
       </c>
       <c r="J137" t="n">
-        <v>14.91909203291419</v>
+        <v>32.9488</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.82</v>
       </c>
       <c r="I138" t="n">
-        <v>0.619738282481713</v>
+        <v>1.6709</v>
       </c>
       <c r="J138" t="n">
-        <v>9.915812519707409</v>
+        <v>26.7344</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1311759152415419</v>
+        <v>0.2811</v>
       </c>
       <c r="J139" t="n">
-        <v>2.09881464386467</v>
+        <v>4.4976</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.113994289125114</v>
+        <v>0.207</v>
       </c>
       <c r="J140" t="n">
-        <v>1.823908626001824</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.008207451917549059</v>
+        <v>-0.4952</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.1313192306807849</v>
+        <v>-7.9232</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.68</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6856889910685142</v>
+        <v>0.9136</v>
       </c>
       <c r="J142" t="n">
-        <v>16.45653578564434</v>
+        <v>21.9264</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3505822340178906</v>
+        <v>0.4433</v>
       </c>
       <c r="J143" t="n">
-        <v>8.413973616429375</v>
+        <v>10.6392</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.09364367654653306</v>
+        <v>0.185</v>
       </c>
       <c r="J144" t="n">
-        <v>2.247448237116794</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2263238169062236</v>
+        <v>-0.2812</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.431771605749367</v>
+        <v>-6.7488</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.309214507628425</v>
+        <v>-0.4127</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.421148183082201</v>
+        <v>-9.9048</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3945849725306878</v>
+        <v>0.8469</v>
       </c>
       <c r="J147" t="n">
-        <v>9.470039340736507</v>
+        <v>20.3256</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2114816564925109</v>
+        <v>0.498</v>
       </c>
       <c r="J148" t="n">
-        <v>5.075559755820262</v>
+        <v>11.952</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.335395310337191</v>
+        <v>-0.241</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.049487448092584</v>
+        <v>-5.784</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6222328046366997</v>
+        <v>-0.6441</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.93358731128079</v>
+        <v>-15.4584</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6222328046366997</v>
+        <v>-0.6441</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.93358731128079</v>
+        <v>-15.4584</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>0.8</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.3126764709549912</v>
+        <v>-0.163</v>
       </c>
       <c r="J152" t="n">
-        <v>-4.690147064324868</v>
+        <v>-2.445</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>0.78</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3272257782549641</v>
+        <v>-0.1942</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.908386673824462</v>
+        <v>-2.913</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4060334217988228</v>
+        <v>-0.3479</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.090501326982343</v>
+        <v>-5.2185</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.28</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7878710387824133</v>
+        <v>-0.9578</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.8180655817362</v>
+        <v>-14.367</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.26</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8002331830069427</v>
+        <v>-0.9826</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.00349774510414</v>
+        <v>-14.739</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>2.17</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7969687832511609</v>
+        <v>2.0593</v>
       </c>
       <c r="J157" t="n">
-        <v>11.95453174876741</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>2.01</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7324882976825278</v>
+        <v>1.9551</v>
       </c>
       <c r="J158" t="n">
-        <v>10.98732446523792</v>
+        <v>29.3265</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3762830553091567</v>
+        <v>1.0094</v>
       </c>
       <c r="J159" t="n">
-        <v>5.644245829637351</v>
+        <v>15.141</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1281827838867877</v>
+        <v>0.0964</v>
       </c>
       <c r="J160" t="n">
-        <v>1.922741758301816</v>
+        <v>1.446</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>1.08</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1229687127050813</v>
+        <v>0.0689</v>
       </c>
       <c r="J161" t="n">
-        <v>1.844530690576219</v>
+        <v>1.0335</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3807444816549845</v>
+        <v>1.2413</v>
       </c>
       <c r="J162" t="n">
-        <v>7.234145151444705</v>
+        <v>23.5847</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3709935480243453</v>
+        <v>1.2014</v>
       </c>
       <c r="J163" t="n">
-        <v>7.04887741246256</v>
+        <v>22.8266</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2379804952631109</v>
+        <v>0.7361</v>
       </c>
       <c r="J164" t="n">
-        <v>4.521629409999107</v>
+        <v>13.9859</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.05398250588636514</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>1.025667611840938</v>
+        <v>1.5884</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.02957746572232718</v>
+        <v>-0.0519</v>
       </c>
       <c r="J166" t="n">
-        <v>0.5619718487242163</v>
+        <v>-0.9861</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1775423958700225</v>
+        <v>0.6349</v>
       </c>
       <c r="J167" t="n">
-        <v>3.373305521530428</v>
+        <v>12.0631</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1867406773140931</v>
+        <v>0.0697</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.548072868967768</v>
+        <v>1.3243</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4247069114065353</v>
+        <v>-0.2728</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.06943131672417</v>
+        <v>-5.1832</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6721611523097302</v>
+        <v>-0.6088</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.77106189388487</v>
+        <v>-11.5672</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7579515643908016</v>
+        <v>-0.745</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.40107972342523</v>
+        <v>-14.155</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.16</v>
       </c>
       <c r="I172" t="n">
-        <v>0.01494247037590304</v>
+        <v>0.3848</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2839069371421578</v>
+        <v>7.3112</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1352740188293731</v>
+        <v>0.1134</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.57020635775809</v>
+        <v>2.1546</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2811022361759703</v>
+        <v>-0.1755</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.340942487343436</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5425622629431445</v>
+        <v>-0.5102</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.30868299591974</v>
+        <v>-9.6938</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7115448030687493</v>
+        <v>-0.7892</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.51935125830624</v>
+        <v>-14.9948</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7004161122292778</v>
+        <v>1.4689</v>
       </c>
       <c r="J177" t="n">
-        <v>13.30790613235628</v>
+        <v>27.9091</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5556924073713155</v>
+        <v>1.0747</v>
       </c>
       <c r="J178" t="n">
-        <v>10.55815574005499</v>
+        <v>20.4193</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2061377760025273</v>
+        <v>0.3507</v>
       </c>
       <c r="J179" t="n">
-        <v>3.916617744048019</v>
+        <v>6.6633</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1953847949908752</v>
+        <v>0.3239</v>
       </c>
       <c r="J180" t="n">
-        <v>3.71231110482663</v>
+        <v>6.1541</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.06539407348147305</v>
+        <v>-0.5438</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.242487396147988</v>
+        <v>-10.3322</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.34</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2055966860261265</v>
+        <v>0.5616</v>
       </c>
       <c r="J182" t="n">
-        <v>6.167900580783796</v>
+        <v>16.848</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.04361789641809714</v>
+        <v>0.1415</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.308536892542914</v>
+        <v>4.245</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.07077686666106825</v>
+        <v>0.1207</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.123305999832048</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3108191582276127</v>
+        <v>-0.1263</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.324574746828382</v>
+        <v>-3.789</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6379412599105975</v>
+        <v>-0.473</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.13823779731792</v>
+        <v>-14.19</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2855131211430241</v>
+        <v>0.6128</v>
       </c>
       <c r="J187" t="n">
-        <v>8.565393634290723</v>
+        <v>18.384</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1854112466883078</v>
+        <v>0.4213</v>
       </c>
       <c r="J188" t="n">
-        <v>5.562337400649234</v>
+        <v>12.639</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1683520866472218</v>
+        <v>0.3911</v>
       </c>
       <c r="J189" t="n">
-        <v>5.050562599416653</v>
+        <v>11.733</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1295345041860677</v>
+        <v>0.3264</v>
       </c>
       <c r="J190" t="n">
-        <v>3.886035125582032</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2030416951618159</v>
+        <v>-0.4385</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.091250854854478</v>
+        <v>-13.155</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.5</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4173670334704835</v>
+        <v>1.2232</v>
       </c>
       <c r="J192" t="n">
-        <v>10.0168088032916</v>
+        <v>29.3568</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>0.374777064171909</v>
+        <v>1.08</v>
       </c>
       <c r="J193" t="n">
-        <v>8.994649540125817</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.34</v>
       </c>
       <c r="I194" t="n">
-        <v>0.312608000061995</v>
+        <v>0.8851</v>
       </c>
       <c r="J194" t="n">
-        <v>7.50259200148788</v>
+        <v>21.2424</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1104873591095174</v>
+        <v>-0.3593</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.651696618628418</v>
+        <v>-8.623200000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3431652451198338</v>
+        <v>-0.7763</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.235965882876013</v>
+        <v>-18.6312</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2224667132981776</v>
+        <v>0.5036</v>
       </c>
       <c r="J197" t="n">
-        <v>5.339201119156263</v>
+        <v>12.0864</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.000482811464581942</v>
+        <v>0.1509</v>
       </c>
       <c r="J198" t="n">
-        <v>-0.01158747514996661</v>
+        <v>3.6216</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.282888365296513</v>
+        <v>-0.2739</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.789320767116312</v>
+        <v>-6.5736</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5438104885563677</v>
+        <v>-0.622</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.05145172535283</v>
+        <v>-14.928</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5522091634576003</v>
+        <v>-0.6347</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.25301992298241</v>
+        <v>-15.2328</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>0.97</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1181751789943663</v>
+        <v>0.0171</v>
       </c>
       <c r="J202" t="n">
-        <v>-2.481678758881692</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1990928312289376</v>
+        <v>-0.1341</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.180949455807689</v>
+        <v>-2.8161</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>0.88</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2099385155886454</v>
+        <v>-0.1515</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.408708827361554</v>
+        <v>-3.1815</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.74</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4127330260278533</v>
+        <v>-0.4049</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.66739354658492</v>
+        <v>-8.5029</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.47</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6486814082369282</v>
+        <v>-0.7693</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.62230957297549</v>
+        <v>-16.1553</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>0.485455492371248</v>
+        <v>1.8264</v>
       </c>
       <c r="J207" t="n">
-        <v>10.19456533979621</v>
+        <v>38.3544</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.36</v>
       </c>
       <c r="I208" t="n">
-        <v>0.265118151647973</v>
+        <v>0.8774</v>
       </c>
       <c r="J208" t="n">
-        <v>5.567481184607432</v>
+        <v>18.4254</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.3</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2161929616649086</v>
+        <v>0.7286</v>
       </c>
       <c r="J209" t="n">
-        <v>4.540052194963081</v>
+        <v>15.3006</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1013018959724731</v>
+        <v>0.358</v>
       </c>
       <c r="J210" t="n">
-        <v>2.127339815421935</v>
+        <v>7.518</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2996667894125454</v>
+        <v>-0.7735</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.293002577663453</v>
+        <v>-16.2435</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.64</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3599361013754804</v>
+        <v>1.4549</v>
       </c>
       <c r="J212" t="n">
-        <v>7.558658128885088</v>
+        <v>30.5529</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2334911798605643</v>
+        <v>0.9072</v>
       </c>
       <c r="J213" t="n">
-        <v>4.903314777071849</v>
+        <v>19.0512</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.27</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1502258360200605</v>
+        <v>0.6482</v>
       </c>
       <c r="J214" t="n">
-        <v>3.15474255642127</v>
+        <v>13.6122</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.06526756649839588</v>
+        <v>0.337</v>
       </c>
       <c r="J215" t="n">
-        <v>1.370618896466314</v>
+        <v>7.077</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.97</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1217491361414553</v>
+        <v>-0.286</v>
       </c>
       <c r="J216" t="n">
-        <v>-2.556731858970561</v>
+        <v>-6.006</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2805287598787631</v>
+        <v>0.6746</v>
       </c>
       <c r="J217" t="n">
-        <v>5.891103957454026</v>
+        <v>14.1666</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1720250988710708</v>
+        <v>0.0101</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.612527076292487</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2493609114959895</v>
+        <v>-0.125</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.23657914141578</v>
+        <v>-2.625</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2919854168953951</v>
+        <v>-0.1735</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.131693754803298</v>
+        <v>-3.6435</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7200148391375624</v>
+        <v>-0.9127</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.12031162188881</v>
+        <v>-19.1667</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>6.7479</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.236</v>
       </c>
       <c r="D2" t="n">
         <v>2.3046</v>
@@ -545,7 +545,7 @@
         <v>5.0135</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.9183</v>
       </c>
       <c r="D3" t="n">
         <v>1.604</v>
@@ -591,7 +591,7 @@
         <v>3.8752</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.7098</v>
       </c>
       <c r="D4" t="n">
         <v>1.1441</v>
@@ -637,7 +637,7 @@
         <v>3.4065</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.624</v>
       </c>
       <c r="D5" t="n">
         <v>0.9548</v>
@@ -683,7 +683,7 @@
         <v>3.2312</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.5919</v>
       </c>
       <c r="D6" t="n">
         <v>0.884</v>
@@ -729,7 +729,7 @@
         <v>2.9554</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.5414</v>
       </c>
       <c r="D7" t="n">
         <v>0.7726</v>
@@ -775,7 +775,7 @@
         <v>2.6465</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.4848</v>
       </c>
       <c r="D8" t="n">
         <v>0.6478</v>
@@ -821,7 +821,7 @@
         <v>2.5899</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.4744</v>
       </c>
       <c r="D9" t="n">
         <v>0.6249</v>
@@ -867,7 +867,7 @@
         <v>1.9611</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.3592</v>
       </c>
       <c r="D10" t="n">
         <v>0.3709</v>
@@ -913,7 +913,7 @@
         <v>1.8629</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.3412</v>
       </c>
       <c r="D11" t="n">
         <v>0.3312</v>
@@ -959,7 +959,7 @@
         <v>1.7453</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.3197</v>
       </c>
       <c r="D12" t="n">
         <v>0.2837</v>
@@ -1005,7 +1005,7 @@
         <v>1.7079</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.3128</v>
       </c>
       <c r="D13" t="n">
         <v>0.2686</v>
@@ -1051,7 +1051,7 @@
         <v>1.3998</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.2564</v>
       </c>
       <c r="D14" t="n">
         <v>0.1441</v>
@@ -1097,7 +1097,7 @@
         <v>1.3866</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="D15" t="n">
         <v>0.1388</v>
@@ -1143,7 +1143,7 @@
         <v>1.1865</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2173</v>
       </c>
       <c r="D16" t="n">
         <v>0.058</v>
@@ -1189,7 +1189,7 @@
         <v>1.184</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.2169</v>
       </c>
       <c r="D17" t="n">
         <v>0.0569</v>
@@ -1235,7 +1235,7 @@
         <v>1.1796</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.2161</v>
       </c>
       <c r="D18" t="n">
         <v>0.0552</v>
@@ -1281,7 +1281,7 @@
         <v>1.026</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1879</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0069</v>
@@ -1327,7 +1327,7 @@
         <v>0.9874000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1809</v>
       </c>
       <c r="D20" t="n">
         <v>-0.0225</v>
@@ -1373,7 +1373,7 @@
         <v>0.899</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1647</v>
       </c>
       <c r="D21" t="n">
         <v>-0.0582</v>
@@ -1419,7 +1419,7 @@
         <v>0.8818</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1615</v>
       </c>
       <c r="D22" t="n">
         <v>-0.06510000000000001</v>
@@ -1465,7 +1465,7 @@
         <v>0.7978</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.1461</v>
       </c>
       <c r="D23" t="n">
         <v>-0.09909999999999999</v>
@@ -1511,7 +1511,7 @@
         <v>0.4715</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.0864</v>
       </c>
       <c r="D24" t="n">
         <v>-0.2309</v>
@@ -1557,7 +1557,7 @@
         <v>0.3185</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0583</v>
       </c>
       <c r="D25" t="n">
         <v>-0.2927</v>
@@ -1603,7 +1603,7 @@
         <v>0.2419</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0443</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3236</v>
@@ -1649,7 +1649,7 @@
         <v>0.1508</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0276</v>
       </c>
       <c r="D27" t="n">
         <v>-0.3604</v>
@@ -1695,7 +1695,7 @@
         <v>-0.1378</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0252</v>
       </c>
       <c r="D28" t="n">
         <v>-0.477</v>
@@ -1741,7 +1741,7 @@
         <v>-0.1744</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0319</v>
       </c>
       <c r="D29" t="n">
         <v>-0.4918</v>
@@ -1787,7 +1787,7 @@
         <v>-0.3852</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.0706</v>
       </c>
       <c r="D30" t="n">
         <v>-0.577</v>
@@ -1833,7 +1833,7 @@
         <v>-0.3901</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="D31" t="n">
         <v>-0.579</v>
@@ -1879,7 +1879,7 @@
         <v>-0.3945</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.0723</v>
       </c>
       <c r="D32" t="n">
         <v>-0.5807</v>
@@ -1925,7 +1925,7 @@
         <v>-0.4475</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.082</v>
       </c>
       <c r="D33" t="n">
         <v>-0.6021</v>
@@ -1971,7 +1971,7 @@
         <v>-0.599</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.1097</v>
       </c>
       <c r="D34" t="n">
         <v>-0.6633</v>
@@ -2017,7 +2017,7 @@
         <v>-0.764</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.1399</v>
       </c>
       <c r="D35" t="n">
         <v>-0.73</v>
@@ -2063,7 +2063,7 @@
         <v>-1.0796</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.1978</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8575</v>
@@ -2109,7 +2109,7 @@
         <v>-1.1661</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.2136</v>
       </c>
       <c r="D37" t="n">
         <v>-0.8924</v>
@@ -2155,7 +2155,7 @@
         <v>-1.2739</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.2333</v>
       </c>
       <c r="D38" t="n">
         <v>-0.9360000000000001</v>
@@ -2201,7 +2201,7 @@
         <v>-1.6124</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.2954</v>
       </c>
       <c r="D39" t="n">
         <v>-1.0727</v>
@@ -2247,7 +2247,7 @@
         <v>-1.6313</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.2988</v>
       </c>
       <c r="D40" t="n">
         <v>-1.0804</v>
@@ -2293,7 +2293,7 @@
         <v>-1.9126</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.3503</v>
       </c>
       <c r="D41" t="n">
         <v>-1.194</v>

--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7479</v>
+        <v>7.5377</v>
       </c>
       <c r="C2" t="n">
-        <v>1.236</v>
+        <v>1.3807</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3046</v>
+        <v>2.5591</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7479</v>
+        <v>7.5377</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7093</v>
+        <v>3.4991</v>
       </c>
       <c r="G2" t="n">
         <v>4.0386</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7093</v>
+        <v>3.4991</v>
       </c>
       <c r="I2" t="n">
-        <v>2.196</v>
+        <v>2.8361</v>
       </c>
       <c r="J2" t="n">
         <v>4.0386</v>
@@ -529,7 +529,7 @@
         <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2346</v>
+        <v>6.8747</v>
       </c>
       <c r="N2" t="n">
         <v>120</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0135</v>
+        <v>5.4587</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9183</v>
+        <v>0.9999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.604</v>
+        <v>1.7308</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0135</v>
+        <v>5.4587</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8087</v>
+        <v>2.254</v>
       </c>
       <c r="G3" t="n">
         <v>3.2047</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8087</v>
+        <v>2.254</v>
       </c>
       <c r="I3" t="n">
-        <v>1.466</v>
+        <v>1.8269</v>
       </c>
       <c r="J3" t="n">
         <v>3.2047</v>
@@ -575,7 +575,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6707</v>
+        <v>5.0316</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -594,7 +594,7 @@
         <v>0.7098</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1441</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="n">
         <v>3.8752</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4065</v>
+        <v>3.4066</v>
       </c>
       <c r="C5" t="n">
         <v>0.624</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9548</v>
+        <v>0.9133</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4065</v>
+        <v>3.4066</v>
       </c>
       <c r="F5" t="n">
-        <v>3.921</v>
+        <v>3.9211</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5145</v>
       </c>
       <c r="H5" t="n">
-        <v>3.921</v>
+        <v>3.9211</v>
       </c>
       <c r="I5" t="n">
         <v>3.1781</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2312</v>
+        <v>3.2632</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5919</v>
+        <v>0.5977</v>
       </c>
       <c r="D6" t="n">
-        <v>0.884</v>
+        <v>0.8561</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2312</v>
+        <v>3.2632</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7219</v>
+        <v>1.6123</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4907</v>
+        <v>1.6509</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7219</v>
+        <v>1.6123</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0167</v>
+        <v>1.3068</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4907</v>
+        <v>1.6509</v>
       </c>
       <c r="K6" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="M6" t="n">
-        <v>2.526</v>
+        <v>2.9577</v>
       </c>
       <c r="N6" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9554</v>
+        <v>3.2312</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5414</v>
+        <v>0.5919</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7726</v>
+        <v>0.8434</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9554</v>
+        <v>3.2312</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3045</v>
+        <v>3.7219</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6509</v>
+        <v>-0.4907</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3045</v>
+        <v>3.7219</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0574</v>
+        <v>3.0167</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6509</v>
+        <v>-0.4907</v>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L7" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7083</v>
+        <v>2.526</v>
       </c>
       <c r="N7" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
@@ -778,7 +778,7 @@
         <v>0.4848</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6478</v>
+        <v>0.6105</v>
       </c>
       <c r="E8" t="n">
         <v>2.6465</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5899</v>
+        <v>2.5907</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4744</v>
+        <v>0.4746</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6249</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5899</v>
+        <v>2.5907</v>
       </c>
       <c r="F9" t="n">
-        <v>1.875</v>
+        <v>1.8758</v>
       </c>
       <c r="G9" t="n">
         <v>0.7149</v>
       </c>
       <c r="H9" t="n">
-        <v>1.875</v>
+        <v>1.8758</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5197</v>
+        <v>1.5204</v>
       </c>
       <c r="J9" t="n">
         <v>0.7149</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2346</v>
+        <v>2.2353</v>
       </c>
       <c r="N9" t="n">
         <v>158</v>
@@ -870,7 +870,7 @@
         <v>0.3592</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3709</v>
+        <v>0.3374</v>
       </c>
       <c r="E10" t="n">
         <v>1.9611</v>
@@ -916,7 +916,7 @@
         <v>0.3412</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3312</v>
+        <v>0.2983</v>
       </c>
       <c r="E11" t="n">
         <v>1.8629</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7453</v>
+        <v>1.8372</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3197</v>
+        <v>0.3365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2837</v>
+        <v>0.288</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7453</v>
+        <v>1.8372</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7453</v>
+        <v>2.0294</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.1922</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7453</v>
+        <v>2.0294</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7453</v>
+        <v>1.6449</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.1922</v>
       </c>
       <c r="K12" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7453</v>
+        <v>1.4527</v>
       </c>
       <c r="N12" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7079</v>
+        <v>1.8221</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3128</v>
+        <v>0.3338</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2686</v>
+        <v>0.282</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7079</v>
+        <v>1.8221</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2974</v>
+        <v>0.4116</v>
       </c>
       <c r="G13" t="n">
         <v>1.4105</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2974</v>
+        <v>0.4116</v>
       </c>
       <c r="I13" t="n">
-        <v>0.241</v>
+        <v>0.3336</v>
       </c>
       <c r="J13" t="n">
         <v>1.4105</v>
@@ -1035,7 +1035,7 @@
         <v>80</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6515</v>
+        <v>1.7441</v>
       </c>
       <c r="N13" t="n">
         <v>120</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3998</v>
+        <v>1.7453</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2564</v>
+        <v>0.3197</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1441</v>
+        <v>0.2514</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3998</v>
+        <v>1.7453</v>
       </c>
       <c r="F14" t="n">
-        <v>1.592</v>
+        <v>1.7453</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1922</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.592</v>
+        <v>1.7453</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2904</v>
+        <v>1.7453</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1922</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0982</v>
+        <v>1.7453</v>
       </c>
       <c r="N14" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
@@ -1100,7 +1100,7 @@
         <v>0.254</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1388</v>
+        <v>0.1085</v>
       </c>
       <c r="E15" t="n">
         <v>1.3866</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1865</v>
+        <v>1.2217</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2173</v>
+        <v>0.2238</v>
       </c>
       <c r="D16" t="n">
-        <v>0.058</v>
+        <v>0.0428</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1865</v>
+        <v>1.2217</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4297</v>
+        <v>0.4649</v>
       </c>
       <c r="G16" t="n">
         <v>0.7568</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4297</v>
+        <v>0.4649</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3483</v>
+        <v>0.3768</v>
       </c>
       <c r="J16" t="n">
         <v>0.7568</v>
@@ -1173,7 +1173,7 @@
         <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1051</v>
+        <v>1.1336</v>
       </c>
       <c r="N16" t="n">
         <v>160</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>deco</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.184</v>
+        <v>1.2106</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2169</v>
+        <v>0.2218</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0569</v>
+        <v>0.0384</v>
       </c>
       <c r="E17" t="n">
-        <v>1.184</v>
+        <v>1.2106</v>
       </c>
       <c r="F17" t="n">
-        <v>1.184</v>
+        <v>1.3316</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.121</v>
       </c>
       <c r="H17" t="n">
-        <v>1.184</v>
+        <v>1.3316</v>
       </c>
       <c r="I17" t="n">
-        <v>1.184</v>
+        <v>1.0793</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.121</v>
       </c>
       <c r="K17" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M17" t="n">
-        <v>1.184</v>
+        <v>0.9582999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>deco</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1796</v>
+        <v>1.184</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2161</v>
+        <v>0.2169</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0552</v>
+        <v>0.0278</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1796</v>
+        <v>1.184</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3006</v>
+        <v>1.184</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3006</v>
+        <v>1.184</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0542</v>
+        <v>1.184</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="L18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9332</v>
+        <v>1.184</v>
       </c>
       <c r="N18" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.026</v>
+        <v>1.106</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1879</v>
+        <v>0.2026</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0069</v>
+        <v>-0.0033</v>
       </c>
       <c r="E19" t="n">
-        <v>1.026</v>
+        <v>1.106</v>
       </c>
       <c r="F19" t="n">
-        <v>0.999</v>
+        <v>1.028</v>
       </c>
       <c r="G19" t="n">
-        <v>0.027</v>
+        <v>0.078</v>
       </c>
       <c r="H19" t="n">
-        <v>0.999</v>
+        <v>1.028</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8097</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.027</v>
+        <v>0.078</v>
       </c>
       <c r="K19" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8367</v>
+        <v>0.9112</v>
       </c>
       <c r="N19" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.026</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1809</v>
+        <v>0.1879</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0225</v>
+        <v>-0.0352</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.026</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9094</v>
+        <v>0.999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.078</v>
+        <v>0.027</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9094</v>
+        <v>0.999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7371</v>
+        <v>0.8097</v>
       </c>
       <c r="J20" t="n">
-        <v>0.078</v>
+        <v>0.027</v>
       </c>
       <c r="K20" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L20" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8150999999999999</v>
+        <v>0.8367</v>
       </c>
       <c r="N20" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21">
@@ -1376,7 +1376,7 @@
         <v>0.1647</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0582</v>
+        <v>-0.0857</v>
       </c>
       <c r="E21" t="n">
         <v>0.899</v>
@@ -1422,7 +1422,7 @@
         <v>0.1615</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0926</v>
       </c>
       <c r="E22" t="n">
         <v>0.8818</v>
@@ -1458,127 +1458,127 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7978</v>
+        <v>0.8639</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1461</v>
+        <v>0.1582</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.0997</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7978</v>
+        <v>0.8639</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7978</v>
+        <v>2.8639</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7978</v>
+        <v>2.8639</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7978</v>
+        <v>2.3213</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K23" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7978</v>
+        <v>0.3212999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4715</v>
+        <v>0.7978</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0864</v>
+        <v>0.1461</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2309</v>
+        <v>-0.1261</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4715</v>
+        <v>0.7978</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4715</v>
+        <v>0.7978</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4715</v>
+        <v>0.7978</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4715</v>
+        <v>0.7978</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4715</v>
+        <v>0.7978</v>
       </c>
       <c r="N24" t="n">
-        <v>122</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3185</v>
+        <v>0.5375</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0583</v>
+        <v>0.0985</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2927</v>
+        <v>-0.2298</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3185</v>
+        <v>0.5375</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3185</v>
+        <v>0.5245</v>
       </c>
       <c r="G25" t="n">
-        <v>-2</v>
+        <v>0.013</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3185</v>
+        <v>0.5245</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8792</v>
+        <v>0.4251</v>
       </c>
       <c r="J25" t="n">
-        <v>-2</v>
+        <v>0.013</v>
       </c>
       <c r="K25" t="n">
         <v>43</v>
@@ -1587,7 +1587,7 @@
         <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1208</v>
+        <v>0.4381</v>
       </c>
       <c r="N25" t="n">
         <v>160</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2419</v>
+        <v>0.4715</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0443</v>
+        <v>0.0864</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3236</v>
+        <v>-0.2561</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2419</v>
+        <v>0.4715</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2289</v>
+        <v>0.4715</v>
       </c>
       <c r="G26" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2289</v>
+        <v>0.4715</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1856</v>
+        <v>0.4715</v>
       </c>
       <c r="J26" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="L26" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1986</v>
+        <v>0.4715</v>
       </c>
       <c r="N26" t="n">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1508</v>
+        <v>0.2817</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0276</v>
+        <v>0.0516</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3604</v>
+        <v>-0.3317</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1508</v>
+        <v>0.2817</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1658</v>
+        <v>0.2967</v>
       </c>
       <c r="G27" t="n">
         <v>-0.015</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1658</v>
+        <v>0.2967</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1344</v>
+        <v>0.2405</v>
       </c>
       <c r="J27" t="n">
         <v>-0.015</v>
@@ -1679,7 +1679,7 @@
         <v>82</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1194</v>
+        <v>0.2255</v>
       </c>
       <c r="N27" t="n">
         <v>158</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0252</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.477</v>
+        <v>-0.4988</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1378</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0319</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4918</v>
+        <v>-0.5134</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1744</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0706</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.577</v>
+        <v>-0.5974</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3852</v>
@@ -1836,7 +1836,7 @@
         <v>-0.07149999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.579</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3901</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0723</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5807</v>
+        <v>-0.6011</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3945</v>
@@ -1928,7 +1928,7 @@
         <v>-0.082</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6021</v>
+        <v>-0.6222</v>
       </c>
       <c r="E33" t="n">
         <v>-0.4475</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1097</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6633</v>
+        <v>-0.6826</v>
       </c>
       <c r="E34" t="n">
         <v>-0.599</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.764</v>
+        <v>-0.7574</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1399</v>
+        <v>-0.1387</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.73</v>
+        <v>-0.7457</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.764</v>
+        <v>-0.7574</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.764</v>
+        <v>-0.7574</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.764</v>
+        <v>-0.7574</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.764</v>
+        <v>-0.7574</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.764</v>
+        <v>-0.7574</v>
       </c>
       <c r="N35" t="n">
         <v>105</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1978</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8575</v>
+        <v>-0.874</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0796</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2136</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8924</v>
+        <v>-0.9085</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1661</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2333</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9514</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2739</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2954</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0727</v>
+        <v>-1.0863</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6124</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2988</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0804</v>
+        <v>-1.0938</v>
       </c>
       <c r="E40" t="n">
         <v>-1.6313</v>
@@ -2296,7 +2296,7 @@
         <v>-0.3503</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.194</v>
+        <v>-1.2059</v>
       </c>
       <c r="E41" t="n">
         <v>-1.9126</v>

--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5377</v>
+        <v>6.4865</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3807</v>
+        <v>1.1882</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5591</v>
+        <v>2.2903</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5377</v>
+        <v>6.4865</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4991</v>
+        <v>2.9672</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0386</v>
+        <v>3.5193</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4991</v>
+        <v>4.9683</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8361</v>
+        <v>2.5833</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0386</v>
+        <v>3.5193</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -529,7 +529,7 @@
         <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8747</v>
+        <v>6.1026</v>
       </c>
       <c r="N2" t="n">
         <v>120</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4587</v>
+        <v>5.3945</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9999</v>
+        <v>0.9881</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7308</v>
+        <v>1.7973</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4587</v>
+        <v>5.3945</v>
       </c>
       <c r="F3" t="n">
-        <v>2.254</v>
+        <v>2.5108</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2047</v>
+        <v>2.8837</v>
       </c>
       <c r="H3" t="n">
-        <v>2.254</v>
+        <v>3.3601</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8269</v>
+        <v>1.7471</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2047</v>
+        <v>2.8837</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -575,7 +575,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0316</v>
+        <v>4.630800000000001</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8752</v>
+        <v>3.7489</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7098</v>
+        <v>0.6867</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>1.0544</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8752</v>
+        <v>3.7489</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4935</v>
+        <v>3.3017</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3817</v>
+        <v>0.4472</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4935</v>
+        <v>6.1469</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8316</v>
+        <v>3.1961</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3817</v>
+        <v>0.4472</v>
       </c>
       <c r="K4" t="n">
         <v>76</v>
@@ -621,7 +621,7 @@
         <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2133</v>
+        <v>3.6433</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
@@ -630,277 +630,277 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4066</v>
+        <v>3.5212</v>
       </c>
       <c r="C5" t="n">
-        <v>0.624</v>
+        <v>0.645</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9133</v>
+        <v>0.9516</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4066</v>
+        <v>3.5212</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9211</v>
+        <v>2.2699</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5145</v>
+        <v>1.2513</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9211</v>
+        <v>2.5116</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1781</v>
+        <v>1.3059</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5145</v>
+        <v>1.2513</v>
       </c>
       <c r="K5" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6636</v>
+        <v>2.5572</v>
       </c>
       <c r="N5" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2632</v>
+        <v>3.3243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5977</v>
+        <v>0.6089</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8561</v>
+        <v>0.8627</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2632</v>
+        <v>3.3243</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6123</v>
+        <v>2.6335</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6509</v>
+        <v>0.6908</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6123</v>
+        <v>3.7926</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3068</v>
+        <v>1.972</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6509</v>
+        <v>0.6908</v>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L6" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9577</v>
+        <v>2.6628</v>
       </c>
       <c r="N6" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2312</v>
+        <v>3.1243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5919</v>
+        <v>0.5723</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8434</v>
+        <v>0.7725</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2312</v>
+        <v>3.1243</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7219</v>
+        <v>3.1243</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4907</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7219</v>
+        <v>3.5006</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0167</v>
+        <v>3.5006</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4907</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.526</v>
+        <v>3.5006</v>
       </c>
       <c r="N7" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6465</v>
+        <v>3.0953</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4848</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6105</v>
+        <v>0.7594</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6465</v>
+        <v>3.0953</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6465</v>
+        <v>3.4301</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.3348</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6465</v>
+        <v>6.5992</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6465</v>
+        <v>3.4313</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.3348</v>
       </c>
       <c r="K8" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6465</v>
+        <v>3.0965</v>
       </c>
       <c r="N8" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5907</v>
+        <v>3.0302</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4746</v>
+        <v>0.5551</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5907</v>
+        <v>3.0302</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8758</v>
+        <v>3.3899</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7149</v>
+        <v>-0.3597</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8758</v>
+        <v>6.4575</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5204</v>
+        <v>3.3576</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7149</v>
+        <v>-0.3597</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L9" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2353</v>
+        <v>2.9979</v>
       </c>
       <c r="N9" t="n">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9611</v>
+        <v>2.946</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3592</v>
+        <v>0.5396</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3374</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9611</v>
+        <v>2.946</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5547</v>
+        <v>2.946</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5158</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5547</v>
+        <v>3.1091</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4496</v>
+        <v>3.1091</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5158</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="L10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0662</v>
+        <v>3.1091</v>
       </c>
       <c r="N10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8629</v>
+        <v>2.6904</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3412</v>
+        <v>0.4928</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2983</v>
+        <v>0.5766</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8629</v>
+        <v>2.6904</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1528</v>
+        <v>2.6869</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2899</v>
+        <v>0.0035</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1528</v>
+        <v>3.9805</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7449</v>
+        <v>2.0697</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2899</v>
+        <v>0.0035</v>
       </c>
       <c r="K11" t="n">
         <v>76</v>
@@ -943,7 +943,7 @@
         <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>1.455</v>
+        <v>2.0732</v>
       </c>
       <c r="N11" t="n">
         <v>158</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8372</v>
+        <v>2.4399</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3365</v>
+        <v>0.4469</v>
       </c>
       <c r="D12" t="n">
-        <v>0.288</v>
+        <v>0.4635</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8372</v>
+        <v>2.4399</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0294</v>
+        <v>2.4971</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1922</v>
+        <v>-0.0572</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0294</v>
+        <v>3.3118</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6449</v>
+        <v>1.722</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1922</v>
+        <v>-0.0572</v>
       </c>
       <c r="K12" t="n">
         <v>76</v>
@@ -989,7 +989,7 @@
         <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4527</v>
+        <v>1.6648</v>
       </c>
       <c r="N12" t="n">
         <v>158</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8221</v>
+        <v>2.3414</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3338</v>
+        <v>0.4289</v>
       </c>
       <c r="D13" t="n">
-        <v>0.282</v>
+        <v>0.419</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8221</v>
+        <v>2.3414</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4116</v>
+        <v>2.4371</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4105</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4116</v>
+        <v>3.1007</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3336</v>
+        <v>1.6122</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4105</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="L13" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7441</v>
+        <v>1.5165</v>
       </c>
       <c r="N13" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7453</v>
+        <v>2.277</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3197</v>
+        <v>0.4171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2514</v>
+        <v>0.3899</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7453</v>
+        <v>2.277</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7453</v>
+        <v>2.0944</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1826</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7453</v>
+        <v>2.0944</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7453</v>
+        <v>1.089</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.1826</v>
       </c>
       <c r="K14" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7453</v>
+        <v>1.2716</v>
       </c>
       <c r="N14" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3866</v>
+        <v>2.2487</v>
       </c>
       <c r="C15" t="n">
-        <v>0.254</v>
+        <v>0.4119</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1085</v>
+        <v>0.3772</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3866</v>
+        <v>2.2487</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6358</v>
+        <v>2.2121</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2492</v>
+        <v>0.0366</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6358</v>
+        <v>2.3079</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3259</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2492</v>
+        <v>0.0366</v>
       </c>
       <c r="K15" t="n">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="L15" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0767</v>
+        <v>1.2366</v>
       </c>
       <c r="N15" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2217</v>
+        <v>2.2341</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2238</v>
+        <v>0.4092</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0428</v>
+        <v>0.3706</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2217</v>
+        <v>2.2341</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4649</v>
+        <v>0.9476</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7568</v>
+        <v>1.2865</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4649</v>
+        <v>0.9476</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3768</v>
+        <v>0.4927</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7568</v>
+        <v>1.2865</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
@@ -1173,7 +1173,7 @@
         <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1336</v>
+        <v>1.7792</v>
       </c>
       <c r="N16" t="n">
         <v>160</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2106</v>
+        <v>2.1082</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2218</v>
+        <v>0.3862</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0384</v>
+        <v>0.3137</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2106</v>
+        <v>2.1082</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3316</v>
+        <v>0.831</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.121</v>
+        <v>1.2772</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3316</v>
+        <v>0.831</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0793</v>
+        <v>0.4321</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.121</v>
+        <v>1.2772</v>
       </c>
       <c r="K17" t="n">
         <v>40</v>
@@ -1219,7 +1219,7 @@
         <v>80</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9582999999999999</v>
+        <v>1.7093</v>
       </c>
       <c r="N17" t="n">
         <v>120</v>
@@ -1228,357 +1228,357 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>deco</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.184</v>
+        <v>1.8744</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2169</v>
+        <v>0.3433</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0278</v>
+        <v>0.2082</v>
       </c>
       <c r="E18" t="n">
-        <v>1.184</v>
+        <v>1.8744</v>
       </c>
       <c r="F18" t="n">
-        <v>1.184</v>
+        <v>1.7548</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.1196</v>
       </c>
       <c r="H18" t="n">
-        <v>1.184</v>
+        <v>1.7548</v>
       </c>
       <c r="I18" t="n">
-        <v>1.184</v>
+        <v>0.9124</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.1196</v>
       </c>
       <c r="K18" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M18" t="n">
-        <v>1.184</v>
+        <v>1.032</v>
       </c>
       <c r="N18" t="n">
-        <v>105</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.106</v>
+        <v>1.7503</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2026</v>
+        <v>0.3206</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0033</v>
+        <v>0.1522</v>
       </c>
       <c r="E19" t="n">
-        <v>1.106</v>
+        <v>1.7503</v>
       </c>
       <c r="F19" t="n">
-        <v>1.028</v>
+        <v>-0.6179</v>
       </c>
       <c r="G19" t="n">
-        <v>0.078</v>
+        <v>2.3682</v>
       </c>
       <c r="H19" t="n">
-        <v>1.028</v>
+        <v>-0.6179</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.3213</v>
       </c>
       <c r="J19" t="n">
-        <v>0.078</v>
+        <v>2.3682</v>
       </c>
       <c r="K19" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L19" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9112</v>
+        <v>2.0469</v>
       </c>
       <c r="N19" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.026</v>
+        <v>1.6897</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1879</v>
+        <v>0.3095</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0352</v>
+        <v>0.1248</v>
       </c>
       <c r="E20" t="n">
-        <v>1.026</v>
+        <v>1.6897</v>
       </c>
       <c r="F20" t="n">
-        <v>0.999</v>
+        <v>1.6897</v>
       </c>
       <c r="G20" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.999</v>
+        <v>1.6897</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8097</v>
+        <v>1.6897</v>
       </c>
       <c r="J20" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8367</v>
+        <v>1.6897</v>
       </c>
       <c r="N20" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>deco</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.899</v>
+        <v>1.4845</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1647</v>
+        <v>0.2719</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0857</v>
+        <v>0.0322</v>
       </c>
       <c r="E21" t="n">
-        <v>0.899</v>
+        <v>1.4845</v>
       </c>
       <c r="F21" t="n">
-        <v>0.899</v>
+        <v>1.4845</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.899</v>
+        <v>1.4845</v>
       </c>
       <c r="I21" t="n">
-        <v>0.899</v>
+        <v>1.4845</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.899</v>
+        <v>1.4845</v>
       </c>
       <c r="N21" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8818</v>
+        <v>1.2735</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1615</v>
+        <v>0.2333</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0926</v>
+        <v>-0.0631</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8818</v>
+        <v>1.2735</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8818</v>
+        <v>1.1886</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0849</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8818</v>
+        <v>1.1886</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8818</v>
+        <v>0.618</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.0849</v>
       </c>
       <c r="K22" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8818</v>
+        <v>0.7029</v>
       </c>
       <c r="N22" t="n">
-        <v>69</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8639</v>
+        <v>1.1734</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1582</v>
+        <v>0.2149</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0997</v>
+        <v>-0.1083</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8639</v>
+        <v>1.1734</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8639</v>
+        <v>1.1734</v>
       </c>
       <c r="G23" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8639</v>
+        <v>1.1734</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3213</v>
+        <v>1.1734</v>
       </c>
       <c r="J23" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="L23" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3212999999999999</v>
+        <v>1.1734</v>
       </c>
       <c r="N23" t="n">
-        <v>160</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7978</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1461</v>
+        <v>0.1578</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1261</v>
+        <v>-0.2491</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7978</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7978</v>
+        <v>0.788</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7978</v>
+        <v>0.788</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7978</v>
+        <v>0.4097</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7978</v>
+        <v>0.4831</v>
       </c>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5375</v>
+        <v>0.7643</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0985</v>
+        <v>0.14</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2298</v>
+        <v>-0.293</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5375</v>
+        <v>0.7643</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5245</v>
+        <v>2.7643</v>
       </c>
       <c r="G25" t="n">
-        <v>0.013</v>
+        <v>-2</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5245</v>
+        <v>4.2533</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4251</v>
+        <v>2.2115</v>
       </c>
       <c r="J25" t="n">
-        <v>0.013</v>
+        <v>-2</v>
       </c>
       <c r="K25" t="n">
         <v>43</v>
@@ -1587,7 +1587,7 @@
         <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4381</v>
+        <v>0.2115</v>
       </c>
       <c r="N25" t="n">
         <v>160</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4715</v>
+        <v>0.7416</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0864</v>
+        <v>0.1358</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2561</v>
+        <v>-0.3032</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4715</v>
+        <v>0.7416</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4715</v>
+        <v>0.7416</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4715</v>
+        <v>0.7416</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4715</v>
+        <v>0.7416</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4715</v>
+        <v>0.7416</v>
       </c>
       <c r="N26" t="n">
         <v>122</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2817</v>
+        <v>0.6952</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0516</v>
+        <v>0.1273</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3317</v>
+        <v>-0.3242</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2817</v>
+        <v>0.6952</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2967</v>
+        <v>0.6952</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2967</v>
+        <v>0.6952</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2405</v>
+        <v>0.6952</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L27" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2255</v>
+        <v>0.6952</v>
       </c>
       <c r="N27" t="n">
-        <v>158</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1378</v>
+        <v>0.0752</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0252</v>
+        <v>0.0138</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4988</v>
+        <v>-0.6041</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1378</v>
+        <v>0.0752</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1378</v>
+        <v>0.0752</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1378</v>
+        <v>0.0752</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1378</v>
+        <v>0.0752</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1378</v>
+        <v>0.0752</v>
       </c>
       <c r="N28" t="n">
         <v>69</v>
@@ -1734,216 +1734,216 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>aNdu</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1744</v>
+        <v>-0.0122</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0319</v>
+        <v>-0.0022</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5134</v>
+        <v>-0.6435</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1744</v>
+        <v>-0.0122</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1744</v>
+        <v>-0.0122</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1744</v>
+        <v>-0.0122</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1744</v>
+        <v>-0.0122</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1744</v>
+        <v>-0.0122</v>
       </c>
       <c r="N29" t="n">
-        <v>105</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>Noktse</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3852</v>
+        <v>-0.0517</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0706</v>
+        <v>-0.0095</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5974</v>
+        <v>-0.6614</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3852</v>
+        <v>-0.0517</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3852</v>
+        <v>-0.0517</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3852</v>
+        <v>-0.0517</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3852</v>
+        <v>-0.0517</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3852</v>
+        <v>-0.0517</v>
       </c>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Noktse</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3901</v>
+        <v>-0.18</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.033</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3901</v>
+        <v>-0.18</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3901</v>
+        <v>-0.18</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3901</v>
+        <v>-0.18</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3901</v>
+        <v>-0.18</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3901</v>
+        <v>-0.18</v>
       </c>
       <c r="N31" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aNdu</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3945</v>
+        <v>-0.1812</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0723</v>
+        <v>-0.0332</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6011</v>
+        <v>-0.7198</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3945</v>
+        <v>-0.1812</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3945</v>
+        <v>-0.1812</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3945</v>
+        <v>-0.1812</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3945</v>
+        <v>-0.1812</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3945</v>
+        <v>-0.1812</v>
       </c>
       <c r="N32" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4475</v>
+        <v>-0.2734</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.082</v>
+        <v>-0.0501</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6222</v>
+        <v>-0.7614</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4475</v>
+        <v>-0.2734</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4475</v>
+        <v>-0.2734</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4475</v>
+        <v>-0.2734</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4475</v>
+        <v>-0.2734</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4475</v>
+        <v>-0.2734</v>
       </c>
       <c r="N33" t="n">
         <v>69</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.599</v>
+        <v>-0.2861</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1097</v>
+        <v>-0.0524</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6826</v>
+        <v>-0.7672</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.599</v>
+        <v>-0.2861</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.599</v>
+        <v>-0.2861</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.599</v>
+        <v>-0.2861</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.599</v>
+        <v>-0.2861</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.599</v>
+        <v>-0.2861</v>
       </c>
       <c r="N34" t="n">
         <v>105</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>reversive</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7574</v>
+        <v>-0.2963</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1387</v>
+        <v>-0.0543</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7457</v>
+        <v>-0.7718</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7574</v>
+        <v>-0.2963</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7574</v>
+        <v>-0.2963</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7574</v>
+        <v>-0.2963</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7574</v>
+        <v>-0.2963</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7574</v>
+        <v>-0.2963</v>
       </c>
       <c r="N35" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>reversive</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0796</v>
+        <v>-0.5824</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1978</v>
+        <v>-0.1067</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.874</v>
+        <v>-0.9009</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0796</v>
+        <v>-0.5824</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0796</v>
+        <v>-0.5824</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0796</v>
+        <v>-0.5824</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0796</v>
+        <v>-0.5824</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0796</v>
+        <v>-0.5824</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2136</v>
+        <v>-0.1522</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9085</v>
+        <v>-1.0132</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2739</v>
+        <v>-1.0322</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2333</v>
+        <v>-0.1891</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9514</v>
+        <v>-1.104</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2739</v>
+        <v>-1.0322</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2739</v>
+        <v>-1.0322</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2739</v>
+        <v>-1.0322</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2739</v>
+        <v>-1.0322</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2739</v>
+        <v>-1.0322</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6124</v>
+        <v>-1.0688</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2954</v>
+        <v>-0.1958</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0863</v>
+        <v>-1.1205</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6124</v>
+        <v>-1.0688</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6124</v>
+        <v>-1.0688</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6124</v>
+        <v>-1.0688</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6124</v>
+        <v>-1.0688</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6124</v>
+        <v>-1.0688</v>
       </c>
       <c r="N39" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6313</v>
+        <v>-1.1824</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2988</v>
+        <v>-0.2166</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0938</v>
+        <v>-1.1718</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6313</v>
+        <v>-1.1824</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6313</v>
+        <v>-1.1824</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6313</v>
+        <v>-1.1824</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6313</v>
+        <v>-1.1824</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6313</v>
+        <v>-1.1824</v>
       </c>
       <c r="N40" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9126</v>
+        <v>-1.7425</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3503</v>
+        <v>-0.3192</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2059</v>
+        <v>-1.4247</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9126</v>
+        <v>-1.7425</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5079</v>
+        <v>-1.4653</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4047</v>
+        <v>-0.2772</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5079</v>
+        <v>-1.4653</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2222</v>
+        <v>-0.7619</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4047</v>
+        <v>-0.2772</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6269</v>
+        <v>-1.0391</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2429,10 +2429,10 @@
         <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3022</v>
+        <v>1.1984</v>
       </c>
       <c r="J2" t="n">
-        <v>23.4396</v>
+        <v>21.5712</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0384</v>
+        <v>1.0335</v>
       </c>
       <c r="J3" t="n">
-        <v>18.6912</v>
+        <v>18.603</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5942</v>
+        <v>0.6645</v>
       </c>
       <c r="J4" t="n">
-        <v>10.6956</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3891</v>
+        <v>0.471</v>
       </c>
       <c r="J5" t="n">
-        <v>7.0038</v>
+        <v>8.478</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2079</v>
+        <v>-0.1231</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.7422</v>
+        <v>-2.2158</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5678</v>
+        <v>0.6794</v>
       </c>
       <c r="J7" t="n">
-        <v>10.2204</v>
+        <v>12.2292</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.215</v>
+        <v>-0.153</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.87</v>
+        <v>-2.754</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2773</v>
+        <v>-0.183</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.9914</v>
+        <v>-3.294</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3903</v>
+        <v>-0.2524</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.0254</v>
+        <v>-4.5432</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6734</v>
+        <v>-0.451</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.1212</v>
+        <v>-8.118</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5465</v>
+        <v>1.3678</v>
       </c>
       <c r="J12" t="n">
-        <v>26.2905</v>
+        <v>23.2526</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.72</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5282</v>
+        <v>1.3562</v>
       </c>
       <c r="J13" t="n">
-        <v>25.9794</v>
+        <v>23.0554</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3212</v>
+        <v>1.228</v>
       </c>
       <c r="J14" t="n">
-        <v>22.4604</v>
+        <v>20.876</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.19</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3767</v>
+        <v>0.4846</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4039</v>
+        <v>8.238200000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1929</v>
+        <v>-0.1052</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.2793</v>
+        <v>-1.7884</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8804</v>
+        <v>1.1098</v>
       </c>
       <c r="J17" t="n">
-        <v>14.9668</v>
+        <v>18.8666</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.355</v>
+        <v>-0.2758</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.035</v>
+        <v>-4.6886</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6514</v>
+        <v>-0.4413</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.0738</v>
+        <v>-7.5021</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.45</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7701</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.0917</v>
+        <v>-8.9369</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0795</v>
+        <v>-0.7693</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.3515</v>
+        <v>-13.0781</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.56</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3891</v>
+        <v>0.973</v>
       </c>
       <c r="J22" t="n">
-        <v>48.6185</v>
+        <v>34.055</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4399</v>
+        <v>0.3897</v>
       </c>
       <c r="J23" t="n">
-        <v>15.3965</v>
+        <v>13.6395</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1844</v>
+        <v>-0.1198</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.454</v>
+        <v>-4.193</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2584</v>
+        <v>-0.1919</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.044</v>
+        <v>-6.7165</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4994</v>
+        <v>-0.4355</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.479</v>
+        <v>-15.2425</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5174</v>
+        <v>0.4975</v>
       </c>
       <c r="J27" t="n">
-        <v>18.109</v>
+        <v>17.4125</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1279</v>
+        <v>0.1224</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4765</v>
+        <v>4.284</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1623</v>
+        <v>-0.097</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.6805</v>
+        <v>-3.395</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1814</v>
+        <v>-0.1085</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.349</v>
+        <v>-3.7975</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5536</v>
+        <v>-0.3611</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.376</v>
+        <v>-12.6385</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.309</v>
+        <v>0.264</v>
       </c>
       <c r="J32" t="n">
-        <v>7.416</v>
+        <v>6.336</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2105</v>
+        <v>0.1728</v>
       </c>
       <c r="J33" t="n">
-        <v>5.052</v>
+        <v>4.1472</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.2152</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1743</v>
+        <v>-0.1</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.1832</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2934</v>
+        <v>-0.1775</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.0416</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3718</v>
+        <v>0.3049</v>
       </c>
       <c r="J37" t="n">
-        <v>8.9232</v>
+        <v>7.3176</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1593</v>
+        <v>0.1259</v>
       </c>
       <c r="J38" t="n">
-        <v>3.8232</v>
+        <v>3.0216</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1395</v>
+        <v>0.1106</v>
       </c>
       <c r="J39" t="n">
-        <v>3.348</v>
+        <v>2.6544</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0139</v>
+        <v>0.024</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3336</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3476</v>
+        <v>-0.2125</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.3424</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.67</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6015</v>
+        <v>1.1176</v>
       </c>
       <c r="J42" t="n">
-        <v>36.8345</v>
+        <v>25.7048</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9624</v>
+        <v>0.695</v>
       </c>
       <c r="J43" t="n">
-        <v>22.1352</v>
+        <v>15.985</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0177</v>
+        <v>0.0328</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.4071</v>
+        <v>0.7544</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0177</v>
+        <v>0.0328</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.4071</v>
+        <v>0.7544</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.44</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.4616</v>
+        <v>-1.5065</v>
       </c>
       <c r="J46" t="n">
-        <v>-33.6168</v>
+        <v>-34.6495</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7179</v>
+        <v>0.6619</v>
       </c>
       <c r="J47" t="n">
-        <v>16.5117</v>
+        <v>15.2237</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6113</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>14.0599</v>
+        <v>13.2733</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1496</v>
+        <v>-0.0743</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.4408</v>
+        <v>-1.7089</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2054</v>
+        <v>-0.1115</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.7242</v>
+        <v>-2.5645</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4596</v>
+        <v>-0.2902</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.5708</v>
+        <v>-6.6746</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.8066</v>
+        <v>1.3073</v>
       </c>
       <c r="J52" t="n">
-        <v>43.3584</v>
+        <v>31.3752</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0606</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>25.4544</v>
+        <v>18.2784</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2791</v>
+        <v>-0.2052</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.6984</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5164</v>
+        <v>-0.4488</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.3936</v>
+        <v>-10.7712</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.989</v>
+        <v>-0.9625</v>
       </c>
       <c r="J56" t="n">
-        <v>-23.736</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5867</v>
+        <v>0.5527</v>
       </c>
       <c r="J57" t="n">
-        <v>14.0808</v>
+        <v>13.2648</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0281</v>
+        <v>0.007</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6744</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0599</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.0184</v>
+        <v>-1.4376</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4578</v>
+        <v>-0.2928</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.9872</v>
+        <v>-7.0272</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4578</v>
+        <v>-0.2928</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.9872</v>
+        <v>-7.0272</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6892</v>
+        <v>0.5407</v>
       </c>
       <c r="J62" t="n">
-        <v>14.4732</v>
+        <v>11.3547</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5589</v>
+        <v>0.4701</v>
       </c>
       <c r="J63" t="n">
-        <v>11.7369</v>
+        <v>9.8721</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4656</v>
+        <v>0.4273</v>
       </c>
       <c r="J64" t="n">
-        <v>9.7776</v>
+        <v>8.9733</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4656</v>
+        <v>0.4273</v>
       </c>
       <c r="J65" t="n">
-        <v>9.7776</v>
+        <v>8.9733</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1293</v>
+        <v>0.1915</v>
       </c>
       <c r="J66" t="n">
-        <v>2.7153</v>
+        <v>4.0215</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2086</v>
+        <v>0.1971</v>
       </c>
       <c r="J67" t="n">
-        <v>4.3806</v>
+        <v>4.1391</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0567</v>
+        <v>-0.0669</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.1907</v>
+        <v>-1.4049</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3206</v>
+        <v>-0.2173</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.7326</v>
+        <v>-4.5633</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5188</v>
+        <v>-0.3418</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.8948</v>
+        <v>-7.1778</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5597</v>
+        <v>-0.3701</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.7537</v>
+        <v>-7.7721</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2091</v>
+        <v>1.1321</v>
       </c>
       <c r="J72" t="n">
-        <v>24.182</v>
+        <v>22.642</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1069</v>
+        <v>1.0672</v>
       </c>
       <c r="J73" t="n">
-        <v>22.138</v>
+        <v>21.344</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4763</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>9.526</v>
+        <v>10.292</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.99</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1766</v>
+        <v>-0.1</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.532</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6539</v>
+        <v>-0.5933</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.078</v>
+        <v>-11.866</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7866</v>
+        <v>0.9829</v>
       </c>
       <c r="J77" t="n">
-        <v>15.732</v>
+        <v>19.658</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0512</v>
+        <v>0.0196</v>
       </c>
       <c r="J78" t="n">
-        <v>1.024</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.7</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5002</v>
+        <v>-0.3247</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.004</v>
+        <v>-6.494</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5002</v>
+        <v>-0.3247</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.004</v>
+        <v>-6.494</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.63</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5923</v>
+        <v>-0.3906</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.846</v>
+        <v>-7.812</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.27</v>
       </c>
       <c r="I82" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J82" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9746</v>
+        <v>1.058</v>
       </c>
       <c r="J83" t="n">
-        <v>15.5936</v>
+        <v>16.928</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6081</v>
+        <v>0.7337</v>
       </c>
       <c r="J84" t="n">
-        <v>9.7296</v>
+        <v>11.7392</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5421</v>
+        <v>0.6647</v>
       </c>
       <c r="J85" t="n">
-        <v>8.6736</v>
+        <v>10.6352</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4974</v>
+        <v>0.6178</v>
       </c>
       <c r="J86" t="n">
-        <v>7.9584</v>
+        <v>9.8848</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0371</v>
+        <v>-0.0625</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.5936</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.84</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1546</v>
+        <v>-0.1461</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.4736</v>
+        <v>-2.3376</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4532</v>
+        <v>-0.3285</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.2512</v>
+        <v>-5.256</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7531</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.0496</v>
+        <v>-8.217599999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.43</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7917</v>
+        <v>-0.5419</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.6672</v>
+        <v>-8.670400000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2.28</v>
       </c>
       <c r="I92" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J92" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>2.03</v>
       </c>
       <c r="I93" t="n">
-        <v>1.9822</v>
+        <v>1.6874</v>
       </c>
       <c r="J93" t="n">
-        <v>31.7152</v>
+        <v>26.9984</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8756</v>
+        <v>0.999</v>
       </c>
       <c r="J94" t="n">
-        <v>14.0096</v>
+        <v>15.984</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0176</v>
+        <v>0.1096</v>
       </c>
       <c r="J95" t="n">
-        <v>0.2816</v>
+        <v>1.7536</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5491</v>
+        <v>-0.4742</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.785600000000001</v>
+        <v>-7.5872</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7315</v>
+        <v>0.9411</v>
       </c>
       <c r="J97" t="n">
-        <v>11.704</v>
+        <v>15.0576</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.4541</v>
+        <v>-0.3154</v>
       </c>
       <c r="J98" t="n">
-        <v>-7.2656</v>
+        <v>-5.0464</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.5626</v>
+        <v>-0.3802</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.0016</v>
+        <v>-6.0832</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.43</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.8012</v>
+        <v>-0.5485</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.8192</v>
+        <v>-8.776</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.42</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8136</v>
+        <v>-0.5578</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.0176</v>
+        <v>-8.924799999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2375</v>
+        <v>1.1589</v>
       </c>
       <c r="J102" t="n">
-        <v>25.9875</v>
+        <v>24.3369</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.45</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0745</v>
+        <v>1.0586</v>
       </c>
       <c r="J103" t="n">
-        <v>22.5645</v>
+        <v>22.2306</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5104</v>
+        <v>0.5917</v>
       </c>
       <c r="J104" t="n">
-        <v>10.7184</v>
+        <v>12.4257</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.332</v>
+        <v>0.4168</v>
       </c>
       <c r="J105" t="n">
-        <v>6.972</v>
+        <v>8.752800000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2252</v>
+        <v>0.309</v>
       </c>
       <c r="J106" t="n">
-        <v>4.7292</v>
+        <v>6.489</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.55</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8468</v>
+        <v>1.0451</v>
       </c>
       <c r="J107" t="n">
-        <v>17.7828</v>
+        <v>21.9471</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4241</v>
+        <v>0.4845</v>
       </c>
       <c r="J108" t="n">
-        <v>8.9061</v>
+        <v>10.1745</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3641</v>
+        <v>-0.2301</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.6461</v>
+        <v>-4.8321</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5581</v>
+        <v>-0.3653</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.7201</v>
+        <v>-7.6713</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.41</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8579</v>
+        <v>-0.5926</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.0159</v>
+        <v>-12.4446</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5382</v>
+        <v>1.3478</v>
       </c>
       <c r="J112" t="n">
-        <v>36.9168</v>
+        <v>32.3472</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>1.1067</v>
+        <v>1.0638</v>
       </c>
       <c r="J113" t="n">
-        <v>26.5608</v>
+        <v>25.5312</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1016</v>
+        <v>-0.0348</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.4384</v>
+        <v>-0.8352000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1016</v>
+        <v>-0.0348</v>
       </c>
       <c r="J115" t="n">
-        <v>-2.4384</v>
+        <v>-0.8352000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.0511</v>
+        <v>-1.0325</v>
       </c>
       <c r="J116" t="n">
-        <v>-25.2264</v>
+        <v>-24.78</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3832</v>
+        <v>0.4337</v>
       </c>
       <c r="J117" t="n">
-        <v>9.1968</v>
+        <v>10.4088</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1718</v>
+        <v>0.1713</v>
       </c>
       <c r="J118" t="n">
-        <v>4.1232</v>
+        <v>4.1112</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.488</v>
+        <v>-1.1328</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.91</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1957</v>
+        <v>-0.1188</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.6968</v>
+        <v>-2.8512</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5518</v>
+        <v>-0.36</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.2432</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.7973</v>
       </c>
       <c r="J122" t="n">
-        <v>19.8504</v>
+        <v>19.1352</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4459</v>
+        <v>0.4145</v>
       </c>
       <c r="J123" t="n">
-        <v>10.7016</v>
+        <v>9.948</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4169</v>
+        <v>0.3872</v>
       </c>
       <c r="J124" t="n">
-        <v>10.0056</v>
+        <v>9.2928</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.395</v>
+        <v>-0.3357</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.48</v>
+        <v>-8.056800000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5876</v>
+        <v>-0.5319</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.1024</v>
+        <v>-12.7656</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.85</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1149</v>
+        <v>1.2732</v>
       </c>
       <c r="J127" t="n">
-        <v>26.7576</v>
+        <v>30.5568</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1177</v>
+        <v>-0.0567</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.8248</v>
+        <v>-1.3608</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3102</v>
+        <v>-0.1851</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.4448</v>
+        <v>-4.4424</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3403</v>
+        <v>-0.206</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.167199999999999</v>
+        <v>-4.944</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3695</v>
+        <v>-0.2265</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.868</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="J132" t="n">
-        <v>1.0048</v>
+        <v>0.2544</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1037</v>
+        <v>-0.1088</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.6592</v>
+        <v>-1.7408</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4632</v>
+        <v>-0.323</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.4112</v>
+        <v>-5.168</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.7352</v>
+        <v>-0.4998</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.7632</v>
+        <v>-7.9968</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7735</v>
+        <v>-0.5279</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.376</v>
+        <v>-8.446400000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.67</v>
       </c>
       <c r="I137" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J137" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.82</v>
       </c>
       <c r="I138" t="n">
-        <v>1.6709</v>
+        <v>1.4546</v>
       </c>
       <c r="J138" t="n">
-        <v>26.7344</v>
+        <v>23.2736</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2811</v>
+        <v>0.3901</v>
       </c>
       <c r="J139" t="n">
-        <v>4.4976</v>
+        <v>6.2416</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.207</v>
+        <v>0.311</v>
       </c>
       <c r="J140" t="n">
-        <v>3.312</v>
+        <v>4.976</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4952</v>
+        <v>-0.4159</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.9232</v>
+        <v>-6.6544</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.68</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9136</v>
+        <v>0.8297</v>
       </c>
       <c r="J142" t="n">
-        <v>21.9264</v>
+        <v>19.9128</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4433</v>
+        <v>0.3825</v>
       </c>
       <c r="J143" t="n">
-        <v>10.6392</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.185</v>
+        <v>0.1849</v>
       </c>
       <c r="J144" t="n">
-        <v>4.44</v>
+        <v>4.4376</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2812</v>
+        <v>-0.1618</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.7488</v>
+        <v>-3.8832</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4127</v>
+        <v>-0.2555</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.9048</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8469</v>
+        <v>0.8213</v>
       </c>
       <c r="J147" t="n">
-        <v>20.3256</v>
+        <v>19.7112</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.498</v>
+        <v>0.449</v>
       </c>
       <c r="J148" t="n">
-        <v>11.952</v>
+        <v>10.776</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.241</v>
+        <v>-0.1439</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.784</v>
+        <v>-3.4536</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6441</v>
+        <v>-0.428</v>
       </c>
       <c r="J150" t="n">
-        <v>-15.4584</v>
+        <v>-10.272</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6441</v>
+        <v>-0.428</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.4584</v>
+        <v>-10.272</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.8</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.163</v>
+        <v>-0.1551</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.445</v>
+        <v>-2.3265</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.78</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1942</v>
+        <v>-0.1783</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.913</v>
+        <v>-2.6745</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3479</v>
+        <v>-0.2875</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.2185</v>
+        <v>-4.3125</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.28</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.9578</v>
+        <v>-0.6692</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.367</v>
+        <v>-10.038</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.26</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9826</v>
+        <v>-0.6889</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.739</v>
+        <v>-10.3335</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.17</v>
       </c>
       <c r="I157" t="n">
-        <v>2.0593</v>
+        <v>1.8328</v>
       </c>
       <c r="J157" t="n">
-        <v>30.8895</v>
+        <v>27.492</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>2.01</v>
       </c>
       <c r="I158" t="n">
-        <v>1.9551</v>
+        <v>1.6594</v>
       </c>
       <c r="J158" t="n">
-        <v>29.3265</v>
+        <v>24.891</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0094</v>
+        <v>1.0885</v>
       </c>
       <c r="J159" t="n">
-        <v>15.141</v>
+        <v>16.3275</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0964</v>
+        <v>0.1939</v>
       </c>
       <c r="J160" t="n">
-        <v>1.446</v>
+        <v>2.9085</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.08</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0689</v>
+        <v>0.1647</v>
       </c>
       <c r="J161" t="n">
-        <v>1.0335</v>
+        <v>2.4705</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2413</v>
+        <v>1.1605</v>
       </c>
       <c r="J162" t="n">
-        <v>23.5847</v>
+        <v>22.0495</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2014</v>
+        <v>1.1356</v>
       </c>
       <c r="J163" t="n">
-        <v>22.8266</v>
+        <v>21.5764</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7361</v>
+        <v>0.7749</v>
       </c>
       <c r="J164" t="n">
-        <v>13.9859</v>
+        <v>14.7231</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1639</v>
       </c>
       <c r="J165" t="n">
-        <v>1.5884</v>
+        <v>3.1141</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0519</v>
+        <v>0.0269</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.9861</v>
+        <v>0.5111</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6349</v>
+        <v>0.7749</v>
       </c>
       <c r="J167" t="n">
-        <v>12.0631</v>
+        <v>14.7231</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0697</v>
+        <v>0.0333</v>
       </c>
       <c r="J168" t="n">
-        <v>1.3243</v>
+        <v>0.6327</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2728</v>
+        <v>-0.1822</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.1832</v>
+        <v>-3.4618</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6088</v>
+        <v>-0.4036</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.5672</v>
+        <v>-7.6684</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.745</v>
+        <v>-0.5049</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.155</v>
+        <v>-9.5931</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.16</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3848</v>
+        <v>0.4282</v>
       </c>
       <c r="J172" t="n">
-        <v>7.3112</v>
+        <v>8.1358</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1134</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>2.1546</v>
+        <v>1.5409</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1755</v>
+        <v>-0.1395</v>
       </c>
       <c r="J174" t="n">
-        <v>-3.3345</v>
+        <v>-2.6505</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5102</v>
+        <v>-0.3349</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.6938</v>
+        <v>-6.3631</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7892</v>
+        <v>-0.5387</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.9948</v>
+        <v>-10.2353</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4689</v>
+        <v>1.3044</v>
       </c>
       <c r="J177" t="n">
-        <v>27.9091</v>
+        <v>24.7836</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0747</v>
+        <v>1.0533</v>
       </c>
       <c r="J178" t="n">
-        <v>20.4193</v>
+        <v>20.0127</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3507</v>
+        <v>0.4262</v>
       </c>
       <c r="J179" t="n">
-        <v>6.6633</v>
+        <v>8.097799999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3239</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
-        <v>6.1541</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5438</v>
+        <v>-0.4726</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3322</v>
+        <v>-8.9794</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.34</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5616</v>
+        <v>0.6745</v>
       </c>
       <c r="J182" t="n">
-        <v>16.848</v>
+        <v>20.235</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1415</v>
+        <v>0.156</v>
       </c>
       <c r="J183" t="n">
-        <v>4.245</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1207</v>
+        <v>0.134</v>
       </c>
       <c r="J184" t="n">
-        <v>3.621</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1263</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.789</v>
+        <v>-1.986</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.473</v>
+        <v>-0.3014</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.19</v>
+        <v>-9.042</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6128</v>
+        <v>0.5863</v>
       </c>
       <c r="J187" t="n">
-        <v>18.384</v>
+        <v>17.589</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4213</v>
+        <v>0.4053</v>
       </c>
       <c r="J188" t="n">
-        <v>12.639</v>
+        <v>12.159</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3911</v>
+        <v>0.3786</v>
       </c>
       <c r="J189" t="n">
-        <v>11.733</v>
+        <v>11.358</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3264</v>
+        <v>0.3244</v>
       </c>
       <c r="J190" t="n">
-        <v>9.792</v>
+        <v>9.731999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4385</v>
+        <v>-0.3745</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.155</v>
+        <v>-11.235</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.5</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2232</v>
+        <v>1.142</v>
       </c>
       <c r="J192" t="n">
-        <v>29.3568</v>
+        <v>27.408</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>1.08</v>
+        <v>1.051</v>
       </c>
       <c r="J193" t="n">
-        <v>25.92</v>
+        <v>25.224</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.34</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8851</v>
+        <v>0.8855</v>
       </c>
       <c r="J194" t="n">
-        <v>21.2424</v>
+        <v>21.252</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3593</v>
+        <v>-0.2822</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.623200000000001</v>
+        <v>-6.7728</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7763</v>
+        <v>-0.7259</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.6312</v>
+        <v>-17.4216</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5036</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>12.0864</v>
+        <v>14.1648</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1509</v>
+        <v>0.1294</v>
       </c>
       <c r="J198" t="n">
-        <v>3.6216</v>
+        <v>3.1056</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2739</v>
+        <v>-0.1824</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.5736</v>
+        <v>-4.3776</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.622</v>
+        <v>-0.4132</v>
       </c>
       <c r="J200" t="n">
-        <v>-14.928</v>
+        <v>-9.9168</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6347</v>
+        <v>-0.4225</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.2328</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.97</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0171</v>
+        <v>-0.0202</v>
       </c>
       <c r="J202" t="n">
-        <v>0.3591</v>
+        <v>-0.4242</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1341</v>
+        <v>-0.1208</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.8161</v>
+        <v>-2.5368</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.88</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1515</v>
+        <v>-0.132</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.1815</v>
+        <v>-2.772</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.74</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4049</v>
+        <v>-0.2711</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.5029</v>
+        <v>-5.6931</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.47</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7693</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.1553</v>
+        <v>-10.9977</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8264</v>
+        <v>1.5454</v>
       </c>
       <c r="J207" t="n">
-        <v>38.3544</v>
+        <v>32.4534</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.36</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8774</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>18.4254</v>
+        <v>18.9987</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.3</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7286</v>
+        <v>0.7738</v>
       </c>
       <c r="J209" t="n">
-        <v>15.3006</v>
+        <v>16.2498</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.358</v>
+        <v>0.4427</v>
       </c>
       <c r="J210" t="n">
-        <v>7.518</v>
+        <v>9.2967</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7735</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.2435</v>
+        <v>-15.1473</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.64</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4549</v>
+        <v>1.2968</v>
       </c>
       <c r="J212" t="n">
-        <v>30.5529</v>
+        <v>27.2328</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9072</v>
+        <v>0.9284</v>
       </c>
       <c r="J213" t="n">
-        <v>19.0512</v>
+        <v>19.4964</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.27</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6482</v>
+        <v>0.7098</v>
       </c>
       <c r="J214" t="n">
-        <v>13.6122</v>
+        <v>14.9058</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.337</v>
+        <v>0.4195</v>
       </c>
       <c r="J215" t="n">
-        <v>7.077</v>
+        <v>8.8095</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.97</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.286</v>
+        <v>-0.2015</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.006</v>
+        <v>-4.2315</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6746</v>
+        <v>0.8287</v>
       </c>
       <c r="J217" t="n">
-        <v>14.1666</v>
+        <v>17.4027</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0101</v>
+        <v>-0.0126</v>
       </c>
       <c r="J218" t="n">
-        <v>0.2121</v>
+        <v>-0.2646</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.125</v>
+        <v>-0.0929</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.625</v>
+        <v>-1.9509</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1735</v>
+        <v>-0.1148</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.6435</v>
+        <v>-2.4108</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9127</v>
+        <v>-0.6361</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.1667</v>
+        <v>-13.3581</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.4865</v>
+        <v>6.6588</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1882</v>
+        <v>1.2197</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2903</v>
+        <v>2.407</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4865</v>
+        <v>6.6588</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9672</v>
+        <v>2.9108</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5193</v>
+        <v>3.748</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9683</v>
+        <v>4.7097</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5833</v>
+        <v>2.5432</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5193</v>
+        <v>3.748</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -529,7 +529,7 @@
         <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1026</v>
+        <v>6.2912</v>
       </c>
       <c r="N2" t="n">
         <v>120</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3945</v>
+        <v>5.4705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9881</v>
+        <v>1.0021</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7973</v>
+        <v>1.8661</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3945</v>
+        <v>5.4705</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5108</v>
+        <v>2.4507</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8837</v>
+        <v>3.0198</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3601</v>
+        <v>3.1917</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7471</v>
+        <v>1.7235</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8837</v>
+        <v>3.0198</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -575,7 +575,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>4.630800000000001</v>
+        <v>4.7433</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7489</v>
+        <v>3.8204</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6867</v>
+        <v>0.6998</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0544</v>
+        <v>1.1149</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7489</v>
+        <v>3.8204</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3017</v>
+        <v>3.3206</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4472</v>
+        <v>0.4998</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1469</v>
+        <v>6.0618</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1961</v>
+        <v>3.2733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4472</v>
+        <v>0.4998</v>
       </c>
       <c r="K4" t="n">
         <v>76</v>
@@ -621,7 +621,7 @@
         <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6433</v>
+        <v>3.7731</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5212</v>
+        <v>3.5605</v>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.6522</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9516</v>
+        <v>0.9966</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5212</v>
+        <v>3.5605</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2699</v>
+        <v>2.2076</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2513</v>
+        <v>1.3529</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5116</v>
+        <v>2.3895</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3059</v>
+        <v>1.2903</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2513</v>
+        <v>1.3529</v>
       </c>
       <c r="K5" t="n">
         <v>43</v>
@@ -667,7 +667,7 @@
         <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5572</v>
+        <v>2.6432</v>
       </c>
       <c r="N5" t="n">
         <v>160</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3243</v>
+        <v>3.3056</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6089</v>
+        <v>0.6055</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8627</v>
+        <v>0.8806</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3243</v>
+        <v>3.3056</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6335</v>
+        <v>2.5334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6908</v>
+        <v>0.7722</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7926</v>
+        <v>3.4643</v>
       </c>
       <c r="I6" t="n">
-        <v>1.972</v>
+        <v>1.8707</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6908</v>
+        <v>0.7722</v>
       </c>
       <c r="K6" t="n">
         <v>76</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6628</v>
+        <v>2.6429</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -722,81 +722,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1243</v>
+        <v>3.0888</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5723</v>
+        <v>0.5658</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7725</v>
+        <v>0.7819</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1243</v>
+        <v>3.0888</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1243</v>
+        <v>3.4411</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.3523</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5006</v>
+        <v>6.4594</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5006</v>
+        <v>3.488</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.3523</v>
       </c>
       <c r="K7" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5006</v>
+        <v>3.1357</v>
       </c>
       <c r="N7" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0953</v>
+        <v>2.9508</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5405</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7594</v>
+        <v>0.7191</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0953</v>
+        <v>2.9508</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4301</v>
+        <v>3.3399</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3348</v>
+        <v>-0.3891</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5992</v>
+        <v>6.1255</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4313</v>
+        <v>3.3077</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3348</v>
+        <v>-0.3891</v>
       </c>
       <c r="K8" t="n">
         <v>86</v>
@@ -805,7 +805,7 @@
         <v>45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0965</v>
+        <v>2.9186</v>
       </c>
       <c r="N8" t="n">
         <v>131</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0302</v>
+        <v>2.7696</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5551</v>
+        <v>0.5073</v>
       </c>
       <c r="D9" t="n">
-        <v>0.73</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0302</v>
+        <v>2.7696</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3899</v>
+        <v>2.7696</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3597</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4575</v>
+        <v>3.3368</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3576</v>
+        <v>3.3368</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3597</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9979</v>
+        <v>3.3368</v>
       </c>
       <c r="N9" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.946</v>
+        <v>2.6578</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5396</v>
+        <v>0.4868</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5857</v>
       </c>
       <c r="E10" t="n">
-        <v>2.946</v>
+        <v>2.6578</v>
       </c>
       <c r="F10" t="n">
-        <v>2.946</v>
+        <v>2.608</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1091</v>
+        <v>3.7106</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1091</v>
+        <v>2.0037</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="K10" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1091</v>
+        <v>2.0535</v>
       </c>
       <c r="N10" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6904</v>
+        <v>2.6509</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4928</v>
+        <v>0.4856</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5766</v>
+        <v>0.5825</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6904</v>
+        <v>2.6509</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6869</v>
+        <v>2.6509</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9805</v>
+        <v>3.077</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0697</v>
+        <v>3.077</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="L11" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0732</v>
+        <v>3.077</v>
       </c>
       <c r="N11" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4399</v>
+        <v>2.3762</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4469</v>
+        <v>0.4353</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4635</v>
+        <v>0.4575</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4399</v>
+        <v>2.3762</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4971</v>
+        <v>2.4247</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0572</v>
+        <v>-0.0485</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3118</v>
+        <v>3.1058</v>
       </c>
       <c r="I12" t="n">
-        <v>1.722</v>
+        <v>1.6771</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0572</v>
+        <v>-0.0485</v>
       </c>
       <c r="K12" t="n">
         <v>76</v>
@@ -989,7 +989,7 @@
         <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6648</v>
+        <v>1.6286</v>
       </c>
       <c r="N12" t="n">
         <v>158</v>
@@ -998,81 +998,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3414</v>
+        <v>2.2798</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4289</v>
+        <v>0.4176</v>
       </c>
       <c r="D13" t="n">
-        <v>0.419</v>
+        <v>0.4136</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3414</v>
+        <v>2.2798</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4371</v>
+        <v>2.1375</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.1423</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1007</v>
+        <v>2.1584</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6122</v>
+        <v>1.1655</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.1423</v>
       </c>
       <c r="K13" t="n">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5165</v>
+        <v>1.3078</v>
       </c>
       <c r="N13" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.277</v>
+        <v>2.237</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4171</v>
+        <v>0.4098</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3899</v>
+        <v>0.3941</v>
       </c>
       <c r="E14" t="n">
-        <v>2.277</v>
+        <v>2.237</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0944</v>
+        <v>2.3533</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1826</v>
+        <v>-0.1163</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0944</v>
+        <v>2.8702</v>
       </c>
       <c r="I14" t="n">
-        <v>1.089</v>
+        <v>1.5499</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1826</v>
+        <v>-0.1163</v>
       </c>
       <c r="K14" t="n">
         <v>86</v>
@@ -1081,7 +1081,7 @@
         <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2716</v>
+        <v>1.4336</v>
       </c>
       <c r="N14" t="n">
         <v>131</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2487</v>
+        <v>2.2322</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4119</v>
+        <v>0.4089</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3772</v>
+        <v>0.3919</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2487</v>
+        <v>2.2322</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2121</v>
+        <v>0.767</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0366</v>
+        <v>1.4652</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3079</v>
+        <v>0.767</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.4142</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0366</v>
+        <v>1.4652</v>
       </c>
       <c r="K15" t="n">
         <v>40</v>
@@ -1127,7 +1127,7 @@
         <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2366</v>
+        <v>1.8794</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -1136,185 +1136,185 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2341</v>
+        <v>2.2137</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4092</v>
+        <v>0.4055</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3706</v>
+        <v>0.3835</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2341</v>
+        <v>2.2137</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9476</v>
+        <v>1.9854</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2865</v>
+        <v>0.2283</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9476</v>
+        <v>1.9854</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4927</v>
+        <v>1.0721</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2865</v>
+        <v>0.2283</v>
       </c>
       <c r="K16" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L16" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7792</v>
+        <v>1.3004</v>
       </c>
       <c r="N16" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1082</v>
+        <v>2.1056</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3862</v>
+        <v>0.3857</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3137</v>
+        <v>0.3343</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1082</v>
+        <v>2.1056</v>
       </c>
       <c r="F17" t="n">
-        <v>0.831</v>
+        <v>0.8756</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2772</v>
+        <v>1.23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.831</v>
+        <v>0.8756</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4321</v>
+        <v>0.4728</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2772</v>
+        <v>1.23</v>
       </c>
       <c r="K17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L17" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7093</v>
+        <v>1.7028</v>
       </c>
       <c r="N17" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8744</v>
+        <v>2.0146</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3433</v>
+        <v>0.369</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2082</v>
+        <v>0.2929</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8744</v>
+        <v>2.0146</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7548</v>
+        <v>-0.4822</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1196</v>
+        <v>2.4968</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7548</v>
+        <v>-0.4822</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9124</v>
+        <v>-0.2604</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1196</v>
+        <v>2.4968</v>
       </c>
       <c r="K18" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L18" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M18" t="n">
-        <v>1.032</v>
+        <v>2.2364</v>
       </c>
       <c r="N18" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7503</v>
+        <v>1.8258</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3206</v>
+        <v>0.3344</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1522</v>
+        <v>0.2069</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7503</v>
+        <v>1.8258</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6179</v>
+        <v>1.6424</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3682</v>
+        <v>0.1834</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6179</v>
+        <v>1.6424</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3213</v>
+        <v>0.8869</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3682</v>
+        <v>0.1834</v>
       </c>
       <c r="K19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L19" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0469</v>
+        <v>1.0703</v>
       </c>
       <c r="N19" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6897</v>
+        <v>1.8168</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3095</v>
+        <v>0.3328</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1248</v>
+        <v>0.2028</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6897</v>
+        <v>1.8168</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6897</v>
+        <v>1.8168</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6897</v>
+        <v>1.8168</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6897</v>
+        <v>1.8168</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6897</v>
+        <v>1.8168</v>
       </c>
       <c r="N20" t="n">
         <v>122</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4845</v>
+        <v>1.3466</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2719</v>
+        <v>0.2467</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0322</v>
+        <v>-0.0112</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4845</v>
+        <v>1.3466</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4845</v>
+        <v>1.3466</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4845</v>
+        <v>1.3466</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4845</v>
+        <v>1.3466</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4845</v>
+        <v>1.3466</v>
       </c>
       <c r="N21" t="n">
         <v>105</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2735</v>
+        <v>1.1534</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2333</v>
+        <v>0.2113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0631</v>
+        <v>-0.0992</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2735</v>
+        <v>1.1534</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1886</v>
+        <v>1.0783</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0849</v>
+        <v>0.0751</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1886</v>
+        <v>1.0783</v>
       </c>
       <c r="I22" t="n">
-        <v>0.618</v>
+        <v>0.5823</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0849</v>
+        <v>0.0751</v>
       </c>
       <c r="K22" t="n">
         <v>76</v>
@@ -1449,7 +1449,7 @@
         <v>82</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7029</v>
+        <v>0.6574</v>
       </c>
       <c r="N22" t="n">
         <v>158</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1734</v>
+        <v>1.1473</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2149</v>
+        <v>0.2102</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1083</v>
+        <v>-0.1019</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1734</v>
+        <v>1.1473</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1734</v>
+        <v>1.1473</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1734</v>
+        <v>1.1473</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1734</v>
+        <v>1.1473</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1734</v>
+        <v>1.1473</v>
       </c>
       <c r="N23" t="n">
         <v>69</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.922</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1578</v>
+        <v>0.1689</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2491</v>
+        <v>-0.2045</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.922</v>
       </c>
       <c r="F24" t="n">
-        <v>0.788</v>
+        <v>0.7982</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1238</v>
       </c>
       <c r="H24" t="n">
-        <v>0.788</v>
+        <v>0.7982</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4097</v>
+        <v>0.431</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1238</v>
       </c>
       <c r="K24" t="n">
         <v>43</v>
@@ -1541,7 +1541,7 @@
         <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4831</v>
+        <v>0.5548</v>
       </c>
       <c r="N24" t="n">
         <v>160</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7643</v>
+        <v>0.7432</v>
       </c>
       <c r="C25" t="n">
-        <v>0.14</v>
+        <v>0.1361</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.293</v>
+        <v>-0.2859</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7643</v>
+        <v>0.7432</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7643</v>
+        <v>0.7432</v>
       </c>
       <c r="G25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2533</v>
+        <v>0.7432</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2115</v>
+        <v>0.7432</v>
       </c>
       <c r="J25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="L25" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2115</v>
+        <v>0.7432</v>
       </c>
       <c r="N25" t="n">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7416</v>
+        <v>0.6787</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1358</v>
+        <v>0.1243</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3032</v>
+        <v>-0.3152</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7416</v>
+        <v>0.6787</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7416</v>
+        <v>2.6787</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7416</v>
+        <v>3.9439</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7416</v>
+        <v>2.1297</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K26" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7416</v>
+        <v>0.1297000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6952</v>
+        <v>0.6212</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1273</v>
+        <v>0.1138</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3242</v>
+        <v>-0.3414</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6952</v>
+        <v>0.6212</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6952</v>
+        <v>0.6212</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6952</v>
+        <v>0.6212</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6952</v>
+        <v>0.6212</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6952</v>
+        <v>0.6212</v>
       </c>
       <c r="N27" t="n">
         <v>79</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0752</v>
+        <v>0.0373</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0138</v>
+        <v>0.0068</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6041</v>
+        <v>-0.6072</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0752</v>
+        <v>0.0373</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0752</v>
+        <v>0.0373</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0752</v>
+        <v>0.0373</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0752</v>
+        <v>0.0373</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0752</v>
+        <v>0.0373</v>
       </c>
       <c r="N28" t="n">
         <v>69</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0122</v>
+        <v>-0.0598</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0022</v>
+        <v>-0.011</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6435</v>
+        <v>-0.6514</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0122</v>
+        <v>-0.0598</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0122</v>
+        <v>-0.0598</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0122</v>
+        <v>-0.0598</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0122</v>
+        <v>-0.0598</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0122</v>
+        <v>-0.0598</v>
       </c>
       <c r="N29" t="n">
         <v>79</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0517</v>
+        <v>-0.1271</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0095</v>
+        <v>-0.0233</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6614</v>
+        <v>-0.6821</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0517</v>
+        <v>-0.1271</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0517</v>
+        <v>-0.1271</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0517</v>
+        <v>-0.1271</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0517</v>
+        <v>-0.1271</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0517</v>
+        <v>-0.1271</v>
       </c>
       <c r="N30" t="n">
         <v>105</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.18</v>
+        <v>-0.186</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.033</v>
+        <v>-0.0341</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.7089</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.18</v>
+        <v>-0.186</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.18</v>
+        <v>-0.186</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.18</v>
+        <v>-0.186</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.18</v>
+        <v>-0.186</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.18</v>
+        <v>-0.186</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1812</v>
+        <v>-0.2157</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0332</v>
+        <v>-0.0395</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7198</v>
+        <v>-0.7224</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1812</v>
+        <v>-0.2157</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1812</v>
+        <v>-0.2157</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1812</v>
+        <v>-0.2157</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1812</v>
+        <v>-0.2157</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1812</v>
+        <v>-0.2157</v>
       </c>
       <c r="N32" t="n">
         <v>105</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2734</v>
+        <v>-0.3092</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0501</v>
+        <v>-0.0566</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7614</v>
+        <v>-0.765</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2734</v>
+        <v>-0.3092</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2734</v>
+        <v>-0.3092</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2734</v>
+        <v>-0.3092</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2734</v>
+        <v>-0.3092</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2734</v>
+        <v>-0.3092</v>
       </c>
       <c r="N33" t="n">
         <v>69</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2861</v>
+        <v>-0.3244</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0524</v>
+        <v>-0.0594</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7672</v>
+        <v>-0.7719</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2861</v>
+        <v>-0.3244</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2861</v>
+        <v>-0.3244</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2861</v>
+        <v>-0.3244</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2861</v>
+        <v>-0.3244</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2861</v>
+        <v>-0.3244</v>
       </c>
       <c r="N34" t="n">
         <v>105</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.2963</v>
+        <v>-0.3349</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0543</v>
+        <v>-0.0613</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7718</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2963</v>
+        <v>-0.3349</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2963</v>
+        <v>-0.3349</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2963</v>
+        <v>-0.3349</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2963</v>
+        <v>-0.3349</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.2963</v>
+        <v>-0.3349</v>
       </c>
       <c r="N35" t="n">
         <v>69</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5824</v>
+        <v>-0.5595</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1067</v>
+        <v>-0.1025</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9009</v>
+        <v>-0.8789</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5824</v>
+        <v>-0.5595</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5824</v>
+        <v>-0.5595</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5824</v>
+        <v>-0.5595</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5824</v>
+        <v>-0.5595</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5824</v>
+        <v>-0.5595</v>
       </c>
       <c r="N36" t="n">
         <v>105</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1522</v>
+        <v>-0.167</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0132</v>
+        <v>-1.0392</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9116</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0322</v>
+        <v>-1.0495</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1891</v>
+        <v>-0.1922</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.104</v>
+        <v>-1.102</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0322</v>
+        <v>-1.0495</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0322</v>
+        <v>-1.0495</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0322</v>
+        <v>-1.0495</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0322</v>
+        <v>-1.0495</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0322</v>
+        <v>-1.0495</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0688</v>
+        <v>-1.0988</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1958</v>
+        <v>-0.2013</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1205</v>
+        <v>-1.1244</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0688</v>
+        <v>-1.0988</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0688</v>
+        <v>-1.0988</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0688</v>
+        <v>-1.0988</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0688</v>
+        <v>-1.0988</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0688</v>
+        <v>-1.0988</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1824</v>
+        <v>-1.1996</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2166</v>
+        <v>-0.2197</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1718</v>
+        <v>-1.1703</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1824</v>
+        <v>-1.1996</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1824</v>
+        <v>-1.1996</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1824</v>
+        <v>-1.1996</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1824</v>
+        <v>-1.1996</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1824</v>
+        <v>-1.1996</v>
       </c>
       <c r="N40" t="n">
         <v>79</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7425</v>
+        <v>-1.6467</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3192</v>
+        <v>-0.3016</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4247</v>
+        <v>-1.3738</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7425</v>
+        <v>-1.6467</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4653</v>
+        <v>-1.3411</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2772</v>
+        <v>-0.3056</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4653</v>
+        <v>-1.3411</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7619</v>
+        <v>-0.7242</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.2772</v>
+        <v>-0.3056</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0391</v>
+        <v>-1.0298</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2429,10 +2429,10 @@
         <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1984</v>
+        <v>1.2269</v>
       </c>
       <c r="J2" t="n">
-        <v>21.5712</v>
+        <v>22.0842</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0335</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>18.603</v>
+        <v>17.8092</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6645</v>
+        <v>0.6417</v>
       </c>
       <c r="J4" t="n">
-        <v>11.961</v>
+        <v>11.5506</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.471</v>
+        <v>0.4681</v>
       </c>
       <c r="J5" t="n">
-        <v>8.478</v>
+        <v>8.425800000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1231</v>
+        <v>-0.1071</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.2158</v>
+        <v>-1.9278</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6794</v>
+        <v>0.6434</v>
       </c>
       <c r="J7" t="n">
-        <v>12.2292</v>
+        <v>11.5812</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.153</v>
+        <v>-0.1696</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.754</v>
+        <v>-3.0528</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.183</v>
+        <v>-0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.294</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2524</v>
+        <v>-0.269</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.5432</v>
+        <v>-4.842</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.451</v>
+        <v>-0.4603</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.118</v>
+        <v>-8.285399999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3678</v>
+        <v>1.4759</v>
       </c>
       <c r="J12" t="n">
-        <v>23.2526</v>
+        <v>25.0903</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.72</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3562</v>
+        <v>1.4604</v>
       </c>
       <c r="J13" t="n">
-        <v>23.0554</v>
+        <v>24.8268</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.228</v>
+        <v>1.2778</v>
       </c>
       <c r="J14" t="n">
-        <v>20.876</v>
+        <v>21.7226</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.19</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4846</v>
+        <v>0.4879</v>
       </c>
       <c r="J15" t="n">
-        <v>8.238200000000001</v>
+        <v>8.2943</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1052</v>
+        <v>-0.0733</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7884</v>
+        <v>-1.2461</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1098</v>
+        <v>1.0681</v>
       </c>
       <c r="J17" t="n">
-        <v>18.8666</v>
+        <v>18.1577</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2758</v>
+        <v>-0.2971</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.6886</v>
+        <v>-5.0507</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4413</v>
+        <v>-0.4557</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.5021</v>
+        <v>-7.7469</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.45</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.5347</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.9369</v>
+        <v>-9.0899</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7693</v>
+        <v>-0.7589</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.0781</v>
+        <v>-12.9013</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.56</v>
       </c>
       <c r="I22" t="n">
-        <v>0.973</v>
+        <v>1.0643</v>
       </c>
       <c r="J22" t="n">
-        <v>34.055</v>
+        <v>37.2505</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3897</v>
+        <v>0.4206</v>
       </c>
       <c r="J23" t="n">
-        <v>13.6395</v>
+        <v>14.721</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1198</v>
+        <v>-0.1175</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.193</v>
+        <v>-4.1125</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1919</v>
+        <v>-0.1878</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.7165</v>
+        <v>-6.573</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4355</v>
+        <v>-0.4147</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.2425</v>
+        <v>-14.5145</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4975</v>
+        <v>0.5507</v>
       </c>
       <c r="J27" t="n">
-        <v>17.4125</v>
+        <v>19.2745</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1224</v>
+        <v>0.1291</v>
       </c>
       <c r="J28" t="n">
-        <v>4.284</v>
+        <v>4.5185</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.097</v>
+        <v>-0.1092</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.395</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1085</v>
+        <v>-0.1212</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.7975</v>
+        <v>-4.242</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3611</v>
+        <v>-0.3724</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.6385</v>
+        <v>-13.034</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.264</v>
+        <v>0.2712</v>
       </c>
       <c r="J32" t="n">
-        <v>6.336</v>
+        <v>6.5088</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1728</v>
+        <v>0.1823</v>
       </c>
       <c r="J33" t="n">
-        <v>4.1472</v>
+        <v>4.3752</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.05</v>
+        <v>-0.0582</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.2</v>
+        <v>-1.3968</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1</v>
+        <v>-0.1115</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.4</v>
+        <v>-2.676</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1775</v>
+        <v>-0.1909</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.26</v>
+        <v>-4.5816</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3049</v>
+        <v>0.3167</v>
       </c>
       <c r="J37" t="n">
-        <v>7.3176</v>
+        <v>7.6008</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1259</v>
+        <v>0.1387</v>
       </c>
       <c r="J38" t="n">
-        <v>3.0216</v>
+        <v>3.3288</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1106</v>
+        <v>0.123</v>
       </c>
       <c r="J39" t="n">
-        <v>2.6544</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.024</v>
+        <v>0.0301</v>
       </c>
       <c r="J40" t="n">
-        <v>0.576</v>
+        <v>0.7224</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2125</v>
+        <v>-0.2252</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.1</v>
+        <v>-5.4048</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.67</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1176</v>
+        <v>1.2167</v>
       </c>
       <c r="J42" t="n">
-        <v>25.7048</v>
+        <v>27.9841</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.695</v>
+        <v>0.7651</v>
       </c>
       <c r="J43" t="n">
-        <v>15.985</v>
+        <v>17.5973</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0328</v>
+        <v>0.0447</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7544</v>
+        <v>1.0281</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0328</v>
+        <v>0.0447</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7544</v>
+        <v>1.0281</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.44</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.5065</v>
+        <v>-1.3468</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.6495</v>
+        <v>-30.9764</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6619</v>
+        <v>0.7427</v>
       </c>
       <c r="J47" t="n">
-        <v>15.2237</v>
+        <v>17.0821</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.6474</v>
       </c>
       <c r="J48" t="n">
-        <v>13.2733</v>
+        <v>14.8902</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0743</v>
+        <v>-0.081</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.7089</v>
+        <v>-1.863</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1115</v>
+        <v>-0.1204</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.5645</v>
+        <v>-2.7692</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2902</v>
+        <v>-0.3006</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.6746</v>
+        <v>-6.9138</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3073</v>
+        <v>1.4191</v>
       </c>
       <c r="J52" t="n">
-        <v>31.3752</v>
+        <v>34.0584</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8404</v>
       </c>
       <c r="J53" t="n">
-        <v>18.2784</v>
+        <v>20.1696</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2052</v>
+        <v>-0.1971</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.9248</v>
+        <v>-4.7304</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4488</v>
+        <v>-0.4241</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.7712</v>
+        <v>-10.1784</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9625</v>
+        <v>-0.8797</v>
       </c>
       <c r="J56" t="n">
-        <v>-23.1</v>
+        <v>-21.1128</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5527</v>
+        <v>0.6127</v>
       </c>
       <c r="J57" t="n">
-        <v>13.2648</v>
+        <v>14.7048</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.007</v>
+        <v>0.0049</v>
       </c>
       <c r="J58" t="n">
-        <v>0.168</v>
+        <v>0.1176</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0599</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.4376</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2928</v>
+        <v>-0.3063</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.0272</v>
+        <v>-7.3512</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2928</v>
+        <v>-0.3063</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.0272</v>
+        <v>-7.3512</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5407</v>
+        <v>0.599</v>
       </c>
       <c r="J62" t="n">
-        <v>11.3547</v>
+        <v>12.579</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4701</v>
+        <v>0.5198</v>
       </c>
       <c r="J63" t="n">
-        <v>9.8721</v>
+        <v>10.9158</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4273</v>
+        <v>0.4711</v>
       </c>
       <c r="J64" t="n">
-        <v>8.9733</v>
+        <v>9.8931</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4273</v>
+        <v>0.4711</v>
       </c>
       <c r="J65" t="n">
-        <v>8.9733</v>
+        <v>9.8931</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1915</v>
+        <v>0.2048</v>
       </c>
       <c r="J66" t="n">
-        <v>4.0215</v>
+        <v>4.3008</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1971</v>
+        <v>0.19</v>
       </c>
       <c r="J67" t="n">
-        <v>4.1391</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0669</v>
+        <v>-0.0828</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.4049</v>
+        <v>-1.7388</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2173</v>
+        <v>-0.2356</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.5633</v>
+        <v>-4.9476</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3418</v>
+        <v>-0.3572</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.1778</v>
+        <v>-7.5012</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3701</v>
+        <v>-0.3844</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.7721</v>
+        <v>-8.0724</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>1.1321</v>
+        <v>1.0935</v>
       </c>
       <c r="J72" t="n">
-        <v>22.642</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0672</v>
+        <v>1.0203</v>
       </c>
       <c r="J73" t="n">
-        <v>21.344</v>
+        <v>20.406</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5034</v>
       </c>
       <c r="J74" t="n">
-        <v>10.292</v>
+        <v>10.068</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.99</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>-2</v>
+        <v>-1.818</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5933</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.866</v>
+        <v>-11.058</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9829</v>
+        <v>0.924</v>
       </c>
       <c r="J77" t="n">
-        <v>19.658</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0196</v>
+        <v>0.0141</v>
       </c>
       <c r="J78" t="n">
-        <v>0.392</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.7</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3247</v>
+        <v>-0.3386</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.494</v>
+        <v>-6.772</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3247</v>
+        <v>-0.3386</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.494</v>
+        <v>-6.772</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.63</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3906</v>
+        <v>-0.4021</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.812</v>
+        <v>-8.042</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.27</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J82" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>1.058</v>
+        <v>1.0206</v>
       </c>
       <c r="J83" t="n">
-        <v>16.928</v>
+        <v>16.3296</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7337</v>
+        <v>0.7119</v>
       </c>
       <c r="J84" t="n">
-        <v>11.7392</v>
+        <v>11.3904</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6647</v>
+        <v>0.6509</v>
       </c>
       <c r="J85" t="n">
-        <v>10.6352</v>
+        <v>10.4144</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6178</v>
+        <v>0.6093</v>
       </c>
       <c r="J86" t="n">
-        <v>9.8848</v>
+        <v>9.748799999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0625</v>
+        <v>-0.0883</v>
       </c>
       <c r="J87" t="n">
-        <v>-1</v>
+        <v>-1.4128</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.84</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1461</v>
+        <v>-0.1714</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.3376</v>
+        <v>-2.7424</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3285</v>
+        <v>-0.3487</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.256</v>
+        <v>-5.5792</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5239</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.217599999999999</v>
+        <v>-8.382400000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.43</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5419</v>
+        <v>-0.5501</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.670400000000001</v>
+        <v>-8.801600000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2.28</v>
       </c>
       <c r="I92" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J92" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>2.03</v>
       </c>
       <c r="I93" t="n">
-        <v>1.6874</v>
+        <v>1.6951</v>
       </c>
       <c r="J93" t="n">
-        <v>26.9984</v>
+        <v>27.1216</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.999</v>
+        <v>0.9544</v>
       </c>
       <c r="J94" t="n">
-        <v>15.984</v>
+        <v>15.2704</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1096</v>
+        <v>0.1475</v>
       </c>
       <c r="J95" t="n">
-        <v>1.7536</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4742</v>
+        <v>-0.43</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.5872</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9411</v>
+        <v>0.8592</v>
       </c>
       <c r="J97" t="n">
-        <v>15.0576</v>
+        <v>13.7472</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3154</v>
+        <v>-0.335</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.0464</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3802</v>
+        <v>-0.3972</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.0832</v>
+        <v>-6.3552</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.43</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5485</v>
+        <v>-0.5553</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.776</v>
+        <v>-8.8848</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.42</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5578</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.924799999999999</v>
+        <v>-9.023999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1589</v>
+        <v>1.1269</v>
       </c>
       <c r="J102" t="n">
-        <v>24.3369</v>
+        <v>23.6649</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.45</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0586</v>
+        <v>1.0149</v>
       </c>
       <c r="J103" t="n">
-        <v>22.2306</v>
+        <v>21.3129</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5917</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>12.4257</v>
+        <v>12.1191</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4168</v>
+        <v>0.4196</v>
       </c>
       <c r="J105" t="n">
-        <v>8.752800000000001</v>
+        <v>8.8116</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.309</v>
+        <v>0.3211</v>
       </c>
       <c r="J106" t="n">
-        <v>6.489</v>
+        <v>6.7431</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.55</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0451</v>
+        <v>0.9964</v>
       </c>
       <c r="J107" t="n">
-        <v>21.9471</v>
+        <v>20.9244</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4845</v>
+        <v>0.4709</v>
       </c>
       <c r="J108" t="n">
-        <v>10.1745</v>
+        <v>9.8889</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2301</v>
+        <v>-0.2455</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.8321</v>
+        <v>-5.1555</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3653</v>
+        <v>-0.3773</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.6713</v>
+        <v>-7.9233</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.41</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5926</v>
+        <v>-0.5928</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.4446</v>
+        <v>-12.4488</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3478</v>
+        <v>1.3211</v>
       </c>
       <c r="J112" t="n">
-        <v>32.3472</v>
+        <v>31.7064</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0638</v>
+        <v>1.0139</v>
       </c>
       <c r="J113" t="n">
-        <v>25.5312</v>
+        <v>24.3336</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0348</v>
+        <v>-0.024</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0348</v>
+        <v>-0.024</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.0325</v>
+        <v>-0.9406</v>
       </c>
       <c r="J116" t="n">
-        <v>-24.78</v>
+        <v>-22.5744</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4337</v>
+        <v>0.4265</v>
       </c>
       <c r="J117" t="n">
-        <v>10.4088</v>
+        <v>10.236</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1713</v>
+        <v>0.177</v>
       </c>
       <c r="J118" t="n">
-        <v>4.1112</v>
+        <v>4.248</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.1328</v>
+        <v>-1.3464</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.91</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1188</v>
+        <v>-0.1321</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.8512</v>
+        <v>-3.1704</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.36</v>
+        <v>-0.3715</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.916</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7973</v>
+        <v>0.7471</v>
       </c>
       <c r="J122" t="n">
-        <v>19.1352</v>
+        <v>17.9304</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4145</v>
+        <v>0.4061</v>
       </c>
       <c r="J123" t="n">
-        <v>9.948</v>
+        <v>9.7464</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3872</v>
+        <v>0.3812</v>
       </c>
       <c r="J124" t="n">
-        <v>9.2928</v>
+        <v>9.1488</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3357</v>
+        <v>-0.3262</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.056800000000001</v>
+        <v>-7.8288</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5319</v>
+        <v>-0.5047</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.7656</v>
+        <v>-12.1128</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.85</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2732</v>
+        <v>1.2598</v>
       </c>
       <c r="J127" t="n">
-        <v>30.5568</v>
+        <v>30.2352</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0567</v>
+        <v>-0.0633</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.3608</v>
+        <v>-1.5192</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1851</v>
+        <v>-0.1969</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.4424</v>
+        <v>-4.7256</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.206</v>
+        <v>-0.2179</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.944</v>
+        <v>-5.2296</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2265</v>
+        <v>-0.2384</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.436</v>
+        <v>-5.7216</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0159</v>
+        <v>-0.0124</v>
       </c>
       <c r="J132" t="n">
-        <v>0.2544</v>
+        <v>-0.1984</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1088</v>
+        <v>-0.1327</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.7408</v>
+        <v>-2.1232</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.323</v>
+        <v>-0.3426</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.168</v>
+        <v>-5.4816</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4998</v>
+        <v>-0.5103</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.9968</v>
+        <v>-8.1648</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5279</v>
+        <v>-0.5365</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.446400000000001</v>
+        <v>-8.584</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J137" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.82</v>
       </c>
       <c r="I138" t="n">
-        <v>1.4546</v>
+        <v>1.4504</v>
       </c>
       <c r="J138" t="n">
-        <v>23.2736</v>
+        <v>23.2064</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3901</v>
+        <v>0.4063</v>
       </c>
       <c r="J139" t="n">
-        <v>6.2416</v>
+        <v>6.5008</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.311</v>
+        <v>0.3343</v>
       </c>
       <c r="J140" t="n">
-        <v>4.976</v>
+        <v>5.3488</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4159</v>
+        <v>-0.3759</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.6544</v>
+        <v>-6.0144</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.68</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8297</v>
+        <v>0.8137</v>
       </c>
       <c r="J142" t="n">
-        <v>19.9128</v>
+        <v>19.5288</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3825</v>
+        <v>0.3958</v>
       </c>
       <c r="J143" t="n">
-        <v>9.18</v>
+        <v>9.4992</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1849</v>
+        <v>0.2019</v>
       </c>
       <c r="J144" t="n">
-        <v>4.4376</v>
+        <v>4.8456</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1618</v>
+        <v>-0.1711</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.8832</v>
+        <v>-4.1064</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2555</v>
+        <v>-0.2653</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.132</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8213</v>
+        <v>0.7861</v>
       </c>
       <c r="J147" t="n">
-        <v>19.7112</v>
+        <v>18.8664</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.449</v>
+        <v>0.4456</v>
       </c>
       <c r="J148" t="n">
-        <v>10.776</v>
+        <v>10.6944</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1439</v>
+        <v>-0.1572</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.4536</v>
+        <v>-3.7728</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.428</v>
+        <v>-0.4362</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.272</v>
+        <v>-10.4688</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.428</v>
+        <v>-0.4362</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.272</v>
+        <v>-10.4688</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.8</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1551</v>
+        <v>-0.1871</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.3265</v>
+        <v>-2.8065</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.78</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1783</v>
+        <v>-0.2093</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.6745</v>
+        <v>-3.1395</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2875</v>
+        <v>-0.3135</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.3125</v>
+        <v>-4.7025</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.28</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6692</v>
+        <v>-0.6693</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.038</v>
+        <v>-10.0395</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.26</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6889</v>
+        <v>-0.6872</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.3335</v>
+        <v>-10.308</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.17</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8328</v>
+        <v>1.8477</v>
       </c>
       <c r="J157" t="n">
-        <v>27.492</v>
+        <v>27.7155</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>2.01</v>
       </c>
       <c r="I158" t="n">
-        <v>1.6594</v>
+        <v>1.6668</v>
       </c>
       <c r="J158" t="n">
-        <v>24.891</v>
+        <v>25.002</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0885</v>
+        <v>1.0576</v>
       </c>
       <c r="J159" t="n">
-        <v>16.3275</v>
+        <v>15.864</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1939</v>
+        <v>0.2278</v>
       </c>
       <c r="J160" t="n">
-        <v>2.9085</v>
+        <v>3.417</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.08</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1647</v>
+        <v>0.2006</v>
       </c>
       <c r="J161" t="n">
-        <v>2.4705</v>
+        <v>3.009</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1605</v>
+        <v>1.1283</v>
       </c>
       <c r="J162" t="n">
-        <v>22.0495</v>
+        <v>21.4377</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1356</v>
+        <v>1.1015</v>
       </c>
       <c r="J163" t="n">
-        <v>21.5764</v>
+        <v>20.9285</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7749</v>
+        <v>0.7402</v>
       </c>
       <c r="J164" t="n">
-        <v>14.7231</v>
+        <v>14.0638</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1639</v>
+        <v>0.1856</v>
       </c>
       <c r="J165" t="n">
-        <v>3.1141</v>
+        <v>3.5264</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0269</v>
+        <v>0.0534</v>
       </c>
       <c r="J166" t="n">
-        <v>0.5111</v>
+        <v>1.0146</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7749</v>
+        <v>0.7284</v>
       </c>
       <c r="J167" t="n">
-        <v>14.7231</v>
+        <v>13.8396</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0333</v>
+        <v>0.0241</v>
       </c>
       <c r="J168" t="n">
-        <v>0.6327</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1822</v>
+        <v>-0.1994</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.4618</v>
+        <v>-3.7886</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4036</v>
+        <v>-0.4155</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.6684</v>
+        <v>-7.8945</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5049</v>
+        <v>-0.5115</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.5931</v>
+        <v>-9.718500000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.16</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4282</v>
+        <v>0.4113</v>
       </c>
       <c r="J172" t="n">
-        <v>8.1358</v>
+        <v>7.8147</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>1.5409</v>
+        <v>1.4212</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1395</v>
+        <v>-0.1566</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.6505</v>
+        <v>-2.9754</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3349</v>
+        <v>-0.3501</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.3631</v>
+        <v>-6.6519</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5387</v>
+        <v>-0.5436</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.2353</v>
+        <v>-10.3284</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3044</v>
+        <v>1.2804</v>
       </c>
       <c r="J177" t="n">
-        <v>24.7836</v>
+        <v>24.3276</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0533</v>
+        <v>1.0067</v>
       </c>
       <c r="J178" t="n">
-        <v>20.0127</v>
+        <v>19.1273</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4262</v>
+        <v>0.4261</v>
       </c>
       <c r="J179" t="n">
-        <v>8.097799999999999</v>
+        <v>8.0959</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>0.4023</v>
       </c>
       <c r="J180" t="n">
-        <v>7.6</v>
+        <v>7.6437</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4726</v>
+        <v>-0.4408</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.9794</v>
+        <v>-8.3752</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.34</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6745</v>
+        <v>0.6513</v>
       </c>
       <c r="J182" t="n">
-        <v>20.235</v>
+        <v>19.539</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.156</v>
+        <v>0.166</v>
       </c>
       <c r="J183" t="n">
-        <v>4.68</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>0.134</v>
+        <v>0.1441</v>
       </c>
       <c r="J184" t="n">
-        <v>4.02</v>
+        <v>4.323</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.986</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3014</v>
+        <v>-0.3131</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.042</v>
+        <v>-9.393000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5863</v>
+        <v>0.5631</v>
       </c>
       <c r="J187" t="n">
-        <v>17.589</v>
+        <v>16.893</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4053</v>
+        <v>0.3998</v>
       </c>
       <c r="J188" t="n">
-        <v>12.159</v>
+        <v>11.994</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3786</v>
+        <v>0.3753</v>
       </c>
       <c r="J189" t="n">
-        <v>11.358</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3244</v>
+        <v>0.3252</v>
       </c>
       <c r="J190" t="n">
-        <v>9.731999999999999</v>
+        <v>9.756</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3745</v>
+        <v>-0.3598</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.235</v>
+        <v>-10.794</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.5</v>
       </c>
       <c r="I192" t="n">
-        <v>1.142</v>
+        <v>1.1047</v>
       </c>
       <c r="J192" t="n">
-        <v>27.408</v>
+        <v>26.5128</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>1.051</v>
+        <v>1.0014</v>
       </c>
       <c r="J193" t="n">
-        <v>25.224</v>
+        <v>24.0336</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.34</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8855</v>
+        <v>0.8335</v>
       </c>
       <c r="J194" t="n">
-        <v>21.252</v>
+        <v>20.004</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2822</v>
+        <v>-0.2674</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.7728</v>
+        <v>-6.4176</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7259</v>
+        <v>-0.6705</v>
       </c>
       <c r="J196" t="n">
-        <v>-17.4216</v>
+        <v>-16.092</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5621</v>
       </c>
       <c r="J197" t="n">
-        <v>14.1648</v>
+        <v>13.4904</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1294</v>
+        <v>0.1273</v>
       </c>
       <c r="J198" t="n">
-        <v>3.1056</v>
+        <v>3.0552</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1824</v>
+        <v>-0.1996</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.3776</v>
+        <v>-4.7904</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4132</v>
+        <v>-0.4246</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.9168</v>
+        <v>-10.1904</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4225</v>
+        <v>-0.4334</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.14</v>
+        <v>-10.4016</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.97</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0202</v>
+        <v>-0.0352</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.4242</v>
+        <v>-0.7392</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1208</v>
+        <v>-0.1395</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.5368</v>
+        <v>-2.9295</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.88</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.132</v>
+        <v>-0.1508</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.772</v>
+        <v>-3.1668</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.74</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2711</v>
+        <v>-0.2895</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.6931</v>
+        <v>-6.0795</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.47</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5304</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.9977</v>
+        <v>-11.1384</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5454</v>
+        <v>1.5365</v>
       </c>
       <c r="J207" t="n">
-        <v>32.4534</v>
+        <v>32.2665</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.36</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.855</v>
       </c>
       <c r="J208" t="n">
-        <v>18.9987</v>
+        <v>17.955</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.3</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7738</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>16.2498</v>
+        <v>15.5274</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4427</v>
+        <v>0.4431</v>
       </c>
       <c r="J210" t="n">
-        <v>9.2967</v>
+        <v>9.305099999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.6627</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.1473</v>
+        <v>-13.9167</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.64</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2968</v>
+        <v>1.2737</v>
       </c>
       <c r="J212" t="n">
-        <v>27.2328</v>
+        <v>26.7477</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.9284</v>
+        <v>0.876</v>
       </c>
       <c r="J213" t="n">
-        <v>19.4964</v>
+        <v>18.396</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.27</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7098</v>
+        <v>0.6821</v>
       </c>
       <c r="J214" t="n">
-        <v>14.9058</v>
+        <v>14.3241</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4195</v>
+        <v>0.4214</v>
       </c>
       <c r="J215" t="n">
-        <v>8.8095</v>
+        <v>8.849399999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.97</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2015</v>
+        <v>-0.1852</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.2315</v>
+        <v>-3.8892</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8287</v>
+        <v>0.7815</v>
       </c>
       <c r="J217" t="n">
-        <v>17.4027</v>
+        <v>16.4115</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0126</v>
+        <v>-0.0192</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.2646</v>
+        <v>-0.4032</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0929</v>
+        <v>-0.1061</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.9509</v>
+        <v>-2.2281</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1148</v>
+        <v>-0.1291</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.4108</v>
+        <v>-2.7111</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6361</v>
+        <v>-0.6335</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.3581</v>
+        <v>-13.3035</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6588</v>
+        <v>6.9658</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2197</v>
+        <v>1.276</v>
       </c>
       <c r="D2" t="n">
-        <v>2.407</v>
+        <v>2.4977</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6588</v>
+        <v>6.9658</v>
       </c>
       <c r="F2" t="n">
         <v>2.9108</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4705</v>
+        <v>5.5154</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0021</v>
+        <v>1.0103</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8661</v>
+        <v>1.8498</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4705</v>
+        <v>5.5154</v>
       </c>
       <c r="F3" t="n">
         <v>2.4507</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8204</v>
+        <v>4.0297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6998</v>
+        <v>0.7381</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1149</v>
+        <v>1.1862</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8204</v>
+        <v>4.0297</v>
       </c>
       <c r="F4" t="n">
         <v>3.3206</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5605</v>
+        <v>3.635</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6522</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9966</v>
+        <v>1.0099</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5605</v>
+        <v>3.635</v>
       </c>
       <c r="F5" t="n">
         <v>2.2076</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3056</v>
+        <v>3.2962</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6055</v>
+        <v>0.6038</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8806</v>
+        <v>0.8585</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3056</v>
+        <v>3.2962</v>
       </c>
       <c r="F6" t="n">
         <v>2.5334</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0888</v>
+        <v>3.2109</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5658</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7819</v>
+        <v>0.8204</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0888</v>
+        <v>3.2109</v>
       </c>
       <c r="F7" t="n">
         <v>3.4411</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9508</v>
+        <v>2.9825</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5405</v>
+        <v>0.5463</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7191</v>
+        <v>0.7184</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9508</v>
+        <v>2.9825</v>
       </c>
       <c r="F8" t="n">
         <v>3.3399</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7696</v>
+        <v>2.922</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5073</v>
+        <v>0.5352</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7696</v>
+        <v>2.922</v>
       </c>
       <c r="F9" t="n">
         <v>2.7696</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6578</v>
+        <v>2.7192</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4868</v>
+        <v>0.4981</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5857</v>
+        <v>0.6008</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6578</v>
+        <v>2.7192</v>
       </c>
       <c r="F10" t="n">
-        <v>2.608</v>
+        <v>2.6509</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0498</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7106</v>
+        <v>3.077</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0037</v>
+        <v>3.077</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0498</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="L10" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0535</v>
+        <v>3.077</v>
       </c>
       <c r="N10" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6509</v>
+        <v>2.5944</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4856</v>
+        <v>0.4752</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5825</v>
+        <v>0.545</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6509</v>
+        <v>2.5944</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6509</v>
+        <v>2.608</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="H11" t="n">
-        <v>3.077</v>
+        <v>3.7106</v>
       </c>
       <c r="I11" t="n">
-        <v>3.077</v>
+        <v>2.0037</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="K11" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.077</v>
+        <v>2.0535</v>
       </c>
       <c r="N11" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3762</v>
+        <v>2.4565</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4353</v>
+        <v>0.45</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4575</v>
+        <v>0.4834</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3762</v>
+        <v>2.4565</v>
       </c>
       <c r="F12" t="n">
         <v>2.4247</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2798</v>
+        <v>2.3196</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4176</v>
+        <v>0.4249</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4136</v>
+        <v>0.4223</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2798</v>
+        <v>2.3196</v>
       </c>
       <c r="F13" t="n">
         <v>2.1375</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.237</v>
+        <v>2.3093</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4098</v>
+        <v>0.423</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3941</v>
+        <v>0.4177</v>
       </c>
       <c r="E14" t="n">
-        <v>2.237</v>
+        <v>2.3093</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3533</v>
+        <v>0.8756</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1163</v>
+        <v>1.23</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8702</v>
+        <v>0.8756</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5499</v>
+        <v>0.4728</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1163</v>
+        <v>1.23</v>
       </c>
       <c r="K14" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4336</v>
+        <v>1.7028</v>
       </c>
       <c r="N14" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2322</v>
+        <v>2.2122</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4089</v>
+        <v>0.4052</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3919</v>
+        <v>0.3743</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2322</v>
+        <v>2.2122</v>
       </c>
       <c r="F15" t="n">
         <v>0.767</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2137</v>
+        <v>2.2002</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4055</v>
+        <v>0.403</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3835</v>
+        <v>0.369</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2137</v>
+        <v>2.2002</v>
       </c>
       <c r="F16" t="n">
         <v>1.9854</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1056</v>
+        <v>2.1802</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3857</v>
+        <v>0.3994</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3343</v>
+        <v>0.36</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1056</v>
+        <v>2.1802</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8756</v>
+        <v>2.3533</v>
       </c>
       <c r="G17" t="n">
-        <v>1.23</v>
+        <v>-0.1163</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8756</v>
+        <v>2.8702</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4728</v>
+        <v>1.5499</v>
       </c>
       <c r="J17" t="n">
-        <v>1.23</v>
+        <v>-0.1163</v>
       </c>
       <c r="K17" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L17" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7028</v>
+        <v>1.4336</v>
       </c>
       <c r="N17" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0146</v>
+        <v>2.1053</v>
       </c>
       <c r="C18" t="n">
-        <v>0.369</v>
+        <v>0.3856</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2929</v>
+        <v>0.3266</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0146</v>
+        <v>2.1053</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4822</v>
+        <v>1.8168</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4968</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4822</v>
+        <v>1.8168</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2604</v>
+        <v>1.8168</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4968</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="L18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2364</v>
+        <v>1.8168</v>
       </c>
       <c r="N18" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8258</v>
+        <v>1.9415</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3344</v>
+        <v>0.3556</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2069</v>
+        <v>0.2534</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8258</v>
+        <v>1.9415</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6424</v>
+        <v>-0.4822</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1834</v>
+        <v>2.4968</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6424</v>
+        <v>-0.4822</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8869</v>
+        <v>-0.2604</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1834</v>
+        <v>2.4968</v>
       </c>
       <c r="K19" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L19" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0703</v>
+        <v>2.2364</v>
       </c>
       <c r="N19" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8168</v>
+        <v>1.7752</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3328</v>
+        <v>0.3252</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2028</v>
+        <v>0.1791</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8168</v>
+        <v>1.7752</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8168</v>
+        <v>1.6424</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1834</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8168</v>
+        <v>1.6424</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8168</v>
+        <v>0.8869</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1834</v>
       </c>
       <c r="K20" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8168</v>
+        <v>1.0703</v>
       </c>
       <c r="N20" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3466</v>
+        <v>1.291</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2467</v>
+        <v>0.2365</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0112</v>
+        <v>-0.0372</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3466</v>
+        <v>1.291</v>
       </c>
       <c r="F21" t="n">
         <v>1.3466</v>
@@ -1412,277 +1412,277 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Swisher</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1534</v>
+        <v>1.1903</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2113</v>
+        <v>0.218</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0992</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1534</v>
+        <v>1.1903</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0783</v>
+        <v>1.1473</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0751</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0783</v>
+        <v>1.1473</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5823</v>
+        <v>1.1473</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0751</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6574</v>
+        <v>1.1473</v>
       </c>
       <c r="N22" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Swisher</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1473</v>
+        <v>1.1517</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2102</v>
+        <v>0.211</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1019</v>
+        <v>-0.0994</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1473</v>
+        <v>1.1517</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1473</v>
+        <v>1.0783</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0751</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1473</v>
+        <v>1.0783</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1473</v>
+        <v>0.5823</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.0751</v>
       </c>
       <c r="K23" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1473</v>
+        <v>0.6574</v>
       </c>
       <c r="N23" t="n">
-        <v>69</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.922</v>
+        <v>0.9778</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1689</v>
+        <v>0.1791</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2045</v>
+        <v>-0.1771</v>
       </c>
       <c r="E24" t="n">
-        <v>0.922</v>
+        <v>0.9778</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7982</v>
+        <v>0.6212</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7982</v>
+        <v>0.6212</v>
       </c>
       <c r="I24" t="n">
-        <v>0.431</v>
+        <v>0.6212</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L24" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5548</v>
+        <v>0.6212</v>
       </c>
       <c r="N24" t="n">
-        <v>160</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7432</v>
+        <v>0.9215</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1361</v>
+        <v>0.1688</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2859</v>
+        <v>-0.2022</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7432</v>
+        <v>0.9215</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7432</v>
+        <v>0.7982</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7432</v>
+        <v>0.7982</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7432</v>
+        <v>0.431</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="K25" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7432</v>
+        <v>0.5548</v>
       </c>
       <c r="N25" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6787</v>
+        <v>0.5411</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1243</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3152</v>
+        <v>-0.3721</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6787</v>
+        <v>0.5411</v>
       </c>
       <c r="F26" t="n">
-        <v>2.6787</v>
+        <v>0.7432</v>
       </c>
       <c r="G26" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9439</v>
+        <v>0.7432</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1297</v>
+        <v>0.7432</v>
       </c>
       <c r="J26" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="L26" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1297000000000001</v>
+        <v>0.7432</v>
       </c>
       <c r="N26" t="n">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6212</v>
+        <v>0.5337</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1138</v>
+        <v>0.0978</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3414</v>
+        <v>-0.3754</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6212</v>
+        <v>0.5337</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6212</v>
+        <v>2.6787</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6212</v>
+        <v>3.9439</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6212</v>
+        <v>2.1297</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K27" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6212</v>
+        <v>0.1297000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28">
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0373</v>
+        <v>0.3112</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0068</v>
+        <v>0.057</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6072</v>
+        <v>-0.4748</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0373</v>
+        <v>0.3112</v>
       </c>
       <c r="F28" t="n">
         <v>0.0373</v>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0598</v>
+        <v>0.1007</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.011</v>
+        <v>0.0184</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6514</v>
+        <v>-0.5688</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0598</v>
+        <v>0.1007</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0598</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Noktse</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1271</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0233</v>
+        <v>-0.0146</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6821</v>
+        <v>-0.6494</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1271</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1271</v>
+        <v>-0.3349</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1271</v>
+        <v>-0.3349</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1271</v>
+        <v>-0.3349</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1271</v>
+        <v>-0.3349</v>
       </c>
       <c r="N30" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.186</v>
+        <v>-0.1283</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0341</v>
+        <v>-0.0235</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7089</v>
+        <v>-0.6711</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.186</v>
+        <v>-0.1283</v>
       </c>
       <c r="F31" t="n">
         <v>-0.186</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>NikoM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2157</v>
+        <v>-0.2179</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0395</v>
+        <v>-0.0399</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7224</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2157</v>
+        <v>-0.2179</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2157</v>
+        <v>-0.3244</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2157</v>
+        <v>-0.3244</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2157</v>
+        <v>-0.3244</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2157</v>
+        <v>-0.3244</v>
       </c>
       <c r="N32" t="n">
         <v>105</v>
@@ -1918,78 +1918,78 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>Noktse</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3092</v>
+        <v>-0.256</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0566</v>
+        <v>-0.0469</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.765</v>
+        <v>-0.7282</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3092</v>
+        <v>-0.256</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3092</v>
+        <v>-0.1271</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3092</v>
+        <v>-0.1271</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3092</v>
+        <v>-0.1271</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3092</v>
+        <v>-0.1271</v>
       </c>
       <c r="N33" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NikoM</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3244</v>
+        <v>-0.508</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0594</v>
+        <v>-0.0931</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7719</v>
+        <v>-0.8407</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3244</v>
+        <v>-0.508</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3244</v>
+        <v>-0.2157</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3244</v>
+        <v>-0.2157</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3244</v>
+        <v>-0.2157</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3244</v>
+        <v>-0.2157</v>
       </c>
       <c r="N34" t="n">
         <v>105</v>
@@ -2010,124 +2010,124 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>reversive</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3349</v>
+        <v>-0.5587</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0613</v>
+        <v>-0.1023</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3349</v>
+        <v>-0.5587</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3349</v>
+        <v>-0.5595</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3349</v>
+        <v>-0.5595</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3349</v>
+        <v>-0.5595</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3349</v>
+        <v>-0.5595</v>
       </c>
       <c r="N35" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>reversive</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5595</v>
+        <v>-0.5933</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1025</v>
+        <v>-0.1087</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8789</v>
+        <v>-0.8788</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5595</v>
+        <v>-0.5933</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5595</v>
+        <v>-0.3092</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5595</v>
+        <v>-0.3092</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5595</v>
+        <v>-0.3092</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5595</v>
+        <v>-0.3092</v>
       </c>
       <c r="N36" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9116</v>
+        <v>-0.9832</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.167</v>
+        <v>-0.1801</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0392</v>
+        <v>-1.053</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9116</v>
+        <v>-0.9832</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9116</v>
+        <v>-1.0495</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9116</v>
+        <v>-1.0495</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9116</v>
+        <v>-1.0495</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9116</v>
+        <v>-1.0495</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0495</v>
+        <v>-1.2465</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1922</v>
+        <v>-0.2283</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.102</v>
+        <v>-1.1706</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0495</v>
+        <v>-1.2465</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0495</v>
+        <v>-0.9116</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0495</v>
+        <v>-0.9116</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0495</v>
+        <v>-0.9116</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0495</v>
+        <v>-0.9116</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0988</v>
+        <v>-1.5664</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2013</v>
+        <v>-0.2869</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1244</v>
+        <v>-1.3135</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0988</v>
+        <v>-1.5664</v>
       </c>
       <c r="F39" t="n">
         <v>-1.0988</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1996</v>
+        <v>-1.6266</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2197</v>
+        <v>-0.298</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1703</v>
+        <v>-1.3404</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1996</v>
+        <v>-1.6266</v>
       </c>
       <c r="F40" t="n">
         <v>-1.1996</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6467</v>
+        <v>-1.9631</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3016</v>
+        <v>-0.3596</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3738</v>
+        <v>-1.4907</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6467</v>
+        <v>-1.9631</v>
       </c>
       <c r="F41" t="n">
         <v>-1.3411</v>

--- a/database/event/6869/event_6869_evp_summary.xlsx
+++ b/database/event/6869/event_6869_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9658</v>
+        <v>7.0031</v>
       </c>
       <c r="C2" t="n">
-        <v>1.276</v>
+        <v>1.2828</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4977</v>
+        <v>2.5845</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9658</v>
+        <v>7.0031</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9108</v>
+        <v>2.9392</v>
       </c>
       <c r="G2" t="n">
-        <v>3.748</v>
+        <v>3.7569</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7097</v>
+        <v>4.5922</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5432</v>
+        <v>2.5784</v>
       </c>
       <c r="J2" t="n">
-        <v>3.748</v>
+        <v>3.7569</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -529,7 +529,7 @@
         <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2912</v>
+        <v>6.3353</v>
       </c>
       <c r="N2" t="n">
         <v>120</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5154</v>
+        <v>5.5302</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0103</v>
+        <v>1.013</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8498</v>
+        <v>1.9135</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5154</v>
+        <v>5.5302</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4507</v>
+        <v>2.5273</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0198</v>
+        <v>2.958</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1917</v>
+        <v>3.0459</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7235</v>
+        <v>1.7102</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0198</v>
+        <v>2.958</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -575,7 +575,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7433</v>
+        <v>4.668200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>120</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0297</v>
+        <v>3.9223</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7381</v>
+        <v>0.7185</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1862</v>
+        <v>1.181</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0297</v>
+        <v>3.9223</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3206</v>
+        <v>3.2336</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4998</v>
+        <v>0.4794</v>
       </c>
       <c r="H4" t="n">
-        <v>6.0618</v>
+        <v>5.6976</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2733</v>
+        <v>3.199</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4998</v>
+        <v>0.4794</v>
       </c>
       <c r="K4" t="n">
         <v>76</v>
@@ -621,7 +621,7 @@
         <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7731</v>
+        <v>3.6784</v>
       </c>
       <c r="N4" t="n">
         <v>158</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.635</v>
+        <v>3.6761</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6734</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0099</v>
+        <v>1.0689</v>
       </c>
       <c r="E5" t="n">
-        <v>3.635</v>
+        <v>3.6761</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2076</v>
+        <v>2.2689</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3529</v>
+        <v>1.3327</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3895</v>
+        <v>2.2689</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2903</v>
+        <v>1.2739</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3529</v>
+        <v>1.3327</v>
       </c>
       <c r="K5" t="n">
         <v>43</v>
@@ -667,7 +667,7 @@
         <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6432</v>
+        <v>2.6066</v>
       </c>
       <c r="N5" t="n">
         <v>160</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2962</v>
+        <v>3.2894</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6038</v>
+        <v>0.6025</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8585</v>
+        <v>0.8927</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2962</v>
+        <v>3.2894</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5334</v>
+        <v>2.5801</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7722</v>
+        <v>0.7187</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4643</v>
+        <v>3.2442</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8707</v>
+        <v>1.8215</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7722</v>
+        <v>0.7187</v>
       </c>
       <c r="K6" t="n">
         <v>76</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6429</v>
+        <v>2.5402</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2109</v>
+        <v>3.1585</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5786</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8204</v>
+        <v>0.8331</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2109</v>
+        <v>3.1585</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4411</v>
+        <v>3.3763</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3523</v>
+        <v>-0.3399</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4594</v>
+        <v>6.2337</v>
       </c>
       <c r="I7" t="n">
-        <v>3.488</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3523</v>
+        <v>-0.3399</v>
       </c>
       <c r="K7" t="n">
         <v>86</v>
@@ -759,7 +759,7 @@
         <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1357</v>
+        <v>3.1601</v>
       </c>
       <c r="N7" t="n">
         <v>131</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9825</v>
+        <v>2.9258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5463</v>
+        <v>0.5359</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7184</v>
+        <v>0.7271</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9825</v>
+        <v>2.9258</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3399</v>
+        <v>3.2526</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3891</v>
+        <v>-0.3585</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1255</v>
+        <v>5.769</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3077</v>
+        <v>3.2391</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3891</v>
+        <v>-0.3585</v>
       </c>
       <c r="K8" t="n">
         <v>86</v>
@@ -805,7 +805,7 @@
         <v>45</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9186</v>
+        <v>2.8806</v>
       </c>
       <c r="N8" t="n">
         <v>131</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.922</v>
+        <v>2.8976</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5352</v>
+        <v>0.5308</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6914</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.922</v>
+        <v>2.8976</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7696</v>
+        <v>2.7452</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3368</v>
+        <v>3.3411</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3368</v>
+        <v>3.3411</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3368</v>
+        <v>3.3411</v>
       </c>
       <c r="N9" t="n">
         <v>122</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7192</v>
+        <v>2.6978</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4981</v>
+        <v>0.4942</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6008</v>
+        <v>0.6232</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7192</v>
+        <v>2.6978</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6509</v>
+        <v>2.6295</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.077</v>
+        <v>3.0758</v>
       </c>
       <c r="I10" t="n">
-        <v>3.077</v>
+        <v>3.0758</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.077</v>
+        <v>3.0758</v>
       </c>
       <c r="N10" t="n">
         <v>122</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5944</v>
+        <v>2.67</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4752</v>
+        <v>0.4891</v>
       </c>
       <c r="D11" t="n">
-        <v>0.545</v>
+        <v>0.6105</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5944</v>
+        <v>2.67</v>
       </c>
       <c r="F11" t="n">
-        <v>2.608</v>
+        <v>2.682</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0498</v>
+        <v>0.0514</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7106</v>
+        <v>3.6269</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0037</v>
+        <v>2.0364</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0498</v>
+        <v>0.0514</v>
       </c>
       <c r="K11" t="n">
         <v>76</v>
@@ -943,7 +943,7 @@
         <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0535</v>
+        <v>2.0878</v>
       </c>
       <c r="N11" t="n">
         <v>158</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4565</v>
+        <v>2.5135</v>
       </c>
       <c r="C12" t="n">
-        <v>0.45</v>
+        <v>0.4604</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4834</v>
+        <v>0.5392</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4565</v>
+        <v>2.5135</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4247</v>
+        <v>2.5279</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0485</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1058</v>
+        <v>3.0483</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6771</v>
+        <v>1.7115</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0485</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>76</v>
@@ -989,7 +989,7 @@
         <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6286</v>
+        <v>1.6168</v>
       </c>
       <c r="N12" t="n">
         <v>158</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3196</v>
+        <v>2.3419</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4249</v>
+        <v>0.429</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4223</v>
+        <v>0.4611</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3196</v>
+        <v>2.3419</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1375</v>
+        <v>0.8681</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1423</v>
+        <v>1.2701</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1584</v>
+        <v>0.8681</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1655</v>
+        <v>0.4874</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1423</v>
+        <v>1.2701</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L13" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3078</v>
+        <v>1.7575</v>
       </c>
       <c r="N13" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3093</v>
+        <v>2.2357</v>
       </c>
       <c r="C14" t="n">
-        <v>0.423</v>
+        <v>0.4095</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4177</v>
+        <v>0.4127</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3093</v>
+        <v>2.2357</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8756</v>
+        <v>2.4279</v>
       </c>
       <c r="G14" t="n">
-        <v>1.23</v>
+        <v>-0.1354</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8756</v>
+        <v>2.6728</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4728</v>
+        <v>1.5007</v>
       </c>
       <c r="J14" t="n">
-        <v>1.23</v>
+        <v>-0.1354</v>
       </c>
       <c r="K14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="L14" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7028</v>
+        <v>1.3653</v>
       </c>
       <c r="N14" t="n">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2122</v>
+        <v>2.2232</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4052</v>
+        <v>0.4072</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3743</v>
+        <v>0.407</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2122</v>
+        <v>2.2232</v>
       </c>
       <c r="F15" t="n">
-        <v>0.767</v>
+        <v>0.778</v>
       </c>
       <c r="G15" t="n">
         <v>1.4652</v>
       </c>
       <c r="H15" t="n">
-        <v>0.767</v>
+        <v>0.778</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4142</v>
+        <v>0.4368</v>
       </c>
       <c r="J15" t="n">
         <v>1.4652</v>
@@ -1127,7 +1127,7 @@
         <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8794</v>
+        <v>1.902</v>
       </c>
       <c r="N15" t="n">
         <v>120</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2002</v>
+        <v>2.2033</v>
       </c>
       <c r="C16" t="n">
-        <v>0.403</v>
+        <v>0.4036</v>
       </c>
       <c r="D16" t="n">
-        <v>0.369</v>
+        <v>0.3979</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2002</v>
+        <v>2.2033</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9854</v>
+        <v>1.9759</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2283</v>
+        <v>0.1876</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9854</v>
+        <v>1.9759</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0721</v>
+        <v>1.1094</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2283</v>
+        <v>0.1876</v>
       </c>
       <c r="K16" t="n">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3004</v>
+        <v>1.297</v>
       </c>
       <c r="N16" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1802</v>
+        <v>2.0886</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3994</v>
+        <v>0.3826</v>
       </c>
       <c r="D17" t="n">
-        <v>0.36</v>
+        <v>0.3457</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1802</v>
+        <v>2.0886</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3533</v>
+        <v>1.8001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1163</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8702</v>
+        <v>1.8001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5499</v>
+        <v>1.8001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1163</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4336</v>
+        <v>1.8001</v>
       </c>
       <c r="N17" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1053</v>
+        <v>2.0054</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3856</v>
+        <v>0.3673</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3266</v>
+        <v>0.3078</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1053</v>
+        <v>2.0054</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8168</v>
+        <v>1.8049</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8168</v>
+        <v>1.8049</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8168</v>
+        <v>1.0134</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="K18" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8168</v>
+        <v>1.2274</v>
       </c>
       <c r="N18" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9415</v>
+        <v>1.9984</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3556</v>
+        <v>0.3661</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2534</v>
+        <v>0.3046</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9415</v>
+        <v>1.9984</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4822</v>
+        <v>-0.4711</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4968</v>
+        <v>2.5426</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4822</v>
+        <v>-0.4711</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2604</v>
+        <v>-0.2645</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4968</v>
+        <v>2.5426</v>
       </c>
       <c r="K19" t="n">
         <v>40</v>
@@ -1311,7 +1311,7 @@
         <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2364</v>
+        <v>2.2781</v>
       </c>
       <c r="N19" t="n">
         <v>120</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7752</v>
+        <v>1.6614</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3252</v>
+        <v>0.3043</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1791</v>
+        <v>0.1511</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7752</v>
+        <v>1.6614</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6424</v>
+        <v>1.5105</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1834</v>
+        <v>0.2015</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6424</v>
+        <v>1.5105</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8869</v>
+        <v>0.8481</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1834</v>
+        <v>0.2015</v>
       </c>
       <c r="K20" t="n">
         <v>43</v>
@@ -1357,7 +1357,7 @@
         <v>117</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0703</v>
+        <v>1.0496</v>
       </c>
       <c r="N20" t="n">
         <v>160</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.291</v>
+        <v>1.2614</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2365</v>
+        <v>0.2311</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0372</v>
+        <v>-0.0312</v>
       </c>
       <c r="E21" t="n">
-        <v>1.291</v>
+        <v>1.2614</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3466</v>
+        <v>1.317</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3466</v>
+        <v>1.317</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3466</v>
+        <v>1.317</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3466</v>
+        <v>1.317</v>
       </c>
       <c r="N21" t="n">
         <v>105</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1903</v>
+        <v>1.1536</v>
       </c>
       <c r="C22" t="n">
-        <v>0.218</v>
+        <v>0.2113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0803</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1903</v>
+        <v>1.1536</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1473</v>
+        <v>1.1106</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1473</v>
+        <v>1.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1473</v>
+        <v>1.1106</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1473</v>
+        <v>1.1106</v>
       </c>
       <c r="N22" t="n">
         <v>69</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1517</v>
+        <v>1.1135</v>
       </c>
       <c r="C23" t="n">
-        <v>0.211</v>
+        <v>0.204</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0994</v>
+        <v>-0.0985</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1517</v>
+        <v>1.1135</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0783</v>
+        <v>1.0608</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0751</v>
+        <v>0.0544</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0783</v>
+        <v>1.0608</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5823</v>
+        <v>0.5956</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0751</v>
+        <v>0.0544</v>
       </c>
       <c r="K23" t="n">
         <v>76</v>
@@ -1495,7 +1495,7 @@
         <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6574</v>
+        <v>0.65</v>
       </c>
       <c r="N23" t="n">
         <v>158</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9778</v>
+        <v>0.9969</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1791</v>
+        <v>0.1826</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1771</v>
+        <v>-0.1517</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9778</v>
+        <v>0.9969</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6212</v>
+        <v>0.8439</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1535</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6212</v>
+        <v>0.8439</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6212</v>
+        <v>0.4738</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1535</v>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6212</v>
+        <v>0.6273</v>
       </c>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9215</v>
+        <v>0.9113</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1688</v>
+        <v>0.1669</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2022</v>
+        <v>-0.1906</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9215</v>
+        <v>0.9113</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7982</v>
+        <v>0.5547</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7982</v>
+        <v>0.5547</v>
       </c>
       <c r="I25" t="n">
-        <v>0.431</v>
+        <v>0.5547</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L25" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5548</v>
+        <v>0.5547</v>
       </c>
       <c r="N25" t="n">
-        <v>160</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5411</v>
+        <v>0.5887</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1078</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3721</v>
+        <v>-0.3376</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5411</v>
+        <v>0.5887</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7432</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7432</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7432</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7432</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>122</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5337</v>
+        <v>0.586</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0978</v>
+        <v>0.1073</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3754</v>
+        <v>-0.3388</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5337</v>
+        <v>0.586</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6787</v>
+        <v>2.731</v>
       </c>
       <c r="G27" t="n">
         <v>-2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9439</v>
+        <v>3.8107</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1297</v>
+        <v>2.1396</v>
       </c>
       <c r="J27" t="n">
         <v>-2</v>
@@ -1679,7 +1679,7 @@
         <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1297000000000001</v>
+        <v>0.1396000000000002</v>
       </c>
       <c r="N27" t="n">
         <v>160</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3112</v>
+        <v>0.2889</v>
       </c>
       <c r="C28" t="n">
-        <v>0.057</v>
+        <v>0.0529</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4748</v>
+        <v>-0.4742</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3112</v>
+        <v>0.2889</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0373</v>
+        <v>0.015</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0373</v>
+        <v>0.015</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0373</v>
+        <v>0.015</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0373</v>
+        <v>0.015</v>
       </c>
       <c r="N28" t="n">
         <v>69</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1007</v>
+        <v>0.014</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5688</v>
+        <v>-0.5994</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1007</v>
+        <v>0.014</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0598</v>
+        <v>-0.1465</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0598</v>
+        <v>-0.1465</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0598</v>
+        <v>-0.1465</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0598</v>
+        <v>-0.1465</v>
       </c>
       <c r="N29" t="n">
         <v>79</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0146</v>
+        <v>-0.0059</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6494</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3349</v>
+        <v>-0.2874</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3349</v>
+        <v>-0.2874</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3349</v>
+        <v>-0.2874</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3349</v>
+        <v>-0.2874</v>
       </c>
       <c r="N30" t="n">
         <v>69</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1283</v>
+        <v>-0.1288</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0235</v>
+        <v>-0.0236</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6711</v>
+        <v>-0.6645</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1283</v>
+        <v>-0.1288</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.186</v>
+        <v>-0.1865</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.186</v>
+        <v>-0.1865</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.186</v>
+        <v>-0.1865</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.186</v>
+        <v>-0.1865</v>
       </c>
       <c r="N31" t="n">
         <v>122</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2179</v>
+        <v>-0.2214</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0399</v>
+        <v>-0.0406</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.7066</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2179</v>
+        <v>-0.2214</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3244</v>
+        <v>-0.3279</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3244</v>
+        <v>-0.3279</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3244</v>
+        <v>-0.3279</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3244</v>
+        <v>-0.3279</v>
       </c>
       <c r="N32" t="n">
         <v>105</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.256</v>
+        <v>-0.3084</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0469</v>
+        <v>-0.0565</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7282</v>
+        <v>-0.7463</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.256</v>
+        <v>-0.3084</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1271</v>
+        <v>-0.1795</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1271</v>
+        <v>-0.1795</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1271</v>
+        <v>-0.1795</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1271</v>
+        <v>-0.1795</v>
       </c>
       <c r="N33" t="n">
         <v>105</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.508</v>
+        <v>-0.4169</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0931</v>
+        <v>-0.0764</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8407</v>
+        <v>-0.7957</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.508</v>
+        <v>-0.4169</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2157</v>
+        <v>-0.1246</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2157</v>
+        <v>-0.1246</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2157</v>
+        <v>-0.1246</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2157</v>
+        <v>-0.1246</v>
       </c>
       <c r="N34" t="n">
         <v>105</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5587</v>
+        <v>-0.5481</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1023</v>
+        <v>-0.1004</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.8555</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5587</v>
+        <v>-0.5481</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5595</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5595</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5595</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5595</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>105</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5933</v>
+        <v>-0.5518</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1087</v>
+        <v>-0.1011</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8788</v>
+        <v>-0.8572</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5933</v>
+        <v>-0.5518</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3092</v>
+        <v>-0.2677</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3092</v>
+        <v>-0.2677</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3092</v>
+        <v>-0.2677</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3092</v>
+        <v>-0.2677</v>
       </c>
       <c r="N36" t="n">
         <v>69</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9832</v>
+        <v>-1.0477</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1801</v>
+        <v>-0.1919</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.053</v>
+        <v>-1.0831</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9832</v>
+        <v>-1.0477</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0495</v>
+        <v>-1.114</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0495</v>
+        <v>-1.114</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0495</v>
+        <v>-1.114</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0495</v>
+        <v>-1.114</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2465</v>
+        <v>-1.1863</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2283</v>
+        <v>-0.2173</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1706</v>
+        <v>-1.1462</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2465</v>
+        <v>-1.1863</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9116</v>
+        <v>-0.8514</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9116</v>
+        <v>-0.8514</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9116</v>
+        <v>-0.8514</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9116</v>
+        <v>-0.8514</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5664</v>
+        <v>-1.5357</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2869</v>
+        <v>-0.2813</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3135</v>
+        <v>-1.3054</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5664</v>
+        <v>-1.5357</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0988</v>
+        <v>-1.0681</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0988</v>
+        <v>-1.0681</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0988</v>
+        <v>-1.0681</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0988</v>
+        <v>-1.0681</v>
       </c>
       <c r="N39" t="n">
         <v>69</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6266</v>
+        <v>-1.6078</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.298</v>
+        <v>-0.2945</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3404</v>
+        <v>-1.3382</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6266</v>
+        <v>-1.6078</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1996</v>
+        <v>-1.1808</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1996</v>
+        <v>-1.1808</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1996</v>
+        <v>-1.1808</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1996</v>
+        <v>-1.1808</v>
       </c>
       <c r="N40" t="n">
         <v>79</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9631</v>
+        <v>-1.805</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3596</v>
+        <v>-0.3306</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4907</v>
+        <v>-1.4281</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9631</v>
+        <v>-1.805</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3411</v>
+        <v>-1.2143</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3056</v>
+        <v>-0.2743</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3411</v>
+        <v>-1.2143</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7242</v>
+        <v>-0.6818</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3056</v>
+        <v>-0.2743</v>
       </c>
       <c r="K41" t="n">
         <v>86</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0298</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="N41" t="n">
         <v>131</v>
@@ -2429,10 +2429,10 @@
         <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2269</v>
+        <v>1.2456</v>
       </c>
       <c r="J2" t="n">
-        <v>22.0842</v>
+        <v>22.4208</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9823</v>
       </c>
       <c r="J3" t="n">
-        <v>17.8092</v>
+        <v>17.6814</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6417</v>
+        <v>0.6139</v>
       </c>
       <c r="J4" t="n">
-        <v>11.5506</v>
+        <v>11.0502</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4681</v>
+        <v>0.4363</v>
       </c>
       <c r="J5" t="n">
-        <v>8.425800000000001</v>
+        <v>7.8534</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1071</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9278</v>
+        <v>-1.566</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6434</v>
+        <v>0.5931</v>
       </c>
       <c r="J7" t="n">
-        <v>11.5812</v>
+        <v>10.6758</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1696</v>
+        <v>-0.1515</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.0528</v>
+        <v>-2.727</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2</v>
+        <v>-0.1811</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.6</v>
+        <v>-3.2598</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.269</v>
+        <v>-0.2501</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.842</v>
+        <v>-4.5018</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4603</v>
+        <v>-0.4553</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.285399999999999</v>
+        <v>-8.195399999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4759</v>
+        <v>1.5107</v>
       </c>
       <c r="J12" t="n">
-        <v>25.0903</v>
+        <v>25.6819</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.72</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4604</v>
+        <v>1.496</v>
       </c>
       <c r="J13" t="n">
-        <v>24.8268</v>
+        <v>25.432</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2778</v>
+        <v>1.3068</v>
       </c>
       <c r="J14" t="n">
-        <v>21.7226</v>
+        <v>22.2156</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.19</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4879</v>
+        <v>0.4585</v>
       </c>
       <c r="J15" t="n">
-        <v>8.2943</v>
+        <v>7.7945</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0733</v>
+        <v>-0.0721</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2461</v>
+        <v>-1.2257</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0681</v>
+        <v>1.1094</v>
       </c>
       <c r="J17" t="n">
-        <v>18.1577</v>
+        <v>18.8598</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2971</v>
+        <v>-0.284</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.0507</v>
+        <v>-4.828</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.54</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4557</v>
+        <v>-0.4493</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.7469</v>
+        <v>-7.6381</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.45</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5347</v>
+        <v>-0.5372</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.0899</v>
+        <v>-9.132400000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7589</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.9013</v>
+        <v>-13.6663</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.56</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0643</v>
+        <v>1.0567</v>
       </c>
       <c r="J22" t="n">
-        <v>37.2505</v>
+        <v>36.9845</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4206</v>
+        <v>0.3823</v>
       </c>
       <c r="J23" t="n">
-        <v>14.721</v>
+        <v>13.3805</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1175</v>
+        <v>-0.0907</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.1125</v>
+        <v>-3.1745</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.96</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1878</v>
+        <v>-0.1533</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.573</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4147</v>
+        <v>-0.372</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.5145</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5507</v>
+        <v>0.525</v>
       </c>
       <c r="J27" t="n">
-        <v>19.2745</v>
+        <v>18.375</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1291</v>
+        <v>0.0974</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5185</v>
+        <v>3.409</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.93</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1092</v>
+        <v>-0.092</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.822</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1212</v>
+        <v>-0.1032</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.242</v>
+        <v>-3.612</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3724</v>
+        <v>-0.3593</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.034</v>
+        <v>-12.5755</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2712</v>
+        <v>0.2572</v>
       </c>
       <c r="J32" t="n">
-        <v>6.5088</v>
+        <v>6.1728</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1823</v>
+        <v>0.1654</v>
       </c>
       <c r="J33" t="n">
-        <v>4.3752</v>
+        <v>3.9696</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0582</v>
+        <v>-0.0456</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.3968</v>
+        <v>-1.0944</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.93</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1115</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.676</v>
+        <v>-2.2512</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.86</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1909</v>
+        <v>-0.1703</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.5816</v>
+        <v>-4.0872</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3167</v>
+        <v>0.2594</v>
       </c>
       <c r="J37" t="n">
-        <v>7.6008</v>
+        <v>6.2256</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1387</v>
+        <v>0.1043</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3288</v>
+        <v>2.5032</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.123</v>
+        <v>0.0914</v>
       </c>
       <c r="J39" t="n">
-        <v>2.952</v>
+        <v>2.1936</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0301</v>
+        <v>0.0198</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7224</v>
+        <v>0.4752</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.83</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2252</v>
+        <v>-0.2048</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.4048</v>
+        <v>-4.9152</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.67</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2167</v>
+        <v>1.2205</v>
       </c>
       <c r="J42" t="n">
-        <v>27.9841</v>
+        <v>28.0715</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.35</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7651</v>
+        <v>0.749</v>
       </c>
       <c r="J43" t="n">
-        <v>17.5973</v>
+        <v>17.227</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0447</v>
+        <v>0.0334</v>
       </c>
       <c r="J44" t="n">
-        <v>1.0281</v>
+        <v>0.7682</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0447</v>
+        <v>0.0334</v>
       </c>
       <c r="J45" t="n">
-        <v>1.0281</v>
+        <v>0.7682</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.44</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.3468</v>
+        <v>-1.3993</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.9764</v>
+        <v>-32.1839</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7427</v>
+        <v>0.7064</v>
       </c>
       <c r="J47" t="n">
-        <v>17.0821</v>
+        <v>16.2472</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6474</v>
+        <v>0.6155</v>
       </c>
       <c r="J48" t="n">
-        <v>14.8902</v>
+        <v>14.1565</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.081</v>
+        <v>-0.0654</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.863</v>
+        <v>-1.5042</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1204</v>
+        <v>-0.1018</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.7692</v>
+        <v>-2.3414</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3006</v>
+        <v>-0.2835</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.9138</v>
+        <v>-6.5205</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.84</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4191</v>
+        <v>1.4391</v>
       </c>
       <c r="J52" t="n">
-        <v>34.0584</v>
+        <v>34.5384</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8404</v>
+        <v>0.8245</v>
       </c>
       <c r="J53" t="n">
-        <v>20.1696</v>
+        <v>19.788</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.96</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1971</v>
+        <v>-0.1624</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.7304</v>
+        <v>-3.8976</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4241</v>
+        <v>-0.3822</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.1784</v>
+        <v>-9.172800000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8797</v>
+        <v>-0.8661</v>
       </c>
       <c r="J56" t="n">
-        <v>-21.1128</v>
+        <v>-20.7864</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6127</v>
+        <v>0.5856</v>
       </c>
       <c r="J57" t="n">
-        <v>14.7048</v>
+        <v>14.0544</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0049</v>
+        <v>0.0027</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1176</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.96</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.68</v>
+        <v>-1.3632</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3063</v>
+        <v>-0.2886</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.3512</v>
+        <v>-6.9264</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3063</v>
+        <v>-0.2886</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.3512</v>
+        <v>-6.9264</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.599</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>12.579</v>
+        <v>12.3522</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5198</v>
+        <v>0.5091</v>
       </c>
       <c r="J63" t="n">
-        <v>10.9158</v>
+        <v>10.6911</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.17</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4711</v>
+        <v>0.4465</v>
       </c>
       <c r="J64" t="n">
-        <v>9.8931</v>
+        <v>9.3765</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.17</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4711</v>
+        <v>0.4465</v>
       </c>
       <c r="J65" t="n">
-        <v>9.8931</v>
+        <v>9.3765</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2048</v>
+        <v>0.1761</v>
       </c>
       <c r="J66" t="n">
-        <v>4.3008</v>
+        <v>3.6981</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.19</v>
+        <v>0.1532</v>
       </c>
       <c r="J67" t="n">
-        <v>3.99</v>
+        <v>3.2172</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0828</v>
+        <v>-0.0699</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.7388</v>
+        <v>-1.4679</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2356</v>
+        <v>-0.2175</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.9476</v>
+        <v>-4.5675</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.67</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3572</v>
+        <v>-0.3426</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.5012</v>
+        <v>-7.1946</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.64</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3844</v>
+        <v>-0.3716</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.0724</v>
+        <v>-7.8036</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0935</v>
+        <v>1.1042</v>
       </c>
       <c r="J72" t="n">
-        <v>21.87</v>
+        <v>22.084</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.44</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0203</v>
+        <v>1.0207</v>
       </c>
       <c r="J73" t="n">
-        <v>20.406</v>
+        <v>20.414</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5034</v>
+        <v>0.4681</v>
       </c>
       <c r="J74" t="n">
-        <v>10.068</v>
+        <v>9.362</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.99</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.818</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.83</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5151</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.058</v>
+        <v>-10.302</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.924</v>
+        <v>0.891</v>
       </c>
       <c r="J77" t="n">
-        <v>18.48</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0141</v>
+        <v>0.0097</v>
       </c>
       <c r="J78" t="n">
-        <v>0.282</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.7</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3386</v>
+        <v>-0.3227</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.772</v>
+        <v>-6.454</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.7</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3386</v>
+        <v>-0.3227</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.772</v>
+        <v>-6.454</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.63</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4021</v>
+        <v>-0.3912</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.042</v>
+        <v>-7.824</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.27</v>
       </c>
       <c r="I82" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J82" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0206</v>
+        <v>1.0318</v>
       </c>
       <c r="J83" t="n">
-        <v>16.3296</v>
+        <v>16.5088</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.3</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7119</v>
+        <v>0.6945</v>
       </c>
       <c r="J84" t="n">
-        <v>11.3904</v>
+        <v>11.112</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.27</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6509</v>
+        <v>0.6297</v>
       </c>
       <c r="J85" t="n">
-        <v>10.4144</v>
+        <v>10.0752</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.25</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6093</v>
+        <v>0.5856</v>
       </c>
       <c r="J86" t="n">
-        <v>9.748799999999999</v>
+        <v>9.3696</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.91</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0883</v>
+        <v>-0.0702</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.4128</v>
+        <v>-1.1232</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.84</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1714</v>
+        <v>-0.155</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.7424</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.66</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3487</v>
+        <v>-0.3371</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.5792</v>
+        <v>-5.3936</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5239</v>
+        <v>-0.5248</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.382400000000001</v>
+        <v>-8.396800000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.43</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5501</v>
+        <v>-0.5546</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.801600000000001</v>
+        <v>-8.8736</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2.28</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J92" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>2.03</v>
       </c>
       <c r="I93" t="n">
-        <v>1.6951</v>
+        <v>1.7422</v>
       </c>
       <c r="J93" t="n">
-        <v>27.1216</v>
+        <v>27.8752</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9544</v>
+        <v>0.9579</v>
       </c>
       <c r="J94" t="n">
-        <v>15.2704</v>
+        <v>15.3264</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1475</v>
+        <v>0.1152</v>
       </c>
       <c r="J95" t="n">
-        <v>2.36</v>
+        <v>1.8432</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.9</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.43</v>
+        <v>-0.3997</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.88</v>
+        <v>-6.3952</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.37</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8592</v>
+        <v>0.8577</v>
       </c>
       <c r="J97" t="n">
-        <v>13.7472</v>
+        <v>13.7232</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.68</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.335</v>
+        <v>-0.3215</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.36</v>
+        <v>-5.144</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.61</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.3552</v>
+        <v>-6.1776</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.43</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5553</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.8848</v>
+        <v>-8.976000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.42</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.571</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.023999999999999</v>
+        <v>-9.135999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1269</v>
+        <v>1.1397</v>
       </c>
       <c r="J102" t="n">
-        <v>23.6649</v>
+        <v>23.9337</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.45</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0149</v>
+        <v>1.0163</v>
       </c>
       <c r="J103" t="n">
-        <v>21.3129</v>
+        <v>21.3423</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="J104" t="n">
-        <v>12.1191</v>
+        <v>11.508</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4196</v>
+        <v>0.3875</v>
       </c>
       <c r="J105" t="n">
-        <v>8.8116</v>
+        <v>8.137499999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3211</v>
+        <v>0.2892</v>
       </c>
       <c r="J106" t="n">
-        <v>6.7431</v>
+        <v>6.0732</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.55</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9964</v>
+        <v>0.9739</v>
       </c>
       <c r="J107" t="n">
-        <v>20.9244</v>
+        <v>20.4519</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.21</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4709</v>
+        <v>0.414</v>
       </c>
       <c r="J108" t="n">
-        <v>9.8889</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2455</v>
+        <v>-0.2256</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.1555</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3773</v>
+        <v>-0.3643</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.9233</v>
+        <v>-7.6503</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.41</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5928</v>
+        <v>-0.6078</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.4488</v>
+        <v>-12.7638</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3211</v>
+        <v>1.3445</v>
       </c>
       <c r="J112" t="n">
-        <v>31.7064</v>
+        <v>32.268</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.43</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0139</v>
+        <v>1.0132</v>
       </c>
       <c r="J113" t="n">
-        <v>24.3336</v>
+        <v>24.3168</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.024</v>
+        <v>-0.0186</v>
       </c>
       <c r="J114" t="n">
-        <v>-0.576</v>
+        <v>-0.4464</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.024</v>
+        <v>-0.0186</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.576</v>
+        <v>-0.4464</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9406</v>
+        <v>-0.9337</v>
       </c>
       <c r="J116" t="n">
-        <v>-22.5744</v>
+        <v>-22.4088</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4265</v>
+        <v>0.3695</v>
       </c>
       <c r="J117" t="n">
-        <v>10.236</v>
+        <v>8.868</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.06</v>
       </c>
       <c r="I118" t="n">
-        <v>0.177</v>
+        <v>0.1383</v>
       </c>
       <c r="J118" t="n">
-        <v>4.248</v>
+        <v>3.3192</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.3464</v>
+        <v>-1.0704</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.91</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1321</v>
+        <v>-0.1137</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.1704</v>
+        <v>-2.7288</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3715</v>
+        <v>-0.3582</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.916</v>
+        <v>-8.5968</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7471</v>
+        <v>0.7165</v>
       </c>
       <c r="J122" t="n">
-        <v>17.9304</v>
+        <v>17.196</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4061</v>
+        <v>0.3647</v>
       </c>
       <c r="J123" t="n">
-        <v>9.7464</v>
+        <v>8.752800000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3812</v>
+        <v>0.3402</v>
       </c>
       <c r="J124" t="n">
-        <v>9.1488</v>
+        <v>8.1648</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3262</v>
+        <v>-0.2842</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.8288</v>
+        <v>-6.8208</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.84</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5047</v>
+        <v>-0.4628</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.1128</v>
+        <v>-11.1072</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.85</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2598</v>
+        <v>1.2543</v>
       </c>
       <c r="J127" t="n">
-        <v>30.2352</v>
+        <v>30.1032</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0633</v>
+        <v>-0.0496</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.5192</v>
+        <v>-1.1904</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.86</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1969</v>
+        <v>-0.1763</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.7256</v>
+        <v>-4.2312</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2179</v>
+        <v>-0.1974</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.2296</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2384</v>
+        <v>-0.2183</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.7216</v>
+        <v>-5.2392</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.97</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0124</v>
+        <v>0.002</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.1984</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.88</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1327</v>
+        <v>-0.1163</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.1232</v>
+        <v>-1.8608</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.67</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3426</v>
+        <v>-0.3297</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.4816</v>
+        <v>-5.2752</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.48</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5103</v>
+        <v>-0.5097</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.1648</v>
+        <v>-8.155200000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5365</v>
+        <v>-0.5393</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.584</v>
+        <v>-8.6288</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J137" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.82</v>
       </c>
       <c r="I138" t="n">
-        <v>1.4504</v>
+        <v>1.4796</v>
       </c>
       <c r="J138" t="n">
-        <v>23.2064</v>
+        <v>23.6736</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4063</v>
+        <v>0.3737</v>
       </c>
       <c r="J139" t="n">
-        <v>6.5008</v>
+        <v>5.9792</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.13</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3343</v>
+        <v>0.3001</v>
       </c>
       <c r="J140" t="n">
-        <v>5.3488</v>
+        <v>4.8016</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.92</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3759</v>
+        <v>-0.3458</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.0144</v>
+        <v>-5.5328</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.68</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8137</v>
+        <v>0.7449</v>
       </c>
       <c r="J142" t="n">
-        <v>19.5288</v>
+        <v>17.8776</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3958</v>
+        <v>0.3334</v>
       </c>
       <c r="J143" t="n">
-        <v>9.4992</v>
+        <v>8.0016</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2019</v>
+        <v>0.1603</v>
       </c>
       <c r="J144" t="n">
-        <v>4.8456</v>
+        <v>3.8472</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1711</v>
+        <v>-0.1511</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.1064</v>
+        <v>-3.6264</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2653</v>
+        <v>-0.2469</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.3672</v>
+        <v>-5.9256</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.57</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7861</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="J147" t="n">
-        <v>18.8664</v>
+        <v>20.4552</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.28</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4456</v>
+        <v>0.4484</v>
       </c>
       <c r="J148" t="n">
-        <v>10.6944</v>
+        <v>10.7616</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1572</v>
+        <v>-0.1373</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.7728</v>
+        <v>-3.2952</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4362</v>
+        <v>-0.4297</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.4688</v>
+        <v>-10.3128</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4362</v>
+        <v>-0.4297</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.4688</v>
+        <v>-10.3128</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.8</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1871</v>
+        <v>-0.1668</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.8065</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.78</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2093</v>
+        <v>-0.1909</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.1395</v>
+        <v>-2.8635</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3135</v>
+        <v>-0.3031</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.7025</v>
+        <v>-4.5465</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.28</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6693</v>
+        <v>-0.6924</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.0395</v>
+        <v>-10.386</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.26</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6872</v>
+        <v>-0.7139</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.308</v>
+        <v>-10.7085</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.17</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8477</v>
+        <v>1.9096</v>
       </c>
       <c r="J157" t="n">
-        <v>27.7155</v>
+        <v>28.644</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>2.01</v>
       </c>
       <c r="I158" t="n">
-        <v>1.6668</v>
+        <v>1.7114</v>
       </c>
       <c r="J158" t="n">
-        <v>25.002</v>
+        <v>25.671</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0576</v>
+        <v>1.075</v>
       </c>
       <c r="J159" t="n">
-        <v>15.864</v>
+        <v>16.125</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.09</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2278</v>
+        <v>0.1926</v>
       </c>
       <c r="J160" t="n">
-        <v>3.417</v>
+        <v>2.889</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.08</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2006</v>
+        <v>0.1658</v>
       </c>
       <c r="J161" t="n">
-        <v>3.009</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1283</v>
+        <v>1.141</v>
       </c>
       <c r="J162" t="n">
-        <v>21.4377</v>
+        <v>21.679</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1015</v>
+        <v>1.1133</v>
       </c>
       <c r="J163" t="n">
-        <v>20.9285</v>
+        <v>21.1527</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.3</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7402</v>
+        <v>0.7166</v>
       </c>
       <c r="J164" t="n">
-        <v>14.0638</v>
+        <v>13.6154</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1856</v>
+        <v>0.1578</v>
       </c>
       <c r="J165" t="n">
-        <v>3.5264</v>
+        <v>2.9982</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0534</v>
+        <v>0.0368</v>
       </c>
       <c r="J166" t="n">
-        <v>1.0146</v>
+        <v>0.6992</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.35</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7284</v>
+        <v>0.6835</v>
       </c>
       <c r="J167" t="n">
-        <v>13.8396</v>
+        <v>12.9865</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0241</v>
+        <v>0.0185</v>
       </c>
       <c r="J168" t="n">
-        <v>0.4579</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1994</v>
+        <v>-0.1807</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.7886</v>
+        <v>-3.4333</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.61</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4155</v>
+        <v>-0.4056</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.8945</v>
+        <v>-7.7064</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5115</v>
+        <v>-0.5129</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.718500000000001</v>
+        <v>-9.745100000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.16</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4113</v>
+        <v>0.3599</v>
       </c>
       <c r="J172" t="n">
-        <v>7.8147</v>
+        <v>6.8381</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0554</v>
       </c>
       <c r="J173" t="n">
-        <v>1.4212</v>
+        <v>1.0526</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1566</v>
+        <v>-0.1399</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.9754</v>
+        <v>-2.6581</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3501</v>
+        <v>-0.3349</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.6519</v>
+        <v>-6.3631</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.46</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5436</v>
+        <v>-0.5494</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.3284</v>
+        <v>-10.4386</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2804</v>
+        <v>1.2989</v>
       </c>
       <c r="J177" t="n">
-        <v>24.3276</v>
+        <v>24.6791</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0067</v>
+        <v>1.0058</v>
       </c>
       <c r="J178" t="n">
-        <v>19.1273</v>
+        <v>19.1102</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4261</v>
+        <v>0.3932</v>
       </c>
       <c r="J179" t="n">
-        <v>8.0959</v>
+        <v>7.4708</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4023</v>
+        <v>0.3693</v>
       </c>
       <c r="J180" t="n">
-        <v>7.6437</v>
+        <v>7.0167</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4408</v>
+        <v>-0.4013</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.3752</v>
+        <v>-7.6247</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.34</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6513</v>
+        <v>0.5926</v>
       </c>
       <c r="J182" t="n">
-        <v>19.539</v>
+        <v>17.778</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.166</v>
+        <v>0.1303</v>
       </c>
       <c r="J183" t="n">
-        <v>4.98</v>
+        <v>3.909</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.05</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1441</v>
+        <v>0.1115</v>
       </c>
       <c r="J184" t="n">
-        <v>4.323</v>
+        <v>3.345</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.96</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0599</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.244</v>
+        <v>-1.797</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3131</v>
+        <v>-0.2961</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.393000000000001</v>
+        <v>-8.882999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5631</v>
+        <v>0.5242</v>
       </c>
       <c r="J187" t="n">
-        <v>16.893</v>
+        <v>15.726</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3998</v>
+        <v>0.36</v>
       </c>
       <c r="J188" t="n">
-        <v>11.994</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3753</v>
+        <v>0.336</v>
       </c>
       <c r="J189" t="n">
-        <v>11.259</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.1</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3252</v>
+        <v>0.2875</v>
       </c>
       <c r="J190" t="n">
-        <v>9.756</v>
+        <v>8.625</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3598</v>
+        <v>-0.3172</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.794</v>
+        <v>-9.516</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.5</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1047</v>
+        <v>1.1161</v>
       </c>
       <c r="J192" t="n">
-        <v>26.5128</v>
+        <v>26.7864</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.43</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0014</v>
+        <v>0.9986</v>
       </c>
       <c r="J193" t="n">
-        <v>24.0336</v>
+        <v>23.9664</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.34</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8335</v>
+        <v>0.8113</v>
       </c>
       <c r="J194" t="n">
-        <v>20.004</v>
+        <v>19.4712</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2674</v>
+        <v>-0.2292</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.4176</v>
+        <v>-5.5008</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6705</v>
+        <v>-0.6395</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.092</v>
+        <v>-15.348</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.25</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5621</v>
+        <v>0.5095</v>
       </c>
       <c r="J197" t="n">
-        <v>13.4904</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1273</v>
+        <v>0.0968</v>
       </c>
       <c r="J198" t="n">
-        <v>3.0552</v>
+        <v>2.3232</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1996</v>
+        <v>-0.1808</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.7904</v>
+        <v>-4.3392</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.6</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4246</v>
+        <v>-0.4156</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.1904</v>
+        <v>-9.974399999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.59</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4334</v>
+        <v>-0.4253</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.4016</v>
+        <v>-10.2072</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.97</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0352</v>
+        <v>-0.0257</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.7392</v>
+        <v>-0.5397</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.89</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1395</v>
+        <v>-0.1241</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.9295</v>
+        <v>-2.6061</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.88</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1508</v>
+        <v>-0.1352</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.1668</v>
+        <v>-2.8392</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.74</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2895</v>
+        <v>-0.2724</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.0795</v>
+        <v>-5.7204</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.47</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5304</v>
+        <v>-0.5336</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.1384</v>
+        <v>-11.2056</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.85</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5365</v>
+        <v>1.5726</v>
       </c>
       <c r="J207" t="n">
-        <v>32.2665</v>
+        <v>33.0246</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.36</v>
       </c>
       <c r="I208" t="n">
-        <v>0.855</v>
+        <v>0.8381</v>
       </c>
       <c r="J208" t="n">
-        <v>17.955</v>
+        <v>17.6001</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.3</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>15.5274</v>
+        <v>15.0402</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4431</v>
+        <v>0.4113</v>
       </c>
       <c r="J210" t="n">
-        <v>9.305099999999999</v>
+        <v>8.6373</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6627</v>
+        <v>-0.6338</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.9167</v>
+        <v>-13.3098</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.64</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2737</v>
+        <v>1.2917</v>
       </c>
       <c r="J212" t="n">
-        <v>26.7477</v>
+        <v>27.1257</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.37</v>
       </c>
       <c r="I213" t="n">
-        <v>0.876</v>
+        <v>0.86</v>
       </c>
       <c r="J213" t="n">
-        <v>18.396</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.27</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6821</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>14.3241</v>
+        <v>13.7697</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4214</v>
+        <v>0.3892</v>
       </c>
       <c r="J215" t="n">
-        <v>8.849399999999999</v>
+        <v>8.1732</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.97</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1852</v>
+        <v>-0.155</v>
       </c>
       <c r="J216" t="n">
-        <v>-3.8892</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.4</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7815</v>
+        <v>0.7346</v>
       </c>
       <c r="J217" t="n">
-        <v>16.4115</v>
+        <v>15.4266</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.99</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0192</v>
+        <v>-0.0142</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.4032</v>
+        <v>-0.2982</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.93</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1061</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.2281</v>
+        <v>-1.8963</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1291</v>
+        <v>-0.1118</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.7111</v>
+        <v>-2.3478</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6335</v>
+        <v>-0.6556</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.3035</v>
+        <v>-13.7676</v>
       </c>
     </row>
   </sheetData>
